--- a/plantillas/PLANTILLA_PAREJA.xlsx
+++ b/plantillas/PLANTILLA_PAREJA.xlsx
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="56">
   <si>
     <t xml:space="preserve">Cómo se rellena esta plantilla</t>
   </si>
@@ -64,28 +64,34 @@
     <t xml:space="preserve">4. Sesión: nombre de la sesión (Pierna, Tracc, Empuje…). Opcional; si se deja vacío será «Entreno lunes».</t>
   </si>
   <si>
-    <t xml:space="preserve">5. Bloque: Activación / P. Principal / Accesorios / Vuelta a la calma. Se pone al empezar cada bloque; las filas de debajo heredan.</t>
+    <t xml:space="preserve">5. Bloque: Activación / P. Principal / Aeróbico / Accesorios / Vuelta a la calma. Se pone al empezar cada bloque; las filas de debajo heredan.</t>
   </si>
   <si>
-    <t xml:space="preserve">6. A la app solo pasa el bloque «P. Principal». Lo demás se queda en el Excel.</t>
+    <t xml:space="preserve">6. A la app pasan la Activación (como lista para marcar, sin carga), la P. Principal y el Aeróbico. Accesorios y Vuelta a la calma se quedan en el Excel.</t>
   </si>
   <si>
-    <t xml:space="preserve">7. Series y Reps: solo números. Lo que no sea número (6-8, EA, por lado, 3x4") va en «Nota reps».</t>
+    <t xml:space="preserve">7. Aeróbico (al final de la sesión): Bloque «Aeróbico», Ejercicio = Carrera, Bicicleta…, y Minutos + Zona o Intervalos («10 Z2, 3 Z4, 10 Z2»). Una fila por sesión. Se graba con el pulsómetro dentro de la misma sesión.</t>
   </si>
   <si>
-    <t xml:space="preserve">8. Biseries: dos filas seguidas (una por ejercicio) o «Ejercicio A + Ejercicio B» en una fila.</t>
+    <t xml:space="preserve">8. RPE pre y RPE post: para anotar lo que os diga el cliente, en la primera fila de cada día. No pasan a la app (allí lo anota el cliente).</t>
   </si>
   <si>
-    <t xml:space="preserve">9. Unilateral / Pliometría: elige «Sí» si lo es. En pliometría, Reps = contactos.</t>
+    <t xml:space="preserve">9. Series y Reps: solo números. Lo que no sea número (6-8, EA, por lado, 3x4") va en «Nota reps».</t>
   </si>
   <si>
-    <t xml:space="preserve">10. Peso O / Peso S: un peso por cliente. Cambia la letra del título por la inicial de cada uno (Peso A, Peso M…) y usa esas mismas letras en la pestaña «fuentes» de Google (por ejemplo «O: apodo de uno, S: apodo del otro»).</t>
+    <t xml:space="preserve">10. Biseries: dos filas seguidas (una por ejercicio) o «Ejercicio A + Ejercicio B» en una fila.</t>
   </si>
   <si>
-    <t xml:space="preserve">11. No cambies los títulos de la fila 4 ni la celda «SEMANA DEL». Puedes añadir más pestañas (ANUAL, RM…): se ignoran.</t>
+    <t xml:space="preserve">11. Unilateral / Pliometría: elige «Sí» si lo es. En pliometría, Reps = contactos.</t>
   </si>
   <si>
-    <t xml:space="preserve">12. Para el mes siguiente: Archivo &gt; Guardar una copia, cambia la fecha amarilla y borra las filas.</t>
+    <t xml:space="preserve">12. Peso O / Peso S: un peso por cliente. Cambia la letra del título por la inicial de cada uno (Peso A, Peso M…) y usa esas mismas letras en la pestaña «fuentes» de Google (por ejemplo «O: apodo de uno, S: apodo del otro»).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13. No cambies los títulos de la fila 4 ni la celda «SEMANA DEL». Puedes añadir más pestañas (ANUAL, RM…): se ignoran.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14. Para el mes siguiente: Archivo &gt; Guardar una copia, cambia la fecha amarilla y borra las filas.</t>
   </si>
   <si>
     <t xml:space="preserve">Ejemplo (esta pestaña no se importa):</t>
@@ -127,7 +133,22 @@
     <t xml:space="preserve">Pliometría</t>
   </si>
   <si>
+    <t xml:space="preserve">Minutos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zona</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Intervalos</t>
+  </si>
+  <si>
     <t xml:space="preserve">Observaciones</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RPE pre</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RPE post</t>
   </si>
   <si>
     <t xml:space="preserve">Lunes</t>
@@ -163,6 +184,15 @@
     <t xml:space="preserve">Drop jump</t>
   </si>
   <si>
+    <t xml:space="preserve">Aeróbico</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bicicleta</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Z2</t>
+  </si>
+  <si>
     <t xml:space="preserve">Jueves</t>
   </si>
   <si>
@@ -173,6 +203,12 @@
   </si>
   <si>
     <t xml:space="preserve">Descanso 2 min</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Carrera</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5 Z2, 4x(2 Z4, 1 Z1)</t>
   </si>
   <si>
     <t xml:space="preserve">SEMANA DEL</t>
@@ -664,7 +700,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:M22"/>
+  <dimension ref="A1:R26"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="15"/>
@@ -676,7 +712,11 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="8" style="0" width="9"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="7"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="11" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="0" width="7"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="0" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="0" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="17" style="0" width="8"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -700,6 +740,11 @@
       <c r="K3" s="2"/>
       <c r="L3" s="2"/>
       <c r="M3" s="2"/>
+      <c r="N3" s="2"/>
+      <c r="O3" s="2"/>
+      <c r="P3" s="2"/>
+      <c r="Q3" s="2"/>
+      <c r="R3" s="2"/>
     </row>
     <row r="4" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="s">
@@ -717,6 +762,11 @@
       <c r="K4" s="2"/>
       <c r="L4" s="2"/>
       <c r="M4" s="2"/>
+      <c r="N4" s="2"/>
+      <c r="O4" s="2"/>
+      <c r="P4" s="2"/>
+      <c r="Q4" s="2"/>
+      <c r="R4" s="2"/>
     </row>
     <row r="5" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="s">
@@ -734,6 +784,11 @@
       <c r="K5" s="2"/>
       <c r="L5" s="2"/>
       <c r="M5" s="2"/>
+      <c r="N5" s="2"/>
+      <c r="O5" s="2"/>
+      <c r="P5" s="2"/>
+      <c r="Q5" s="2"/>
+      <c r="R5" s="2"/>
     </row>
     <row r="6" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="s">
@@ -751,6 +806,11 @@
       <c r="K6" s="2"/>
       <c r="L6" s="2"/>
       <c r="M6" s="2"/>
+      <c r="N6" s="2"/>
+      <c r="O6" s="2"/>
+      <c r="P6" s="2"/>
+      <c r="Q6" s="2"/>
+      <c r="R6" s="2"/>
     </row>
     <row r="7" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="2" t="s">
@@ -768,6 +828,11 @@
       <c r="K7" s="2"/>
       <c r="L7" s="2"/>
       <c r="M7" s="2"/>
+      <c r="N7" s="2"/>
+      <c r="O7" s="2"/>
+      <c r="P7" s="2"/>
+      <c r="Q7" s="2"/>
+      <c r="R7" s="2"/>
     </row>
     <row r="8" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
@@ -785,6 +850,11 @@
       <c r="K8" s="2"/>
       <c r="L8" s="2"/>
       <c r="M8" s="2"/>
+      <c r="N8" s="2"/>
+      <c r="O8" s="2"/>
+      <c r="P8" s="2"/>
+      <c r="Q8" s="2"/>
+      <c r="R8" s="2"/>
     </row>
     <row r="9" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="2" t="s">
@@ -802,6 +872,11 @@
       <c r="K9" s="2"/>
       <c r="L9" s="2"/>
       <c r="M9" s="2"/>
+      <c r="N9" s="2"/>
+      <c r="O9" s="2"/>
+      <c r="P9" s="2"/>
+      <c r="Q9" s="2"/>
+      <c r="R9" s="2"/>
     </row>
     <row r="10" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="2" t="s">
@@ -819,6 +894,11 @@
       <c r="K10" s="2"/>
       <c r="L10" s="2"/>
       <c r="M10" s="2"/>
+      <c r="N10" s="2"/>
+      <c r="O10" s="2"/>
+      <c r="P10" s="2"/>
+      <c r="Q10" s="2"/>
+      <c r="R10" s="2"/>
     </row>
     <row r="11" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="2" t="s">
@@ -836,6 +916,11 @@
       <c r="K11" s="2"/>
       <c r="L11" s="2"/>
       <c r="M11" s="2"/>
+      <c r="N11" s="2"/>
+      <c r="O11" s="2"/>
+      <c r="P11" s="2"/>
+      <c r="Q11" s="2"/>
+      <c r="R11" s="2"/>
     </row>
     <row r="12" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="2" t="s">
@@ -853,6 +938,11 @@
       <c r="K12" s="2"/>
       <c r="L12" s="2"/>
       <c r="M12" s="2"/>
+      <c r="N12" s="2"/>
+      <c r="O12" s="2"/>
+      <c r="P12" s="2"/>
+      <c r="Q12" s="2"/>
+      <c r="R12" s="2"/>
     </row>
     <row r="13" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="2" t="s">
@@ -870,6 +960,11 @@
       <c r="K13" s="2"/>
       <c r="L13" s="2"/>
       <c r="M13" s="2"/>
+      <c r="N13" s="2"/>
+      <c r="O13" s="2"/>
+      <c r="P13" s="2"/>
+      <c r="Q13" s="2"/>
+      <c r="R13" s="2"/>
     </row>
     <row r="14" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="2" t="s">
@@ -887,175 +982,195 @@
       <c r="K14" s="2"/>
       <c r="L14" s="2"/>
       <c r="M14" s="2"/>
-    </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="3" t="s">
+      <c r="N14" s="2"/>
+      <c r="O14" s="2"/>
+      <c r="P14" s="2"/>
+      <c r="Q14" s="2"/>
+      <c r="R14" s="2"/>
+    </row>
+    <row r="15" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="2" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="17" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="4" t="s">
+      <c r="B15" s="2"/>
+      <c r="C15" s="2"/>
+      <c r="D15" s="2"/>
+      <c r="E15" s="2"/>
+      <c r="F15" s="2"/>
+      <c r="G15" s="2"/>
+      <c r="H15" s="2"/>
+      <c r="I15" s="2"/>
+      <c r="J15" s="2"/>
+      <c r="K15" s="2"/>
+      <c r="L15" s="2"/>
+      <c r="M15" s="2"/>
+      <c r="N15" s="2"/>
+      <c r="O15" s="2"/>
+      <c r="P15" s="2"/>
+      <c r="Q15" s="2"/>
+      <c r="R15" s="2"/>
+    </row>
+    <row r="16" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="B17" s="4" t="s">
+      <c r="B16" s="2"/>
+      <c r="C16" s="2"/>
+      <c r="D16" s="2"/>
+      <c r="E16" s="2"/>
+      <c r="F16" s="2"/>
+      <c r="G16" s="2"/>
+      <c r="H16" s="2"/>
+      <c r="I16" s="2"/>
+      <c r="J16" s="2"/>
+      <c r="K16" s="2"/>
+      <c r="L16" s="2"/>
+      <c r="M16" s="2"/>
+      <c r="N16" s="2"/>
+      <c r="O16" s="2"/>
+      <c r="P16" s="2"/>
+      <c r="Q16" s="2"/>
+      <c r="R16" s="2"/>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="C17" s="4" t="s">
+    </row>
+    <row r="19" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="D17" s="4" t="s">
+      <c r="B19" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="E17" s="4" t="s">
+      <c r="C19" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="F17" s="4" t="s">
+      <c r="D19" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="G17" s="4" t="s">
+      <c r="E19" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="H17" s="4" t="s">
+      <c r="F19" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="I17" s="4" t="s">
+      <c r="G19" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="J17" s="4" t="s">
+      <c r="H19" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="K17" s="4" t="s">
+      <c r="I19" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="L17" s="4" t="s">
+      <c r="J19" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="M17" s="4" t="s">
+      <c r="K19" s="4" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="5" t="s">
+      <c r="L19" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="B18" s="5" t="s">
+      <c r="M19" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="C18" s="5" t="s">
+      <c r="N19" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="D18" s="5" t="s">
+      <c r="O19" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="E18" s="5" t="n">
+      <c r="P19" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q19" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="R19" s="4" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="B20" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="C20" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="D20" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="E20" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="F18" s="5" t="n">
+      <c r="F20" s="5" t="n">
         <v>10</v>
       </c>
-      <c r="G18" s="5"/>
-      <c r="H18" s="5"/>
-      <c r="I18" s="5"/>
-      <c r="J18" s="5"/>
-      <c r="K18" s="5"/>
-      <c r="L18" s="5"/>
-      <c r="M18" s="5"/>
-    </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="5"/>
-      <c r="B19" s="5"/>
-      <c r="C19" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="D19" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="E19" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="F19" s="5" t="n">
-        <v>8</v>
-      </c>
-      <c r="G19" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="H19" s="5" t="n">
-        <v>24</v>
-      </c>
-      <c r="I19" s="5" t="n">
-        <v>12</v>
-      </c>
-      <c r="J19" s="5" t="n">
-        <v>7</v>
-      </c>
-      <c r="K19" s="5"/>
-      <c r="L19" s="5"/>
-      <c r="M19" s="5"/>
-    </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="5"/>
-      <c r="B20" s="5"/>
-      <c r="C20" s="5"/>
-      <c r="D20" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="E20" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="F20" s="5" t="n">
-        <v>8</v>
-      </c>
-      <c r="G20" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="H20" s="5" t="n">
-        <v>10</v>
-      </c>
-      <c r="I20" s="5" t="n">
-        <v>6</v>
-      </c>
+      <c r="G20" s="5"/>
+      <c r="H20" s="5"/>
+      <c r="I20" s="5"/>
       <c r="J20" s="5"/>
-      <c r="K20" s="5" t="s">
-        <v>36</v>
-      </c>
+      <c r="K20" s="5"/>
       <c r="L20" s="5"/>
       <c r="M20" s="5"/>
+      <c r="N20" s="5"/>
+      <c r="O20" s="5"/>
+      <c r="P20" s="5"/>
+      <c r="Q20" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="R20" s="5" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="5"/>
       <c r="B21" s="5"/>
-      <c r="C21" s="5"/>
+      <c r="C21" s="5" t="s">
+        <v>38</v>
+      </c>
       <c r="D21" s="5" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E21" s="5" t="n">
         <v>3</v>
       </c>
       <c r="F21" s="5" t="n">
-        <v>6</v>
-      </c>
-      <c r="G21" s="5"/>
-      <c r="H21" s="5"/>
-      <c r="I21" s="5"/>
-      <c r="J21" s="5"/>
+        <v>8</v>
+      </c>
+      <c r="G21" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="H21" s="5" t="n">
+        <v>24</v>
+      </c>
+      <c r="I21" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="J21" s="5" t="n">
+        <v>7</v>
+      </c>
       <c r="K21" s="5"/>
-      <c r="L21" s="5" t="s">
-        <v>36</v>
-      </c>
+      <c r="L21" s="5"/>
       <c r="M21" s="5"/>
+      <c r="N21" s="5"/>
+      <c r="O21" s="5"/>
+      <c r="P21" s="5"/>
+      <c r="Q21" s="5"/>
+      <c r="R21" s="5"/>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B22" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="C22" s="5" t="s">
-        <v>31</v>
-      </c>
+      <c r="A22" s="5"/>
+      <c r="B22" s="5"/>
+      <c r="C22" s="5"/>
       <c r="D22" s="5" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E22" s="5" t="n">
         <v>3</v>
@@ -1063,36 +1178,169 @@
       <c r="F22" s="5" t="n">
         <v>8</v>
       </c>
-      <c r="G22" s="5"/>
+      <c r="G22" s="5" t="s">
+        <v>42</v>
+      </c>
       <c r="H22" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="I22" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="J22" s="5"/>
+      <c r="K22" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="L22" s="5"/>
+      <c r="M22" s="5"/>
+      <c r="N22" s="5"/>
+      <c r="O22" s="5"/>
+      <c r="P22" s="5"/>
+      <c r="Q22" s="5"/>
+      <c r="R22" s="5"/>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="5"/>
+      <c r="B23" s="5"/>
+      <c r="C23" s="5"/>
+      <c r="D23" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="E23" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="F23" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="G23" s="5"/>
+      <c r="H23" s="5"/>
+      <c r="I23" s="5"/>
+      <c r="J23" s="5"/>
+      <c r="K23" s="5"/>
+      <c r="L23" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="M23" s="5"/>
+      <c r="N23" s="5"/>
+      <c r="O23" s="5"/>
+      <c r="P23" s="5"/>
+      <c r="Q23" s="5"/>
+      <c r="R23" s="5"/>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="5"/>
+      <c r="B24" s="5"/>
+      <c r="C24" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="D24" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="E24" s="5"/>
+      <c r="F24" s="5"/>
+      <c r="G24" s="5"/>
+      <c r="H24" s="5"/>
+      <c r="I24" s="5"/>
+      <c r="J24" s="5"/>
+      <c r="K24" s="5"/>
+      <c r="L24" s="5"/>
+      <c r="M24" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="N24" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="O24" s="5"/>
+      <c r="P24" s="5"/>
+      <c r="Q24" s="5"/>
+      <c r="R24" s="5"/>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="B25" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="C25" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="D25" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="I22" s="5" t="n">
+      <c r="E25" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="F25" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="G25" s="5"/>
+      <c r="H25" s="5" t="n">
+        <v>50</v>
+      </c>
+      <c r="I25" s="5" t="n">
         <v>25</v>
       </c>
-      <c r="J22" s="5" t="n">
+      <c r="J25" s="5" t="n">
         <v>8</v>
       </c>
-      <c r="K22" s="5"/>
-      <c r="L22" s="5"/>
-      <c r="M22" s="5" t="s">
-        <v>41</v>
-      </c>
+      <c r="K25" s="5"/>
+      <c r="L25" s="5"/>
+      <c r="M25" s="5"/>
+      <c r="N25" s="5"/>
+      <c r="O25" s="5"/>
+      <c r="P25" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="Q25" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="R25" s="5" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="5"/>
+      <c r="B26" s="5"/>
+      <c r="C26" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="D26" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="E26" s="5"/>
+      <c r="F26" s="5"/>
+      <c r="G26" s="5"/>
+      <c r="H26" s="5"/>
+      <c r="I26" s="5"/>
+      <c r="J26" s="5"/>
+      <c r="K26" s="5"/>
+      <c r="L26" s="5"/>
+      <c r="M26" s="5"/>
+      <c r="N26" s="5"/>
+      <c r="O26" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="P26" s="5"/>
+      <c r="Q26" s="5"/>
+      <c r="R26" s="5"/>
     </row>
   </sheetData>
-  <mergeCells count="12">
-    <mergeCell ref="A3:M3"/>
-    <mergeCell ref="A4:M4"/>
-    <mergeCell ref="A5:M5"/>
-    <mergeCell ref="A6:M6"/>
-    <mergeCell ref="A7:M7"/>
-    <mergeCell ref="A8:M8"/>
-    <mergeCell ref="A9:M9"/>
-    <mergeCell ref="A10:M10"/>
-    <mergeCell ref="A11:M11"/>
-    <mergeCell ref="A12:M12"/>
-    <mergeCell ref="A13:M13"/>
-    <mergeCell ref="A14:M14"/>
+  <mergeCells count="14">
+    <mergeCell ref="A3:R3"/>
+    <mergeCell ref="A4:R4"/>
+    <mergeCell ref="A5:R5"/>
+    <mergeCell ref="A6:R6"/>
+    <mergeCell ref="A7:R7"/>
+    <mergeCell ref="A8:R8"/>
+    <mergeCell ref="A9:R9"/>
+    <mergeCell ref="A10:R10"/>
+    <mergeCell ref="A11:R11"/>
+    <mergeCell ref="A12:R12"/>
+    <mergeCell ref="A13:R13"/>
+    <mergeCell ref="A14:R14"/>
+    <mergeCell ref="A15:R15"/>
+    <mergeCell ref="A16:R16"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -1109,7 +1357,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:M84"/>
+  <dimension ref="A1:R84"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="15"/>
@@ -1121,12 +1369,16 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="8" style="0" width="9"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="7"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="11" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="0" width="7"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="0" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="0" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="17" style="0" width="8"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="6" t="s">
-        <v>42</v>
+        <v>54</v>
       </c>
       <c r="B1" s="7" t="n">
         <v>46328</v>
@@ -1138,49 +1390,64 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="8" t="s">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="B2" s="9"/>
     </row>
     <row r="4" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="I4" s="4" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="J4" s="4" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="K4" s="4" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="L4" s="4" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="M4" s="4" t="s">
-        <v>26</v>
+        <v>28</v>
+      </c>
+      <c r="N4" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="O4" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="P4" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q4" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="R4" s="4" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1196,7 +1463,12 @@
       <c r="J5" s="10"/>
       <c r="K5" s="10"/>
       <c r="L5" s="10"/>
-      <c r="M5" s="5"/>
+      <c r="M5" s="10"/>
+      <c r="N5" s="10"/>
+      <c r="O5" s="5"/>
+      <c r="P5" s="5"/>
+      <c r="Q5" s="10"/>
+      <c r="R5" s="10"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="5"/>
@@ -1211,7 +1483,12 @@
       <c r="J6" s="10"/>
       <c r="K6" s="10"/>
       <c r="L6" s="10"/>
-      <c r="M6" s="5"/>
+      <c r="M6" s="10"/>
+      <c r="N6" s="10"/>
+      <c r="O6" s="5"/>
+      <c r="P6" s="5"/>
+      <c r="Q6" s="10"/>
+      <c r="R6" s="10"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="5"/>
@@ -1226,7 +1503,12 @@
       <c r="J7" s="10"/>
       <c r="K7" s="10"/>
       <c r="L7" s="10"/>
-      <c r="M7" s="5"/>
+      <c r="M7" s="10"/>
+      <c r="N7" s="10"/>
+      <c r="O7" s="5"/>
+      <c r="P7" s="5"/>
+      <c r="Q7" s="10"/>
+      <c r="R7" s="10"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="5"/>
@@ -1241,7 +1523,12 @@
       <c r="J8" s="10"/>
       <c r="K8" s="10"/>
       <c r="L8" s="10"/>
-      <c r="M8" s="5"/>
+      <c r="M8" s="10"/>
+      <c r="N8" s="10"/>
+      <c r="O8" s="5"/>
+      <c r="P8" s="5"/>
+      <c r="Q8" s="10"/>
+      <c r="R8" s="10"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="5"/>
@@ -1256,7 +1543,12 @@
       <c r="J9" s="10"/>
       <c r="K9" s="10"/>
       <c r="L9" s="10"/>
-      <c r="M9" s="5"/>
+      <c r="M9" s="10"/>
+      <c r="N9" s="10"/>
+      <c r="O9" s="5"/>
+      <c r="P9" s="5"/>
+      <c r="Q9" s="10"/>
+      <c r="R9" s="10"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="5"/>
@@ -1271,7 +1563,12 @@
       <c r="J10" s="10"/>
       <c r="K10" s="10"/>
       <c r="L10" s="10"/>
-      <c r="M10" s="5"/>
+      <c r="M10" s="10"/>
+      <c r="N10" s="10"/>
+      <c r="O10" s="5"/>
+      <c r="P10" s="5"/>
+      <c r="Q10" s="10"/>
+      <c r="R10" s="10"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="5"/>
@@ -1286,7 +1583,12 @@
       <c r="J11" s="10"/>
       <c r="K11" s="10"/>
       <c r="L11" s="10"/>
-      <c r="M11" s="5"/>
+      <c r="M11" s="10"/>
+      <c r="N11" s="10"/>
+      <c r="O11" s="5"/>
+      <c r="P11" s="5"/>
+      <c r="Q11" s="10"/>
+      <c r="R11" s="10"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="5"/>
@@ -1301,7 +1603,12 @@
       <c r="J12" s="10"/>
       <c r="K12" s="10"/>
       <c r="L12" s="10"/>
-      <c r="M12" s="5"/>
+      <c r="M12" s="10"/>
+      <c r="N12" s="10"/>
+      <c r="O12" s="5"/>
+      <c r="P12" s="5"/>
+      <c r="Q12" s="10"/>
+      <c r="R12" s="10"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="5"/>
@@ -1316,7 +1623,12 @@
       <c r="J13" s="10"/>
       <c r="K13" s="10"/>
       <c r="L13" s="10"/>
-      <c r="M13" s="5"/>
+      <c r="M13" s="10"/>
+      <c r="N13" s="10"/>
+      <c r="O13" s="5"/>
+      <c r="P13" s="5"/>
+      <c r="Q13" s="10"/>
+      <c r="R13" s="10"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="5"/>
@@ -1331,7 +1643,12 @@
       <c r="J14" s="10"/>
       <c r="K14" s="10"/>
       <c r="L14" s="10"/>
-      <c r="M14" s="5"/>
+      <c r="M14" s="10"/>
+      <c r="N14" s="10"/>
+      <c r="O14" s="5"/>
+      <c r="P14" s="5"/>
+      <c r="Q14" s="10"/>
+      <c r="R14" s="10"/>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="5"/>
@@ -1346,7 +1663,12 @@
       <c r="J15" s="10"/>
       <c r="K15" s="10"/>
       <c r="L15" s="10"/>
-      <c r="M15" s="5"/>
+      <c r="M15" s="10"/>
+      <c r="N15" s="10"/>
+      <c r="O15" s="5"/>
+      <c r="P15" s="5"/>
+      <c r="Q15" s="10"/>
+      <c r="R15" s="10"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="5"/>
@@ -1361,7 +1683,12 @@
       <c r="J16" s="10"/>
       <c r="K16" s="10"/>
       <c r="L16" s="10"/>
-      <c r="M16" s="5"/>
+      <c r="M16" s="10"/>
+      <c r="N16" s="10"/>
+      <c r="O16" s="5"/>
+      <c r="P16" s="5"/>
+      <c r="Q16" s="10"/>
+      <c r="R16" s="10"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="5"/>
@@ -1376,7 +1703,12 @@
       <c r="J17" s="10"/>
       <c r="K17" s="10"/>
       <c r="L17" s="10"/>
-      <c r="M17" s="5"/>
+      <c r="M17" s="10"/>
+      <c r="N17" s="10"/>
+      <c r="O17" s="5"/>
+      <c r="P17" s="5"/>
+      <c r="Q17" s="10"/>
+      <c r="R17" s="10"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="5"/>
@@ -1391,7 +1723,12 @@
       <c r="J18" s="10"/>
       <c r="K18" s="10"/>
       <c r="L18" s="10"/>
-      <c r="M18" s="5"/>
+      <c r="M18" s="10"/>
+      <c r="N18" s="10"/>
+      <c r="O18" s="5"/>
+      <c r="P18" s="5"/>
+      <c r="Q18" s="10"/>
+      <c r="R18" s="10"/>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="5"/>
@@ -1406,7 +1743,12 @@
       <c r="J19" s="10"/>
       <c r="K19" s="10"/>
       <c r="L19" s="10"/>
-      <c r="M19" s="5"/>
+      <c r="M19" s="10"/>
+      <c r="N19" s="10"/>
+      <c r="O19" s="5"/>
+      <c r="P19" s="5"/>
+      <c r="Q19" s="10"/>
+      <c r="R19" s="10"/>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="5"/>
@@ -1421,7 +1763,12 @@
       <c r="J20" s="10"/>
       <c r="K20" s="10"/>
       <c r="L20" s="10"/>
-      <c r="M20" s="5"/>
+      <c r="M20" s="10"/>
+      <c r="N20" s="10"/>
+      <c r="O20" s="5"/>
+      <c r="P20" s="5"/>
+      <c r="Q20" s="10"/>
+      <c r="R20" s="10"/>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="5"/>
@@ -1436,7 +1783,12 @@
       <c r="J21" s="10"/>
       <c r="K21" s="10"/>
       <c r="L21" s="10"/>
-      <c r="M21" s="5"/>
+      <c r="M21" s="10"/>
+      <c r="N21" s="10"/>
+      <c r="O21" s="5"/>
+      <c r="P21" s="5"/>
+      <c r="Q21" s="10"/>
+      <c r="R21" s="10"/>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="5"/>
@@ -1451,7 +1803,12 @@
       <c r="J22" s="10"/>
       <c r="K22" s="10"/>
       <c r="L22" s="10"/>
-      <c r="M22" s="5"/>
+      <c r="M22" s="10"/>
+      <c r="N22" s="10"/>
+      <c r="O22" s="5"/>
+      <c r="P22" s="5"/>
+      <c r="Q22" s="10"/>
+      <c r="R22" s="10"/>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="5"/>
@@ -1466,7 +1823,12 @@
       <c r="J23" s="10"/>
       <c r="K23" s="10"/>
       <c r="L23" s="10"/>
-      <c r="M23" s="5"/>
+      <c r="M23" s="10"/>
+      <c r="N23" s="10"/>
+      <c r="O23" s="5"/>
+      <c r="P23" s="5"/>
+      <c r="Q23" s="10"/>
+      <c r="R23" s="10"/>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="5"/>
@@ -1481,7 +1843,12 @@
       <c r="J24" s="10"/>
       <c r="K24" s="10"/>
       <c r="L24" s="10"/>
-      <c r="M24" s="5"/>
+      <c r="M24" s="10"/>
+      <c r="N24" s="10"/>
+      <c r="O24" s="5"/>
+      <c r="P24" s="5"/>
+      <c r="Q24" s="10"/>
+      <c r="R24" s="10"/>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="5"/>
@@ -1496,7 +1863,12 @@
       <c r="J25" s="10"/>
       <c r="K25" s="10"/>
       <c r="L25" s="10"/>
-      <c r="M25" s="5"/>
+      <c r="M25" s="10"/>
+      <c r="N25" s="10"/>
+      <c r="O25" s="5"/>
+      <c r="P25" s="5"/>
+      <c r="Q25" s="10"/>
+      <c r="R25" s="10"/>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="5"/>
@@ -1511,7 +1883,12 @@
       <c r="J26" s="10"/>
       <c r="K26" s="10"/>
       <c r="L26" s="10"/>
-      <c r="M26" s="5"/>
+      <c r="M26" s="10"/>
+      <c r="N26" s="10"/>
+      <c r="O26" s="5"/>
+      <c r="P26" s="5"/>
+      <c r="Q26" s="10"/>
+      <c r="R26" s="10"/>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="5"/>
@@ -1526,7 +1903,12 @@
       <c r="J27" s="10"/>
       <c r="K27" s="10"/>
       <c r="L27" s="10"/>
-      <c r="M27" s="5"/>
+      <c r="M27" s="10"/>
+      <c r="N27" s="10"/>
+      <c r="O27" s="5"/>
+      <c r="P27" s="5"/>
+      <c r="Q27" s="10"/>
+      <c r="R27" s="10"/>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="5"/>
@@ -1541,7 +1923,12 @@
       <c r="J28" s="10"/>
       <c r="K28" s="10"/>
       <c r="L28" s="10"/>
-      <c r="M28" s="5"/>
+      <c r="M28" s="10"/>
+      <c r="N28" s="10"/>
+      <c r="O28" s="5"/>
+      <c r="P28" s="5"/>
+      <c r="Q28" s="10"/>
+      <c r="R28" s="10"/>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="5"/>
@@ -1556,7 +1943,12 @@
       <c r="J29" s="10"/>
       <c r="K29" s="10"/>
       <c r="L29" s="10"/>
-      <c r="M29" s="5"/>
+      <c r="M29" s="10"/>
+      <c r="N29" s="10"/>
+      <c r="O29" s="5"/>
+      <c r="P29" s="5"/>
+      <c r="Q29" s="10"/>
+      <c r="R29" s="10"/>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="5"/>
@@ -1571,7 +1963,12 @@
       <c r="J30" s="10"/>
       <c r="K30" s="10"/>
       <c r="L30" s="10"/>
-      <c r="M30" s="5"/>
+      <c r="M30" s="10"/>
+      <c r="N30" s="10"/>
+      <c r="O30" s="5"/>
+      <c r="P30" s="5"/>
+      <c r="Q30" s="10"/>
+      <c r="R30" s="10"/>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="5"/>
@@ -1586,7 +1983,12 @@
       <c r="J31" s="10"/>
       <c r="K31" s="10"/>
       <c r="L31" s="10"/>
-      <c r="M31" s="5"/>
+      <c r="M31" s="10"/>
+      <c r="N31" s="10"/>
+      <c r="O31" s="5"/>
+      <c r="P31" s="5"/>
+      <c r="Q31" s="10"/>
+      <c r="R31" s="10"/>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="5"/>
@@ -1601,7 +2003,12 @@
       <c r="J32" s="10"/>
       <c r="K32" s="10"/>
       <c r="L32" s="10"/>
-      <c r="M32" s="5"/>
+      <c r="M32" s="10"/>
+      <c r="N32" s="10"/>
+      <c r="O32" s="5"/>
+      <c r="P32" s="5"/>
+      <c r="Q32" s="10"/>
+      <c r="R32" s="10"/>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="5"/>
@@ -1616,7 +2023,12 @@
       <c r="J33" s="10"/>
       <c r="K33" s="10"/>
       <c r="L33" s="10"/>
-      <c r="M33" s="5"/>
+      <c r="M33" s="10"/>
+      <c r="N33" s="10"/>
+      <c r="O33" s="5"/>
+      <c r="P33" s="5"/>
+      <c r="Q33" s="10"/>
+      <c r="R33" s="10"/>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="5"/>
@@ -1631,7 +2043,12 @@
       <c r="J34" s="10"/>
       <c r="K34" s="10"/>
       <c r="L34" s="10"/>
-      <c r="M34" s="5"/>
+      <c r="M34" s="10"/>
+      <c r="N34" s="10"/>
+      <c r="O34" s="5"/>
+      <c r="P34" s="5"/>
+      <c r="Q34" s="10"/>
+      <c r="R34" s="10"/>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="5"/>
@@ -1646,7 +2063,12 @@
       <c r="J35" s="10"/>
       <c r="K35" s="10"/>
       <c r="L35" s="10"/>
-      <c r="M35" s="5"/>
+      <c r="M35" s="10"/>
+      <c r="N35" s="10"/>
+      <c r="O35" s="5"/>
+      <c r="P35" s="5"/>
+      <c r="Q35" s="10"/>
+      <c r="R35" s="10"/>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="5"/>
@@ -1661,7 +2083,12 @@
       <c r="J36" s="10"/>
       <c r="K36" s="10"/>
       <c r="L36" s="10"/>
-      <c r="M36" s="5"/>
+      <c r="M36" s="10"/>
+      <c r="N36" s="10"/>
+      <c r="O36" s="5"/>
+      <c r="P36" s="5"/>
+      <c r="Q36" s="10"/>
+      <c r="R36" s="10"/>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="5"/>
@@ -1676,7 +2103,12 @@
       <c r="J37" s="10"/>
       <c r="K37" s="10"/>
       <c r="L37" s="10"/>
-      <c r="M37" s="5"/>
+      <c r="M37" s="10"/>
+      <c r="N37" s="10"/>
+      <c r="O37" s="5"/>
+      <c r="P37" s="5"/>
+      <c r="Q37" s="10"/>
+      <c r="R37" s="10"/>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="5"/>
@@ -1691,7 +2123,12 @@
       <c r="J38" s="10"/>
       <c r="K38" s="10"/>
       <c r="L38" s="10"/>
-      <c r="M38" s="5"/>
+      <c r="M38" s="10"/>
+      <c r="N38" s="10"/>
+      <c r="O38" s="5"/>
+      <c r="P38" s="5"/>
+      <c r="Q38" s="10"/>
+      <c r="R38" s="10"/>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="5"/>
@@ -1706,7 +2143,12 @@
       <c r="J39" s="10"/>
       <c r="K39" s="10"/>
       <c r="L39" s="10"/>
-      <c r="M39" s="5"/>
+      <c r="M39" s="10"/>
+      <c r="N39" s="10"/>
+      <c r="O39" s="5"/>
+      <c r="P39" s="5"/>
+      <c r="Q39" s="10"/>
+      <c r="R39" s="10"/>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="5"/>
@@ -1721,7 +2163,12 @@
       <c r="J40" s="10"/>
       <c r="K40" s="10"/>
       <c r="L40" s="10"/>
-      <c r="M40" s="5"/>
+      <c r="M40" s="10"/>
+      <c r="N40" s="10"/>
+      <c r="O40" s="5"/>
+      <c r="P40" s="5"/>
+      <c r="Q40" s="10"/>
+      <c r="R40" s="10"/>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="5"/>
@@ -1736,7 +2183,12 @@
       <c r="J41" s="10"/>
       <c r="K41" s="10"/>
       <c r="L41" s="10"/>
-      <c r="M41" s="5"/>
+      <c r="M41" s="10"/>
+      <c r="N41" s="10"/>
+      <c r="O41" s="5"/>
+      <c r="P41" s="5"/>
+      <c r="Q41" s="10"/>
+      <c r="R41" s="10"/>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="5"/>
@@ -1751,7 +2203,12 @@
       <c r="J42" s="10"/>
       <c r="K42" s="10"/>
       <c r="L42" s="10"/>
-      <c r="M42" s="5"/>
+      <c r="M42" s="10"/>
+      <c r="N42" s="10"/>
+      <c r="O42" s="5"/>
+      <c r="P42" s="5"/>
+      <c r="Q42" s="10"/>
+      <c r="R42" s="10"/>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="5"/>
@@ -1766,7 +2223,12 @@
       <c r="J43" s="10"/>
       <c r="K43" s="10"/>
       <c r="L43" s="10"/>
-      <c r="M43" s="5"/>
+      <c r="M43" s="10"/>
+      <c r="N43" s="10"/>
+      <c r="O43" s="5"/>
+      <c r="P43" s="5"/>
+      <c r="Q43" s="10"/>
+      <c r="R43" s="10"/>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="5"/>
@@ -1781,7 +2243,12 @@
       <c r="J44" s="10"/>
       <c r="K44" s="10"/>
       <c r="L44" s="10"/>
-      <c r="M44" s="5"/>
+      <c r="M44" s="10"/>
+      <c r="N44" s="10"/>
+      <c r="O44" s="5"/>
+      <c r="P44" s="5"/>
+      <c r="Q44" s="10"/>
+      <c r="R44" s="10"/>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="5"/>
@@ -1796,7 +2263,12 @@
       <c r="J45" s="10"/>
       <c r="K45" s="10"/>
       <c r="L45" s="10"/>
-      <c r="M45" s="5"/>
+      <c r="M45" s="10"/>
+      <c r="N45" s="10"/>
+      <c r="O45" s="5"/>
+      <c r="P45" s="5"/>
+      <c r="Q45" s="10"/>
+      <c r="R45" s="10"/>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="5"/>
@@ -1811,7 +2283,12 @@
       <c r="J46" s="10"/>
       <c r="K46" s="10"/>
       <c r="L46" s="10"/>
-      <c r="M46" s="5"/>
+      <c r="M46" s="10"/>
+      <c r="N46" s="10"/>
+      <c r="O46" s="5"/>
+      <c r="P46" s="5"/>
+      <c r="Q46" s="10"/>
+      <c r="R46" s="10"/>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="5"/>
@@ -1826,7 +2303,12 @@
       <c r="J47" s="10"/>
       <c r="K47" s="10"/>
       <c r="L47" s="10"/>
-      <c r="M47" s="5"/>
+      <c r="M47" s="10"/>
+      <c r="N47" s="10"/>
+      <c r="O47" s="5"/>
+      <c r="P47" s="5"/>
+      <c r="Q47" s="10"/>
+      <c r="R47" s="10"/>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="5"/>
@@ -1841,7 +2323,12 @@
       <c r="J48" s="10"/>
       <c r="K48" s="10"/>
       <c r="L48" s="10"/>
-      <c r="M48" s="5"/>
+      <c r="M48" s="10"/>
+      <c r="N48" s="10"/>
+      <c r="O48" s="5"/>
+      <c r="P48" s="5"/>
+      <c r="Q48" s="10"/>
+      <c r="R48" s="10"/>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="5"/>
@@ -1856,7 +2343,12 @@
       <c r="J49" s="10"/>
       <c r="K49" s="10"/>
       <c r="L49" s="10"/>
-      <c r="M49" s="5"/>
+      <c r="M49" s="10"/>
+      <c r="N49" s="10"/>
+      <c r="O49" s="5"/>
+      <c r="P49" s="5"/>
+      <c r="Q49" s="10"/>
+      <c r="R49" s="10"/>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="5"/>
@@ -1871,7 +2363,12 @@
       <c r="J50" s="10"/>
       <c r="K50" s="10"/>
       <c r="L50" s="10"/>
-      <c r="M50" s="5"/>
+      <c r="M50" s="10"/>
+      <c r="N50" s="10"/>
+      <c r="O50" s="5"/>
+      <c r="P50" s="5"/>
+      <c r="Q50" s="10"/>
+      <c r="R50" s="10"/>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="5"/>
@@ -1886,7 +2383,12 @@
       <c r="J51" s="10"/>
       <c r="K51" s="10"/>
       <c r="L51" s="10"/>
-      <c r="M51" s="5"/>
+      <c r="M51" s="10"/>
+      <c r="N51" s="10"/>
+      <c r="O51" s="5"/>
+      <c r="P51" s="5"/>
+      <c r="Q51" s="10"/>
+      <c r="R51" s="10"/>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="5"/>
@@ -1901,7 +2403,12 @@
       <c r="J52" s="10"/>
       <c r="K52" s="10"/>
       <c r="L52" s="10"/>
-      <c r="M52" s="5"/>
+      <c r="M52" s="10"/>
+      <c r="N52" s="10"/>
+      <c r="O52" s="5"/>
+      <c r="P52" s="5"/>
+      <c r="Q52" s="10"/>
+      <c r="R52" s="10"/>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="5"/>
@@ -1916,7 +2423,12 @@
       <c r="J53" s="10"/>
       <c r="K53" s="10"/>
       <c r="L53" s="10"/>
-      <c r="M53" s="5"/>
+      <c r="M53" s="10"/>
+      <c r="N53" s="10"/>
+      <c r="O53" s="5"/>
+      <c r="P53" s="5"/>
+      <c r="Q53" s="10"/>
+      <c r="R53" s="10"/>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="5"/>
@@ -1931,7 +2443,12 @@
       <c r="J54" s="10"/>
       <c r="K54" s="10"/>
       <c r="L54" s="10"/>
-      <c r="M54" s="5"/>
+      <c r="M54" s="10"/>
+      <c r="N54" s="10"/>
+      <c r="O54" s="5"/>
+      <c r="P54" s="5"/>
+      <c r="Q54" s="10"/>
+      <c r="R54" s="10"/>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="5"/>
@@ -1946,7 +2463,12 @@
       <c r="J55" s="10"/>
       <c r="K55" s="10"/>
       <c r="L55" s="10"/>
-      <c r="M55" s="5"/>
+      <c r="M55" s="10"/>
+      <c r="N55" s="10"/>
+      <c r="O55" s="5"/>
+      <c r="P55" s="5"/>
+      <c r="Q55" s="10"/>
+      <c r="R55" s="10"/>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="5"/>
@@ -1961,7 +2483,12 @@
       <c r="J56" s="10"/>
       <c r="K56" s="10"/>
       <c r="L56" s="10"/>
-      <c r="M56" s="5"/>
+      <c r="M56" s="10"/>
+      <c r="N56" s="10"/>
+      <c r="O56" s="5"/>
+      <c r="P56" s="5"/>
+      <c r="Q56" s="10"/>
+      <c r="R56" s="10"/>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="5"/>
@@ -1976,7 +2503,12 @@
       <c r="J57" s="10"/>
       <c r="K57" s="10"/>
       <c r="L57" s="10"/>
-      <c r="M57" s="5"/>
+      <c r="M57" s="10"/>
+      <c r="N57" s="10"/>
+      <c r="O57" s="5"/>
+      <c r="P57" s="5"/>
+      <c r="Q57" s="10"/>
+      <c r="R57" s="10"/>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="5"/>
@@ -1991,7 +2523,12 @@
       <c r="J58" s="10"/>
       <c r="K58" s="10"/>
       <c r="L58" s="10"/>
-      <c r="M58" s="5"/>
+      <c r="M58" s="10"/>
+      <c r="N58" s="10"/>
+      <c r="O58" s="5"/>
+      <c r="P58" s="5"/>
+      <c r="Q58" s="10"/>
+      <c r="R58" s="10"/>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="5"/>
@@ -2006,7 +2543,12 @@
       <c r="J59" s="10"/>
       <c r="K59" s="10"/>
       <c r="L59" s="10"/>
-      <c r="M59" s="5"/>
+      <c r="M59" s="10"/>
+      <c r="N59" s="10"/>
+      <c r="O59" s="5"/>
+      <c r="P59" s="5"/>
+      <c r="Q59" s="10"/>
+      <c r="R59" s="10"/>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="5"/>
@@ -2021,7 +2563,12 @@
       <c r="J60" s="10"/>
       <c r="K60" s="10"/>
       <c r="L60" s="10"/>
-      <c r="M60" s="5"/>
+      <c r="M60" s="10"/>
+      <c r="N60" s="10"/>
+      <c r="O60" s="5"/>
+      <c r="P60" s="5"/>
+      <c r="Q60" s="10"/>
+      <c r="R60" s="10"/>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="5"/>
@@ -2036,7 +2583,12 @@
       <c r="J61" s="10"/>
       <c r="K61" s="10"/>
       <c r="L61" s="10"/>
-      <c r="M61" s="5"/>
+      <c r="M61" s="10"/>
+      <c r="N61" s="10"/>
+      <c r="O61" s="5"/>
+      <c r="P61" s="5"/>
+      <c r="Q61" s="10"/>
+      <c r="R61" s="10"/>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="5"/>
@@ -2051,7 +2603,12 @@
       <c r="J62" s="10"/>
       <c r="K62" s="10"/>
       <c r="L62" s="10"/>
-      <c r="M62" s="5"/>
+      <c r="M62" s="10"/>
+      <c r="N62" s="10"/>
+      <c r="O62" s="5"/>
+      <c r="P62" s="5"/>
+      <c r="Q62" s="10"/>
+      <c r="R62" s="10"/>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="5"/>
@@ -2066,7 +2623,12 @@
       <c r="J63" s="10"/>
       <c r="K63" s="10"/>
       <c r="L63" s="10"/>
-      <c r="M63" s="5"/>
+      <c r="M63" s="10"/>
+      <c r="N63" s="10"/>
+      <c r="O63" s="5"/>
+      <c r="P63" s="5"/>
+      <c r="Q63" s="10"/>
+      <c r="R63" s="10"/>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="5"/>
@@ -2081,7 +2643,12 @@
       <c r="J64" s="10"/>
       <c r="K64" s="10"/>
       <c r="L64" s="10"/>
-      <c r="M64" s="5"/>
+      <c r="M64" s="10"/>
+      <c r="N64" s="10"/>
+      <c r="O64" s="5"/>
+      <c r="P64" s="5"/>
+      <c r="Q64" s="10"/>
+      <c r="R64" s="10"/>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="5"/>
@@ -2096,7 +2663,12 @@
       <c r="J65" s="10"/>
       <c r="K65" s="10"/>
       <c r="L65" s="10"/>
-      <c r="M65" s="5"/>
+      <c r="M65" s="10"/>
+      <c r="N65" s="10"/>
+      <c r="O65" s="5"/>
+      <c r="P65" s="5"/>
+      <c r="Q65" s="10"/>
+      <c r="R65" s="10"/>
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="5"/>
@@ -2111,7 +2683,12 @@
       <c r="J66" s="10"/>
       <c r="K66" s="10"/>
       <c r="L66" s="10"/>
-      <c r="M66" s="5"/>
+      <c r="M66" s="10"/>
+      <c r="N66" s="10"/>
+      <c r="O66" s="5"/>
+      <c r="P66" s="5"/>
+      <c r="Q66" s="10"/>
+      <c r="R66" s="10"/>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="5"/>
@@ -2126,7 +2703,12 @@
       <c r="J67" s="10"/>
       <c r="K67" s="10"/>
       <c r="L67" s="10"/>
-      <c r="M67" s="5"/>
+      <c r="M67" s="10"/>
+      <c r="N67" s="10"/>
+      <c r="O67" s="5"/>
+      <c r="P67" s="5"/>
+      <c r="Q67" s="10"/>
+      <c r="R67" s="10"/>
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="5"/>
@@ -2141,7 +2723,12 @@
       <c r="J68" s="10"/>
       <c r="K68" s="10"/>
       <c r="L68" s="10"/>
-      <c r="M68" s="5"/>
+      <c r="M68" s="10"/>
+      <c r="N68" s="10"/>
+      <c r="O68" s="5"/>
+      <c r="P68" s="5"/>
+      <c r="Q68" s="10"/>
+      <c r="R68" s="10"/>
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="5"/>
@@ -2156,7 +2743,12 @@
       <c r="J69" s="10"/>
       <c r="K69" s="10"/>
       <c r="L69" s="10"/>
-      <c r="M69" s="5"/>
+      <c r="M69" s="10"/>
+      <c r="N69" s="10"/>
+      <c r="O69" s="5"/>
+      <c r="P69" s="5"/>
+      <c r="Q69" s="10"/>
+      <c r="R69" s="10"/>
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="5"/>
@@ -2171,7 +2763,12 @@
       <c r="J70" s="10"/>
       <c r="K70" s="10"/>
       <c r="L70" s="10"/>
-      <c r="M70" s="5"/>
+      <c r="M70" s="10"/>
+      <c r="N70" s="10"/>
+      <c r="O70" s="5"/>
+      <c r="P70" s="5"/>
+      <c r="Q70" s="10"/>
+      <c r="R70" s="10"/>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="5"/>
@@ -2186,7 +2783,12 @@
       <c r="J71" s="10"/>
       <c r="K71" s="10"/>
       <c r="L71" s="10"/>
-      <c r="M71" s="5"/>
+      <c r="M71" s="10"/>
+      <c r="N71" s="10"/>
+      <c r="O71" s="5"/>
+      <c r="P71" s="5"/>
+      <c r="Q71" s="10"/>
+      <c r="R71" s="10"/>
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="5"/>
@@ -2201,7 +2803,12 @@
       <c r="J72" s="10"/>
       <c r="K72" s="10"/>
       <c r="L72" s="10"/>
-      <c r="M72" s="5"/>
+      <c r="M72" s="10"/>
+      <c r="N72" s="10"/>
+      <c r="O72" s="5"/>
+      <c r="P72" s="5"/>
+      <c r="Q72" s="10"/>
+      <c r="R72" s="10"/>
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="5"/>
@@ -2216,7 +2823,12 @@
       <c r="J73" s="10"/>
       <c r="K73" s="10"/>
       <c r="L73" s="10"/>
-      <c r="M73" s="5"/>
+      <c r="M73" s="10"/>
+      <c r="N73" s="10"/>
+      <c r="O73" s="5"/>
+      <c r="P73" s="5"/>
+      <c r="Q73" s="10"/>
+      <c r="R73" s="10"/>
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="5"/>
@@ -2231,7 +2843,12 @@
       <c r="J74" s="10"/>
       <c r="K74" s="10"/>
       <c r="L74" s="10"/>
-      <c r="M74" s="5"/>
+      <c r="M74" s="10"/>
+      <c r="N74" s="10"/>
+      <c r="O74" s="5"/>
+      <c r="P74" s="5"/>
+      <c r="Q74" s="10"/>
+      <c r="R74" s="10"/>
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="5"/>
@@ -2246,7 +2863,12 @@
       <c r="J75" s="10"/>
       <c r="K75" s="10"/>
       <c r="L75" s="10"/>
-      <c r="M75" s="5"/>
+      <c r="M75" s="10"/>
+      <c r="N75" s="10"/>
+      <c r="O75" s="5"/>
+      <c r="P75" s="5"/>
+      <c r="Q75" s="10"/>
+      <c r="R75" s="10"/>
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="5"/>
@@ -2261,7 +2883,12 @@
       <c r="J76" s="10"/>
       <c r="K76" s="10"/>
       <c r="L76" s="10"/>
-      <c r="M76" s="5"/>
+      <c r="M76" s="10"/>
+      <c r="N76" s="10"/>
+      <c r="O76" s="5"/>
+      <c r="P76" s="5"/>
+      <c r="Q76" s="10"/>
+      <c r="R76" s="10"/>
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="5"/>
@@ -2276,7 +2903,12 @@
       <c r="J77" s="10"/>
       <c r="K77" s="10"/>
       <c r="L77" s="10"/>
-      <c r="M77" s="5"/>
+      <c r="M77" s="10"/>
+      <c r="N77" s="10"/>
+      <c r="O77" s="5"/>
+      <c r="P77" s="5"/>
+      <c r="Q77" s="10"/>
+      <c r="R77" s="10"/>
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="5"/>
@@ -2291,7 +2923,12 @@
       <c r="J78" s="10"/>
       <c r="K78" s="10"/>
       <c r="L78" s="10"/>
-      <c r="M78" s="5"/>
+      <c r="M78" s="10"/>
+      <c r="N78" s="10"/>
+      <c r="O78" s="5"/>
+      <c r="P78" s="5"/>
+      <c r="Q78" s="10"/>
+      <c r="R78" s="10"/>
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="5"/>
@@ -2306,7 +2943,12 @@
       <c r="J79" s="10"/>
       <c r="K79" s="10"/>
       <c r="L79" s="10"/>
-      <c r="M79" s="5"/>
+      <c r="M79" s="10"/>
+      <c r="N79" s="10"/>
+      <c r="O79" s="5"/>
+      <c r="P79" s="5"/>
+      <c r="Q79" s="10"/>
+      <c r="R79" s="10"/>
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="5"/>
@@ -2321,7 +2963,12 @@
       <c r="J80" s="10"/>
       <c r="K80" s="10"/>
       <c r="L80" s="10"/>
-      <c r="M80" s="5"/>
+      <c r="M80" s="10"/>
+      <c r="N80" s="10"/>
+      <c r="O80" s="5"/>
+      <c r="P80" s="5"/>
+      <c r="Q80" s="10"/>
+      <c r="R80" s="10"/>
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="5"/>
@@ -2336,7 +2983,12 @@
       <c r="J81" s="10"/>
       <c r="K81" s="10"/>
       <c r="L81" s="10"/>
-      <c r="M81" s="5"/>
+      <c r="M81" s="10"/>
+      <c r="N81" s="10"/>
+      <c r="O81" s="5"/>
+      <c r="P81" s="5"/>
+      <c r="Q81" s="10"/>
+      <c r="R81" s="10"/>
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="5"/>
@@ -2351,7 +3003,12 @@
       <c r="J82" s="10"/>
       <c r="K82" s="10"/>
       <c r="L82" s="10"/>
-      <c r="M82" s="5"/>
+      <c r="M82" s="10"/>
+      <c r="N82" s="10"/>
+      <c r="O82" s="5"/>
+      <c r="P82" s="5"/>
+      <c r="Q82" s="10"/>
+      <c r="R82" s="10"/>
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="5"/>
@@ -2366,7 +3023,12 @@
       <c r="J83" s="10"/>
       <c r="K83" s="10"/>
       <c r="L83" s="10"/>
-      <c r="M83" s="5"/>
+      <c r="M83" s="10"/>
+      <c r="N83" s="10"/>
+      <c r="O83" s="5"/>
+      <c r="P83" s="5"/>
+      <c r="Q83" s="10"/>
+      <c r="R83" s="10"/>
     </row>
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="5"/>
@@ -2381,10 +3043,15 @@
       <c r="J84" s="10"/>
       <c r="K84" s="10"/>
       <c r="L84" s="10"/>
-      <c r="M84" s="5"/>
+      <c r="M84" s="10"/>
+      <c r="N84" s="10"/>
+      <c r="O84" s="5"/>
+      <c r="P84" s="5"/>
+      <c r="Q84" s="10"/>
+      <c r="R84" s="10"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A5:M84">
+  <conditionalFormatting sqref="A5:R84">
     <cfRule type="expression" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
       <formula>$A5&lt;&gt;""</formula>
     </cfRule>
@@ -2394,13 +3061,13 @@
       <formula>$C5="P. Principal"</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="8">
+  <dataValidations count="12">
     <dataValidation allowBlank="true" error="Elige un día del desplegable (Lunes … Domingo)." errorStyle="stop" errorTitle="Día" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="A5:A84" type="list">
       <formula1>"Lunes,Martes,Miércoles,Jueves,Viernes,Sábado,Domingo"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Elige un bloque del desplegable." errorStyle="stop" errorTitle="Bloque" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C5:C84" type="list">
-      <formula1>"Activación,P. Principal,Accesorios,Vuelta a la calma"</formula1>
+      <formula1>"Activación,P. Principal,Aeróbico,Accesorios,Vuelta a la calma"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Solo un número de 1 a 20." errorStyle="stop" errorTitle="Series" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="E5:E84" type="whole">
@@ -2427,6 +3094,22 @@
       <formula1>"Sí"</formula1>
       <formula2>0</formula2>
     </dataValidation>
+    <dataValidation allowBlank="true" error="Minutos del aeróbico (0,5 = 30 s)." errorStyle="stop" errorTitle="Minutos" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="M5:M84" type="decimal">
+      <formula1>0</formula1>
+      <formula2>600</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Elige una zona del desplegable." errorStyle="stop" errorTitle="Zona" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="N5:N84" type="list">
+      <formula1>"Z1,Z2,Z3,Z4,Z5"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Un número de 0 a 10." errorStyle="stop" errorTitle="RPE pre" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="Q5:Q84" type="decimal">
+      <formula1>0</formula1>
+      <formula2>10</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Un número de 0 a 10." errorStyle="stop" errorTitle="RPE post" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="R5:R84" type="decimal">
+      <formula1>0</formula1>
+      <formula2>10</formula2>
+    </dataValidation>
   </dataValidations>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -2444,7 +3127,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:M84"/>
+  <dimension ref="A1:R84"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="15"/>
@@ -2456,12 +3139,16 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="8" style="0" width="9"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="7"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="11" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="0" width="7"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="0" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="0" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="17" style="0" width="8"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="6" t="s">
-        <v>42</v>
+        <v>54</v>
       </c>
       <c r="B1" s="11" t="n">
         <f aca="false">'Semana 1'!B1+7</f>
@@ -2474,49 +3161,64 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="8" t="s">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="B2" s="9"/>
     </row>
     <row r="4" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="I4" s="4" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="J4" s="4" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="K4" s="4" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="L4" s="4" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="M4" s="4" t="s">
-        <v>26</v>
+        <v>28</v>
+      </c>
+      <c r="N4" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="O4" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="P4" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q4" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="R4" s="4" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2532,7 +3234,12 @@
       <c r="J5" s="10"/>
       <c r="K5" s="10"/>
       <c r="L5" s="10"/>
-      <c r="M5" s="5"/>
+      <c r="M5" s="10"/>
+      <c r="N5" s="10"/>
+      <c r="O5" s="5"/>
+      <c r="P5" s="5"/>
+      <c r="Q5" s="10"/>
+      <c r="R5" s="10"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="5"/>
@@ -2547,7 +3254,12 @@
       <c r="J6" s="10"/>
       <c r="K6" s="10"/>
       <c r="L6" s="10"/>
-      <c r="M6" s="5"/>
+      <c r="M6" s="10"/>
+      <c r="N6" s="10"/>
+      <c r="O6" s="5"/>
+      <c r="P6" s="5"/>
+      <c r="Q6" s="10"/>
+      <c r="R6" s="10"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="5"/>
@@ -2562,7 +3274,12 @@
       <c r="J7" s="10"/>
       <c r="K7" s="10"/>
       <c r="L7" s="10"/>
-      <c r="M7" s="5"/>
+      <c r="M7" s="10"/>
+      <c r="N7" s="10"/>
+      <c r="O7" s="5"/>
+      <c r="P7" s="5"/>
+      <c r="Q7" s="10"/>
+      <c r="R7" s="10"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="5"/>
@@ -2577,7 +3294,12 @@
       <c r="J8" s="10"/>
       <c r="K8" s="10"/>
       <c r="L8" s="10"/>
-      <c r="M8" s="5"/>
+      <c r="M8" s="10"/>
+      <c r="N8" s="10"/>
+      <c r="O8" s="5"/>
+      <c r="P8" s="5"/>
+      <c r="Q8" s="10"/>
+      <c r="R8" s="10"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="5"/>
@@ -2592,7 +3314,12 @@
       <c r="J9" s="10"/>
       <c r="K9" s="10"/>
       <c r="L9" s="10"/>
-      <c r="M9" s="5"/>
+      <c r="M9" s="10"/>
+      <c r="N9" s="10"/>
+      <c r="O9" s="5"/>
+      <c r="P9" s="5"/>
+      <c r="Q9" s="10"/>
+      <c r="R9" s="10"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="5"/>
@@ -2607,7 +3334,12 @@
       <c r="J10" s="10"/>
       <c r="K10" s="10"/>
       <c r="L10" s="10"/>
-      <c r="M10" s="5"/>
+      <c r="M10" s="10"/>
+      <c r="N10" s="10"/>
+      <c r="O10" s="5"/>
+      <c r="P10" s="5"/>
+      <c r="Q10" s="10"/>
+      <c r="R10" s="10"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="5"/>
@@ -2622,7 +3354,12 @@
       <c r="J11" s="10"/>
       <c r="K11" s="10"/>
       <c r="L11" s="10"/>
-      <c r="M11" s="5"/>
+      <c r="M11" s="10"/>
+      <c r="N11" s="10"/>
+      <c r="O11" s="5"/>
+      <c r="P11" s="5"/>
+      <c r="Q11" s="10"/>
+      <c r="R11" s="10"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="5"/>
@@ -2637,7 +3374,12 @@
       <c r="J12" s="10"/>
       <c r="K12" s="10"/>
       <c r="L12" s="10"/>
-      <c r="M12" s="5"/>
+      <c r="M12" s="10"/>
+      <c r="N12" s="10"/>
+      <c r="O12" s="5"/>
+      <c r="P12" s="5"/>
+      <c r="Q12" s="10"/>
+      <c r="R12" s="10"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="5"/>
@@ -2652,7 +3394,12 @@
       <c r="J13" s="10"/>
       <c r="K13" s="10"/>
       <c r="L13" s="10"/>
-      <c r="M13" s="5"/>
+      <c r="M13" s="10"/>
+      <c r="N13" s="10"/>
+      <c r="O13" s="5"/>
+      <c r="P13" s="5"/>
+      <c r="Q13" s="10"/>
+      <c r="R13" s="10"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="5"/>
@@ -2667,7 +3414,12 @@
       <c r="J14" s="10"/>
       <c r="K14" s="10"/>
       <c r="L14" s="10"/>
-      <c r="M14" s="5"/>
+      <c r="M14" s="10"/>
+      <c r="N14" s="10"/>
+      <c r="O14" s="5"/>
+      <c r="P14" s="5"/>
+      <c r="Q14" s="10"/>
+      <c r="R14" s="10"/>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="5"/>
@@ -2682,7 +3434,12 @@
       <c r="J15" s="10"/>
       <c r="K15" s="10"/>
       <c r="L15" s="10"/>
-      <c r="M15" s="5"/>
+      <c r="M15" s="10"/>
+      <c r="N15" s="10"/>
+      <c r="O15" s="5"/>
+      <c r="P15" s="5"/>
+      <c r="Q15" s="10"/>
+      <c r="R15" s="10"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="5"/>
@@ -2697,7 +3454,12 @@
       <c r="J16" s="10"/>
       <c r="K16" s="10"/>
       <c r="L16" s="10"/>
-      <c r="M16" s="5"/>
+      <c r="M16" s="10"/>
+      <c r="N16" s="10"/>
+      <c r="O16" s="5"/>
+      <c r="P16" s="5"/>
+      <c r="Q16" s="10"/>
+      <c r="R16" s="10"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="5"/>
@@ -2712,7 +3474,12 @@
       <c r="J17" s="10"/>
       <c r="K17" s="10"/>
       <c r="L17" s="10"/>
-      <c r="M17" s="5"/>
+      <c r="M17" s="10"/>
+      <c r="N17" s="10"/>
+      <c r="O17" s="5"/>
+      <c r="P17" s="5"/>
+      <c r="Q17" s="10"/>
+      <c r="R17" s="10"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="5"/>
@@ -2727,7 +3494,12 @@
       <c r="J18" s="10"/>
       <c r="K18" s="10"/>
       <c r="L18" s="10"/>
-      <c r="M18" s="5"/>
+      <c r="M18" s="10"/>
+      <c r="N18" s="10"/>
+      <c r="O18" s="5"/>
+      <c r="P18" s="5"/>
+      <c r="Q18" s="10"/>
+      <c r="R18" s="10"/>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="5"/>
@@ -2742,7 +3514,12 @@
       <c r="J19" s="10"/>
       <c r="K19" s="10"/>
       <c r="L19" s="10"/>
-      <c r="M19" s="5"/>
+      <c r="M19" s="10"/>
+      <c r="N19" s="10"/>
+      <c r="O19" s="5"/>
+      <c r="P19" s="5"/>
+      <c r="Q19" s="10"/>
+      <c r="R19" s="10"/>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="5"/>
@@ -2757,7 +3534,12 @@
       <c r="J20" s="10"/>
       <c r="K20" s="10"/>
       <c r="L20" s="10"/>
-      <c r="M20" s="5"/>
+      <c r="M20" s="10"/>
+      <c r="N20" s="10"/>
+      <c r="O20" s="5"/>
+      <c r="P20" s="5"/>
+      <c r="Q20" s="10"/>
+      <c r="R20" s="10"/>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="5"/>
@@ -2772,7 +3554,12 @@
       <c r="J21" s="10"/>
       <c r="K21" s="10"/>
       <c r="L21" s="10"/>
-      <c r="M21" s="5"/>
+      <c r="M21" s="10"/>
+      <c r="N21" s="10"/>
+      <c r="O21" s="5"/>
+      <c r="P21" s="5"/>
+      <c r="Q21" s="10"/>
+      <c r="R21" s="10"/>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="5"/>
@@ -2787,7 +3574,12 @@
       <c r="J22" s="10"/>
       <c r="K22" s="10"/>
       <c r="L22" s="10"/>
-      <c r="M22" s="5"/>
+      <c r="M22" s="10"/>
+      <c r="N22" s="10"/>
+      <c r="O22" s="5"/>
+      <c r="P22" s="5"/>
+      <c r="Q22" s="10"/>
+      <c r="R22" s="10"/>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="5"/>
@@ -2802,7 +3594,12 @@
       <c r="J23" s="10"/>
       <c r="K23" s="10"/>
       <c r="L23" s="10"/>
-      <c r="M23" s="5"/>
+      <c r="M23" s="10"/>
+      <c r="N23" s="10"/>
+      <c r="O23" s="5"/>
+      <c r="P23" s="5"/>
+      <c r="Q23" s="10"/>
+      <c r="R23" s="10"/>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="5"/>
@@ -2817,7 +3614,12 @@
       <c r="J24" s="10"/>
       <c r="K24" s="10"/>
       <c r="L24" s="10"/>
-      <c r="M24" s="5"/>
+      <c r="M24" s="10"/>
+      <c r="N24" s="10"/>
+      <c r="O24" s="5"/>
+      <c r="P24" s="5"/>
+      <c r="Q24" s="10"/>
+      <c r="R24" s="10"/>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="5"/>
@@ -2832,7 +3634,12 @@
       <c r="J25" s="10"/>
       <c r="K25" s="10"/>
       <c r="L25" s="10"/>
-      <c r="M25" s="5"/>
+      <c r="M25" s="10"/>
+      <c r="N25" s="10"/>
+      <c r="O25" s="5"/>
+      <c r="P25" s="5"/>
+      <c r="Q25" s="10"/>
+      <c r="R25" s="10"/>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="5"/>
@@ -2847,7 +3654,12 @@
       <c r="J26" s="10"/>
       <c r="K26" s="10"/>
       <c r="L26" s="10"/>
-      <c r="M26" s="5"/>
+      <c r="M26" s="10"/>
+      <c r="N26" s="10"/>
+      <c r="O26" s="5"/>
+      <c r="P26" s="5"/>
+      <c r="Q26" s="10"/>
+      <c r="R26" s="10"/>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="5"/>
@@ -2862,7 +3674,12 @@
       <c r="J27" s="10"/>
       <c r="K27" s="10"/>
       <c r="L27" s="10"/>
-      <c r="M27" s="5"/>
+      <c r="M27" s="10"/>
+      <c r="N27" s="10"/>
+      <c r="O27" s="5"/>
+      <c r="P27" s="5"/>
+      <c r="Q27" s="10"/>
+      <c r="R27" s="10"/>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="5"/>
@@ -2877,7 +3694,12 @@
       <c r="J28" s="10"/>
       <c r="K28" s="10"/>
       <c r="L28" s="10"/>
-      <c r="M28" s="5"/>
+      <c r="M28" s="10"/>
+      <c r="N28" s="10"/>
+      <c r="O28" s="5"/>
+      <c r="P28" s="5"/>
+      <c r="Q28" s="10"/>
+      <c r="R28" s="10"/>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="5"/>
@@ -2892,7 +3714,12 @@
       <c r="J29" s="10"/>
       <c r="K29" s="10"/>
       <c r="L29" s="10"/>
-      <c r="M29" s="5"/>
+      <c r="M29" s="10"/>
+      <c r="N29" s="10"/>
+      <c r="O29" s="5"/>
+      <c r="P29" s="5"/>
+      <c r="Q29" s="10"/>
+      <c r="R29" s="10"/>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="5"/>
@@ -2907,7 +3734,12 @@
       <c r="J30" s="10"/>
       <c r="K30" s="10"/>
       <c r="L30" s="10"/>
-      <c r="M30" s="5"/>
+      <c r="M30" s="10"/>
+      <c r="N30" s="10"/>
+      <c r="O30" s="5"/>
+      <c r="P30" s="5"/>
+      <c r="Q30" s="10"/>
+      <c r="R30" s="10"/>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="5"/>
@@ -2922,7 +3754,12 @@
       <c r="J31" s="10"/>
       <c r="K31" s="10"/>
       <c r="L31" s="10"/>
-      <c r="M31" s="5"/>
+      <c r="M31" s="10"/>
+      <c r="N31" s="10"/>
+      <c r="O31" s="5"/>
+      <c r="P31" s="5"/>
+      <c r="Q31" s="10"/>
+      <c r="R31" s="10"/>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="5"/>
@@ -2937,7 +3774,12 @@
       <c r="J32" s="10"/>
       <c r="K32" s="10"/>
       <c r="L32" s="10"/>
-      <c r="M32" s="5"/>
+      <c r="M32" s="10"/>
+      <c r="N32" s="10"/>
+      <c r="O32" s="5"/>
+      <c r="P32" s="5"/>
+      <c r="Q32" s="10"/>
+      <c r="R32" s="10"/>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="5"/>
@@ -2952,7 +3794,12 @@
       <c r="J33" s="10"/>
       <c r="K33" s="10"/>
       <c r="L33" s="10"/>
-      <c r="M33" s="5"/>
+      <c r="M33" s="10"/>
+      <c r="N33" s="10"/>
+      <c r="O33" s="5"/>
+      <c r="P33" s="5"/>
+      <c r="Q33" s="10"/>
+      <c r="R33" s="10"/>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="5"/>
@@ -2967,7 +3814,12 @@
       <c r="J34" s="10"/>
       <c r="K34" s="10"/>
       <c r="L34" s="10"/>
-      <c r="M34" s="5"/>
+      <c r="M34" s="10"/>
+      <c r="N34" s="10"/>
+      <c r="O34" s="5"/>
+      <c r="P34" s="5"/>
+      <c r="Q34" s="10"/>
+      <c r="R34" s="10"/>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="5"/>
@@ -2982,7 +3834,12 @@
       <c r="J35" s="10"/>
       <c r="K35" s="10"/>
       <c r="L35" s="10"/>
-      <c r="M35" s="5"/>
+      <c r="M35" s="10"/>
+      <c r="N35" s="10"/>
+      <c r="O35" s="5"/>
+      <c r="P35" s="5"/>
+      <c r="Q35" s="10"/>
+      <c r="R35" s="10"/>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="5"/>
@@ -2997,7 +3854,12 @@
       <c r="J36" s="10"/>
       <c r="K36" s="10"/>
       <c r="L36" s="10"/>
-      <c r="M36" s="5"/>
+      <c r="M36" s="10"/>
+      <c r="N36" s="10"/>
+      <c r="O36" s="5"/>
+      <c r="P36" s="5"/>
+      <c r="Q36" s="10"/>
+      <c r="R36" s="10"/>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="5"/>
@@ -3012,7 +3874,12 @@
       <c r="J37" s="10"/>
       <c r="K37" s="10"/>
       <c r="L37" s="10"/>
-      <c r="M37" s="5"/>
+      <c r="M37" s="10"/>
+      <c r="N37" s="10"/>
+      <c r="O37" s="5"/>
+      <c r="P37" s="5"/>
+      <c r="Q37" s="10"/>
+      <c r="R37" s="10"/>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="5"/>
@@ -3027,7 +3894,12 @@
       <c r="J38" s="10"/>
       <c r="K38" s="10"/>
       <c r="L38" s="10"/>
-      <c r="M38" s="5"/>
+      <c r="M38" s="10"/>
+      <c r="N38" s="10"/>
+      <c r="O38" s="5"/>
+      <c r="P38" s="5"/>
+      <c r="Q38" s="10"/>
+      <c r="R38" s="10"/>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="5"/>
@@ -3042,7 +3914,12 @@
       <c r="J39" s="10"/>
       <c r="K39" s="10"/>
       <c r="L39" s="10"/>
-      <c r="M39" s="5"/>
+      <c r="M39" s="10"/>
+      <c r="N39" s="10"/>
+      <c r="O39" s="5"/>
+      <c r="P39" s="5"/>
+      <c r="Q39" s="10"/>
+      <c r="R39" s="10"/>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="5"/>
@@ -3057,7 +3934,12 @@
       <c r="J40" s="10"/>
       <c r="K40" s="10"/>
       <c r="L40" s="10"/>
-      <c r="M40" s="5"/>
+      <c r="M40" s="10"/>
+      <c r="N40" s="10"/>
+      <c r="O40" s="5"/>
+      <c r="P40" s="5"/>
+      <c r="Q40" s="10"/>
+      <c r="R40" s="10"/>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="5"/>
@@ -3072,7 +3954,12 @@
       <c r="J41" s="10"/>
       <c r="K41" s="10"/>
       <c r="L41" s="10"/>
-      <c r="M41" s="5"/>
+      <c r="M41" s="10"/>
+      <c r="N41" s="10"/>
+      <c r="O41" s="5"/>
+      <c r="P41" s="5"/>
+      <c r="Q41" s="10"/>
+      <c r="R41" s="10"/>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="5"/>
@@ -3087,7 +3974,12 @@
       <c r="J42" s="10"/>
       <c r="K42" s="10"/>
       <c r="L42" s="10"/>
-      <c r="M42" s="5"/>
+      <c r="M42" s="10"/>
+      <c r="N42" s="10"/>
+      <c r="O42" s="5"/>
+      <c r="P42" s="5"/>
+      <c r="Q42" s="10"/>
+      <c r="R42" s="10"/>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="5"/>
@@ -3102,7 +3994,12 @@
       <c r="J43" s="10"/>
       <c r="K43" s="10"/>
       <c r="L43" s="10"/>
-      <c r="M43" s="5"/>
+      <c r="M43" s="10"/>
+      <c r="N43" s="10"/>
+      <c r="O43" s="5"/>
+      <c r="P43" s="5"/>
+      <c r="Q43" s="10"/>
+      <c r="R43" s="10"/>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="5"/>
@@ -3117,7 +4014,12 @@
       <c r="J44" s="10"/>
       <c r="K44" s="10"/>
       <c r="L44" s="10"/>
-      <c r="M44" s="5"/>
+      <c r="M44" s="10"/>
+      <c r="N44" s="10"/>
+      <c r="O44" s="5"/>
+      <c r="P44" s="5"/>
+      <c r="Q44" s="10"/>
+      <c r="R44" s="10"/>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="5"/>
@@ -3132,7 +4034,12 @@
       <c r="J45" s="10"/>
       <c r="K45" s="10"/>
       <c r="L45" s="10"/>
-      <c r="M45" s="5"/>
+      <c r="M45" s="10"/>
+      <c r="N45" s="10"/>
+      <c r="O45" s="5"/>
+      <c r="P45" s="5"/>
+      <c r="Q45" s="10"/>
+      <c r="R45" s="10"/>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="5"/>
@@ -3147,7 +4054,12 @@
       <c r="J46" s="10"/>
       <c r="K46" s="10"/>
       <c r="L46" s="10"/>
-      <c r="M46" s="5"/>
+      <c r="M46" s="10"/>
+      <c r="N46" s="10"/>
+      <c r="O46" s="5"/>
+      <c r="P46" s="5"/>
+      <c r="Q46" s="10"/>
+      <c r="R46" s="10"/>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="5"/>
@@ -3162,7 +4074,12 @@
       <c r="J47" s="10"/>
       <c r="K47" s="10"/>
       <c r="L47" s="10"/>
-      <c r="M47" s="5"/>
+      <c r="M47" s="10"/>
+      <c r="N47" s="10"/>
+      <c r="O47" s="5"/>
+      <c r="P47" s="5"/>
+      <c r="Q47" s="10"/>
+      <c r="R47" s="10"/>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="5"/>
@@ -3177,7 +4094,12 @@
       <c r="J48" s="10"/>
       <c r="K48" s="10"/>
       <c r="L48" s="10"/>
-      <c r="M48" s="5"/>
+      <c r="M48" s="10"/>
+      <c r="N48" s="10"/>
+      <c r="O48" s="5"/>
+      <c r="P48" s="5"/>
+      <c r="Q48" s="10"/>
+      <c r="R48" s="10"/>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="5"/>
@@ -3192,7 +4114,12 @@
       <c r="J49" s="10"/>
       <c r="K49" s="10"/>
       <c r="L49" s="10"/>
-      <c r="M49" s="5"/>
+      <c r="M49" s="10"/>
+      <c r="N49" s="10"/>
+      <c r="O49" s="5"/>
+      <c r="P49" s="5"/>
+      <c r="Q49" s="10"/>
+      <c r="R49" s="10"/>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="5"/>
@@ -3207,7 +4134,12 @@
       <c r="J50" s="10"/>
       <c r="K50" s="10"/>
       <c r="L50" s="10"/>
-      <c r="M50" s="5"/>
+      <c r="M50" s="10"/>
+      <c r="N50" s="10"/>
+      <c r="O50" s="5"/>
+      <c r="P50" s="5"/>
+      <c r="Q50" s="10"/>
+      <c r="R50" s="10"/>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="5"/>
@@ -3222,7 +4154,12 @@
       <c r="J51" s="10"/>
       <c r="K51" s="10"/>
       <c r="L51" s="10"/>
-      <c r="M51" s="5"/>
+      <c r="M51" s="10"/>
+      <c r="N51" s="10"/>
+      <c r="O51" s="5"/>
+      <c r="P51" s="5"/>
+      <c r="Q51" s="10"/>
+      <c r="R51" s="10"/>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="5"/>
@@ -3237,7 +4174,12 @@
       <c r="J52" s="10"/>
       <c r="K52" s="10"/>
       <c r="L52" s="10"/>
-      <c r="M52" s="5"/>
+      <c r="M52" s="10"/>
+      <c r="N52" s="10"/>
+      <c r="O52" s="5"/>
+      <c r="P52" s="5"/>
+      <c r="Q52" s="10"/>
+      <c r="R52" s="10"/>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="5"/>
@@ -3252,7 +4194,12 @@
       <c r="J53" s="10"/>
       <c r="K53" s="10"/>
       <c r="L53" s="10"/>
-      <c r="M53" s="5"/>
+      <c r="M53" s="10"/>
+      <c r="N53" s="10"/>
+      <c r="O53" s="5"/>
+      <c r="P53" s="5"/>
+      <c r="Q53" s="10"/>
+      <c r="R53" s="10"/>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="5"/>
@@ -3267,7 +4214,12 @@
       <c r="J54" s="10"/>
       <c r="K54" s="10"/>
       <c r="L54" s="10"/>
-      <c r="M54" s="5"/>
+      <c r="M54" s="10"/>
+      <c r="N54" s="10"/>
+      <c r="O54" s="5"/>
+      <c r="P54" s="5"/>
+      <c r="Q54" s="10"/>
+      <c r="R54" s="10"/>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="5"/>
@@ -3282,7 +4234,12 @@
       <c r="J55" s="10"/>
       <c r="K55" s="10"/>
       <c r="L55" s="10"/>
-      <c r="M55" s="5"/>
+      <c r="M55" s="10"/>
+      <c r="N55" s="10"/>
+      <c r="O55" s="5"/>
+      <c r="P55" s="5"/>
+      <c r="Q55" s="10"/>
+      <c r="R55" s="10"/>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="5"/>
@@ -3297,7 +4254,12 @@
       <c r="J56" s="10"/>
       <c r="K56" s="10"/>
       <c r="L56" s="10"/>
-      <c r="M56" s="5"/>
+      <c r="M56" s="10"/>
+      <c r="N56" s="10"/>
+      <c r="O56" s="5"/>
+      <c r="P56" s="5"/>
+      <c r="Q56" s="10"/>
+      <c r="R56" s="10"/>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="5"/>
@@ -3312,7 +4274,12 @@
       <c r="J57" s="10"/>
       <c r="K57" s="10"/>
       <c r="L57" s="10"/>
-      <c r="M57" s="5"/>
+      <c r="M57" s="10"/>
+      <c r="N57" s="10"/>
+      <c r="O57" s="5"/>
+      <c r="P57" s="5"/>
+      <c r="Q57" s="10"/>
+      <c r="R57" s="10"/>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="5"/>
@@ -3327,7 +4294,12 @@
       <c r="J58" s="10"/>
       <c r="K58" s="10"/>
       <c r="L58" s="10"/>
-      <c r="M58" s="5"/>
+      <c r="M58" s="10"/>
+      <c r="N58" s="10"/>
+      <c r="O58" s="5"/>
+      <c r="P58" s="5"/>
+      <c r="Q58" s="10"/>
+      <c r="R58" s="10"/>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="5"/>
@@ -3342,7 +4314,12 @@
       <c r="J59" s="10"/>
       <c r="K59" s="10"/>
       <c r="L59" s="10"/>
-      <c r="M59" s="5"/>
+      <c r="M59" s="10"/>
+      <c r="N59" s="10"/>
+      <c r="O59" s="5"/>
+      <c r="P59" s="5"/>
+      <c r="Q59" s="10"/>
+      <c r="R59" s="10"/>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="5"/>
@@ -3357,7 +4334,12 @@
       <c r="J60" s="10"/>
       <c r="K60" s="10"/>
       <c r="L60" s="10"/>
-      <c r="M60" s="5"/>
+      <c r="M60" s="10"/>
+      <c r="N60" s="10"/>
+      <c r="O60" s="5"/>
+      <c r="P60" s="5"/>
+      <c r="Q60" s="10"/>
+      <c r="R60" s="10"/>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="5"/>
@@ -3372,7 +4354,12 @@
       <c r="J61" s="10"/>
       <c r="K61" s="10"/>
       <c r="L61" s="10"/>
-      <c r="M61" s="5"/>
+      <c r="M61" s="10"/>
+      <c r="N61" s="10"/>
+      <c r="O61" s="5"/>
+      <c r="P61" s="5"/>
+      <c r="Q61" s="10"/>
+      <c r="R61" s="10"/>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="5"/>
@@ -3387,7 +4374,12 @@
       <c r="J62" s="10"/>
       <c r="K62" s="10"/>
       <c r="L62" s="10"/>
-      <c r="M62" s="5"/>
+      <c r="M62" s="10"/>
+      <c r="N62" s="10"/>
+      <c r="O62" s="5"/>
+      <c r="P62" s="5"/>
+      <c r="Q62" s="10"/>
+      <c r="R62" s="10"/>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="5"/>
@@ -3402,7 +4394,12 @@
       <c r="J63" s="10"/>
       <c r="K63" s="10"/>
       <c r="L63" s="10"/>
-      <c r="M63" s="5"/>
+      <c r="M63" s="10"/>
+      <c r="N63" s="10"/>
+      <c r="O63" s="5"/>
+      <c r="P63" s="5"/>
+      <c r="Q63" s="10"/>
+      <c r="R63" s="10"/>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="5"/>
@@ -3417,7 +4414,12 @@
       <c r="J64" s="10"/>
       <c r="K64" s="10"/>
       <c r="L64" s="10"/>
-      <c r="M64" s="5"/>
+      <c r="M64" s="10"/>
+      <c r="N64" s="10"/>
+      <c r="O64" s="5"/>
+      <c r="P64" s="5"/>
+      <c r="Q64" s="10"/>
+      <c r="R64" s="10"/>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="5"/>
@@ -3432,7 +4434,12 @@
       <c r="J65" s="10"/>
       <c r="K65" s="10"/>
       <c r="L65" s="10"/>
-      <c r="M65" s="5"/>
+      <c r="M65" s="10"/>
+      <c r="N65" s="10"/>
+      <c r="O65" s="5"/>
+      <c r="P65" s="5"/>
+      <c r="Q65" s="10"/>
+      <c r="R65" s="10"/>
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="5"/>
@@ -3447,7 +4454,12 @@
       <c r="J66" s="10"/>
       <c r="K66" s="10"/>
       <c r="L66" s="10"/>
-      <c r="M66" s="5"/>
+      <c r="M66" s="10"/>
+      <c r="N66" s="10"/>
+      <c r="O66" s="5"/>
+      <c r="P66" s="5"/>
+      <c r="Q66" s="10"/>
+      <c r="R66" s="10"/>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="5"/>
@@ -3462,7 +4474,12 @@
       <c r="J67" s="10"/>
       <c r="K67" s="10"/>
       <c r="L67" s="10"/>
-      <c r="M67" s="5"/>
+      <c r="M67" s="10"/>
+      <c r="N67" s="10"/>
+      <c r="O67" s="5"/>
+      <c r="P67" s="5"/>
+      <c r="Q67" s="10"/>
+      <c r="R67" s="10"/>
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="5"/>
@@ -3477,7 +4494,12 @@
       <c r="J68" s="10"/>
       <c r="K68" s="10"/>
       <c r="L68" s="10"/>
-      <c r="M68" s="5"/>
+      <c r="M68" s="10"/>
+      <c r="N68" s="10"/>
+      <c r="O68" s="5"/>
+      <c r="P68" s="5"/>
+      <c r="Q68" s="10"/>
+      <c r="R68" s="10"/>
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="5"/>
@@ -3492,7 +4514,12 @@
       <c r="J69" s="10"/>
       <c r="K69" s="10"/>
       <c r="L69" s="10"/>
-      <c r="M69" s="5"/>
+      <c r="M69" s="10"/>
+      <c r="N69" s="10"/>
+      <c r="O69" s="5"/>
+      <c r="P69" s="5"/>
+      <c r="Q69" s="10"/>
+      <c r="R69" s="10"/>
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="5"/>
@@ -3507,7 +4534,12 @@
       <c r="J70" s="10"/>
       <c r="K70" s="10"/>
       <c r="L70" s="10"/>
-      <c r="M70" s="5"/>
+      <c r="M70" s="10"/>
+      <c r="N70" s="10"/>
+      <c r="O70" s="5"/>
+      <c r="P70" s="5"/>
+      <c r="Q70" s="10"/>
+      <c r="R70" s="10"/>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="5"/>
@@ -3522,7 +4554,12 @@
       <c r="J71" s="10"/>
       <c r="K71" s="10"/>
       <c r="L71" s="10"/>
-      <c r="M71" s="5"/>
+      <c r="M71" s="10"/>
+      <c r="N71" s="10"/>
+      <c r="O71" s="5"/>
+      <c r="P71" s="5"/>
+      <c r="Q71" s="10"/>
+      <c r="R71" s="10"/>
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="5"/>
@@ -3537,7 +4574,12 @@
       <c r="J72" s="10"/>
       <c r="K72" s="10"/>
       <c r="L72" s="10"/>
-      <c r="M72" s="5"/>
+      <c r="M72" s="10"/>
+      <c r="N72" s="10"/>
+      <c r="O72" s="5"/>
+      <c r="P72" s="5"/>
+      <c r="Q72" s="10"/>
+      <c r="R72" s="10"/>
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="5"/>
@@ -3552,7 +4594,12 @@
       <c r="J73" s="10"/>
       <c r="K73" s="10"/>
       <c r="L73" s="10"/>
-      <c r="M73" s="5"/>
+      <c r="M73" s="10"/>
+      <c r="N73" s="10"/>
+      <c r="O73" s="5"/>
+      <c r="P73" s="5"/>
+      <c r="Q73" s="10"/>
+      <c r="R73" s="10"/>
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="5"/>
@@ -3567,7 +4614,12 @@
       <c r="J74" s="10"/>
       <c r="K74" s="10"/>
       <c r="L74" s="10"/>
-      <c r="M74" s="5"/>
+      <c r="M74" s="10"/>
+      <c r="N74" s="10"/>
+      <c r="O74" s="5"/>
+      <c r="P74" s="5"/>
+      <c r="Q74" s="10"/>
+      <c r="R74" s="10"/>
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="5"/>
@@ -3582,7 +4634,12 @@
       <c r="J75" s="10"/>
       <c r="K75" s="10"/>
       <c r="L75" s="10"/>
-      <c r="M75" s="5"/>
+      <c r="M75" s="10"/>
+      <c r="N75" s="10"/>
+      <c r="O75" s="5"/>
+      <c r="P75" s="5"/>
+      <c r="Q75" s="10"/>
+      <c r="R75" s="10"/>
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="5"/>
@@ -3597,7 +4654,12 @@
       <c r="J76" s="10"/>
       <c r="K76" s="10"/>
       <c r="L76" s="10"/>
-      <c r="M76" s="5"/>
+      <c r="M76" s="10"/>
+      <c r="N76" s="10"/>
+      <c r="O76" s="5"/>
+      <c r="P76" s="5"/>
+      <c r="Q76" s="10"/>
+      <c r="R76" s="10"/>
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="5"/>
@@ -3612,7 +4674,12 @@
       <c r="J77" s="10"/>
       <c r="K77" s="10"/>
       <c r="L77" s="10"/>
-      <c r="M77" s="5"/>
+      <c r="M77" s="10"/>
+      <c r="N77" s="10"/>
+      <c r="O77" s="5"/>
+      <c r="P77" s="5"/>
+      <c r="Q77" s="10"/>
+      <c r="R77" s="10"/>
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="5"/>
@@ -3627,7 +4694,12 @@
       <c r="J78" s="10"/>
       <c r="K78" s="10"/>
       <c r="L78" s="10"/>
-      <c r="M78" s="5"/>
+      <c r="M78" s="10"/>
+      <c r="N78" s="10"/>
+      <c r="O78" s="5"/>
+      <c r="P78" s="5"/>
+      <c r="Q78" s="10"/>
+      <c r="R78" s="10"/>
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="5"/>
@@ -3642,7 +4714,12 @@
       <c r="J79" s="10"/>
       <c r="K79" s="10"/>
       <c r="L79" s="10"/>
-      <c r="M79" s="5"/>
+      <c r="M79" s="10"/>
+      <c r="N79" s="10"/>
+      <c r="O79" s="5"/>
+      <c r="P79" s="5"/>
+      <c r="Q79" s="10"/>
+      <c r="R79" s="10"/>
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="5"/>
@@ -3657,7 +4734,12 @@
       <c r="J80" s="10"/>
       <c r="K80" s="10"/>
       <c r="L80" s="10"/>
-      <c r="M80" s="5"/>
+      <c r="M80" s="10"/>
+      <c r="N80" s="10"/>
+      <c r="O80" s="5"/>
+      <c r="P80" s="5"/>
+      <c r="Q80" s="10"/>
+      <c r="R80" s="10"/>
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="5"/>
@@ -3672,7 +4754,12 @@
       <c r="J81" s="10"/>
       <c r="K81" s="10"/>
       <c r="L81" s="10"/>
-      <c r="M81" s="5"/>
+      <c r="M81" s="10"/>
+      <c r="N81" s="10"/>
+      <c r="O81" s="5"/>
+      <c r="P81" s="5"/>
+      <c r="Q81" s="10"/>
+      <c r="R81" s="10"/>
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="5"/>
@@ -3687,7 +4774,12 @@
       <c r="J82" s="10"/>
       <c r="K82" s="10"/>
       <c r="L82" s="10"/>
-      <c r="M82" s="5"/>
+      <c r="M82" s="10"/>
+      <c r="N82" s="10"/>
+      <c r="O82" s="5"/>
+      <c r="P82" s="5"/>
+      <c r="Q82" s="10"/>
+      <c r="R82" s="10"/>
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="5"/>
@@ -3702,7 +4794,12 @@
       <c r="J83" s="10"/>
       <c r="K83" s="10"/>
       <c r="L83" s="10"/>
-      <c r="M83" s="5"/>
+      <c r="M83" s="10"/>
+      <c r="N83" s="10"/>
+      <c r="O83" s="5"/>
+      <c r="P83" s="5"/>
+      <c r="Q83" s="10"/>
+      <c r="R83" s="10"/>
     </row>
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="5"/>
@@ -3717,10 +4814,15 @@
       <c r="J84" s="10"/>
       <c r="K84" s="10"/>
       <c r="L84" s="10"/>
-      <c r="M84" s="5"/>
+      <c r="M84" s="10"/>
+      <c r="N84" s="10"/>
+      <c r="O84" s="5"/>
+      <c r="P84" s="5"/>
+      <c r="Q84" s="10"/>
+      <c r="R84" s="10"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A5:M84">
+  <conditionalFormatting sqref="A5:R84">
     <cfRule type="expression" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
       <formula>$A5&lt;&gt;""</formula>
     </cfRule>
@@ -3730,7 +4832,7 @@
       <formula>$C5="P. Principal"</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="8">
+  <dataValidations count="12">
     <dataValidation allowBlank="true" error="Solo un número de 1 a 20." errorStyle="stop" errorTitle="Series" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="E5:E84" type="whole">
       <formula1>1</formula1>
       <formula2>20</formula2>
@@ -3755,12 +4857,28 @@
       <formula1>"Sí"</formula1>
       <formula2>0</formula2>
     </dataValidation>
+    <dataValidation allowBlank="true" error="Minutos del aeróbico (0,5 = 30 s)." errorStyle="stop" errorTitle="Minutos" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="M5:M84" type="decimal">
+      <formula1>0</formula1>
+      <formula2>600</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Un número de 0 a 10." errorStyle="stop" errorTitle="RPE pre" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="Q5:Q84" type="decimal">
+      <formula1>0</formula1>
+      <formula2>10</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Un número de 0 a 10." errorStyle="stop" errorTitle="RPE post" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="R5:R84" type="decimal">
+      <formula1>0</formula1>
+      <formula2>10</formula2>
+    </dataValidation>
     <dataValidation allowBlank="true" error="Elige un día del desplegable (Lunes … Domingo)." errorStyle="stop" errorTitle="Día" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="A5:A84" type="list">
       <formula1>"Lunes,Martes,Miércoles,Jueves,Viernes,Sábado,Domingo"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Elige un bloque del desplegable." errorStyle="stop" errorTitle="Bloque" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C5:C84" type="list">
-      <formula1>"Activación,P. Principal,Accesorios,Vuelta a la calma"</formula1>
+      <formula1>"Activación,P. Principal,Aeróbico,Accesorios,Vuelta a la calma"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Elige una zona del desplegable." errorStyle="stop" errorTitle="Zona" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="N5:N84" type="list">
+      <formula1>"Z1,Z2,Z3,Z4,Z5"</formula1>
       <formula2>0</formula2>
     </dataValidation>
   </dataValidations>
@@ -3779,7 +4897,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:M84"/>
+  <dimension ref="A1:R84"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="15"/>
@@ -3791,12 +4909,16 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="8" style="0" width="9"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="7"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="11" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="0" width="7"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="0" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="0" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="17" style="0" width="8"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="6" t="s">
-        <v>42</v>
+        <v>54</v>
       </c>
       <c r="B1" s="11" t="n">
         <f aca="false">'Semana 2'!B1+7</f>
@@ -3809,49 +4931,64 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="8" t="s">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="B2" s="9"/>
     </row>
     <row r="4" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="I4" s="4" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="J4" s="4" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="K4" s="4" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="L4" s="4" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="M4" s="4" t="s">
-        <v>26</v>
+        <v>28</v>
+      </c>
+      <c r="N4" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="O4" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="P4" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q4" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="R4" s="4" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3867,7 +5004,12 @@
       <c r="J5" s="10"/>
       <c r="K5" s="10"/>
       <c r="L5" s="10"/>
-      <c r="M5" s="5"/>
+      <c r="M5" s="10"/>
+      <c r="N5" s="10"/>
+      <c r="O5" s="5"/>
+      <c r="P5" s="5"/>
+      <c r="Q5" s="10"/>
+      <c r="R5" s="10"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="5"/>
@@ -3882,7 +5024,12 @@
       <c r="J6" s="10"/>
       <c r="K6" s="10"/>
       <c r="L6" s="10"/>
-      <c r="M6" s="5"/>
+      <c r="M6" s="10"/>
+      <c r="N6" s="10"/>
+      <c r="O6" s="5"/>
+      <c r="P6" s="5"/>
+      <c r="Q6" s="10"/>
+      <c r="R6" s="10"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="5"/>
@@ -3897,7 +5044,12 @@
       <c r="J7" s="10"/>
       <c r="K7" s="10"/>
       <c r="L7" s="10"/>
-      <c r="M7" s="5"/>
+      <c r="M7" s="10"/>
+      <c r="N7" s="10"/>
+      <c r="O7" s="5"/>
+      <c r="P7" s="5"/>
+      <c r="Q7" s="10"/>
+      <c r="R7" s="10"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="5"/>
@@ -3912,7 +5064,12 @@
       <c r="J8" s="10"/>
       <c r="K8" s="10"/>
       <c r="L8" s="10"/>
-      <c r="M8" s="5"/>
+      <c r="M8" s="10"/>
+      <c r="N8" s="10"/>
+      <c r="O8" s="5"/>
+      <c r="P8" s="5"/>
+      <c r="Q8" s="10"/>
+      <c r="R8" s="10"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="5"/>
@@ -3927,7 +5084,12 @@
       <c r="J9" s="10"/>
       <c r="K9" s="10"/>
       <c r="L9" s="10"/>
-      <c r="M9" s="5"/>
+      <c r="M9" s="10"/>
+      <c r="N9" s="10"/>
+      <c r="O9" s="5"/>
+      <c r="P9" s="5"/>
+      <c r="Q9" s="10"/>
+      <c r="R9" s="10"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="5"/>
@@ -3942,7 +5104,12 @@
       <c r="J10" s="10"/>
       <c r="K10" s="10"/>
       <c r="L10" s="10"/>
-      <c r="M10" s="5"/>
+      <c r="M10" s="10"/>
+      <c r="N10" s="10"/>
+      <c r="O10" s="5"/>
+      <c r="P10" s="5"/>
+      <c r="Q10" s="10"/>
+      <c r="R10" s="10"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="5"/>
@@ -3957,7 +5124,12 @@
       <c r="J11" s="10"/>
       <c r="K11" s="10"/>
       <c r="L11" s="10"/>
-      <c r="M11" s="5"/>
+      <c r="M11" s="10"/>
+      <c r="N11" s="10"/>
+      <c r="O11" s="5"/>
+      <c r="P11" s="5"/>
+      <c r="Q11" s="10"/>
+      <c r="R11" s="10"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="5"/>
@@ -3972,7 +5144,12 @@
       <c r="J12" s="10"/>
       <c r="K12" s="10"/>
       <c r="L12" s="10"/>
-      <c r="M12" s="5"/>
+      <c r="M12" s="10"/>
+      <c r="N12" s="10"/>
+      <c r="O12" s="5"/>
+      <c r="P12" s="5"/>
+      <c r="Q12" s="10"/>
+      <c r="R12" s="10"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="5"/>
@@ -3987,7 +5164,12 @@
       <c r="J13" s="10"/>
       <c r="K13" s="10"/>
       <c r="L13" s="10"/>
-      <c r="M13" s="5"/>
+      <c r="M13" s="10"/>
+      <c r="N13" s="10"/>
+      <c r="O13" s="5"/>
+      <c r="P13" s="5"/>
+      <c r="Q13" s="10"/>
+      <c r="R13" s="10"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="5"/>
@@ -4002,7 +5184,12 @@
       <c r="J14" s="10"/>
       <c r="K14" s="10"/>
       <c r="L14" s="10"/>
-      <c r="M14" s="5"/>
+      <c r="M14" s="10"/>
+      <c r="N14" s="10"/>
+      <c r="O14" s="5"/>
+      <c r="P14" s="5"/>
+      <c r="Q14" s="10"/>
+      <c r="R14" s="10"/>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="5"/>
@@ -4017,7 +5204,12 @@
       <c r="J15" s="10"/>
       <c r="K15" s="10"/>
       <c r="L15" s="10"/>
-      <c r="M15" s="5"/>
+      <c r="M15" s="10"/>
+      <c r="N15" s="10"/>
+      <c r="O15" s="5"/>
+      <c r="P15" s="5"/>
+      <c r="Q15" s="10"/>
+      <c r="R15" s="10"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="5"/>
@@ -4032,7 +5224,12 @@
       <c r="J16" s="10"/>
       <c r="K16" s="10"/>
       <c r="L16" s="10"/>
-      <c r="M16" s="5"/>
+      <c r="M16" s="10"/>
+      <c r="N16" s="10"/>
+      <c r="O16" s="5"/>
+      <c r="P16" s="5"/>
+      <c r="Q16" s="10"/>
+      <c r="R16" s="10"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="5"/>
@@ -4047,7 +5244,12 @@
       <c r="J17" s="10"/>
       <c r="K17" s="10"/>
       <c r="L17" s="10"/>
-      <c r="M17" s="5"/>
+      <c r="M17" s="10"/>
+      <c r="N17" s="10"/>
+      <c r="O17" s="5"/>
+      <c r="P17" s="5"/>
+      <c r="Q17" s="10"/>
+      <c r="R17" s="10"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="5"/>
@@ -4062,7 +5264,12 @@
       <c r="J18" s="10"/>
       <c r="K18" s="10"/>
       <c r="L18" s="10"/>
-      <c r="M18" s="5"/>
+      <c r="M18" s="10"/>
+      <c r="N18" s="10"/>
+      <c r="O18" s="5"/>
+      <c r="P18" s="5"/>
+      <c r="Q18" s="10"/>
+      <c r="R18" s="10"/>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="5"/>
@@ -4077,7 +5284,12 @@
       <c r="J19" s="10"/>
       <c r="K19" s="10"/>
       <c r="L19" s="10"/>
-      <c r="M19" s="5"/>
+      <c r="M19" s="10"/>
+      <c r="N19" s="10"/>
+      <c r="O19" s="5"/>
+      <c r="P19" s="5"/>
+      <c r="Q19" s="10"/>
+      <c r="R19" s="10"/>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="5"/>
@@ -4092,7 +5304,12 @@
       <c r="J20" s="10"/>
       <c r="K20" s="10"/>
       <c r="L20" s="10"/>
-      <c r="M20" s="5"/>
+      <c r="M20" s="10"/>
+      <c r="N20" s="10"/>
+      <c r="O20" s="5"/>
+      <c r="P20" s="5"/>
+      <c r="Q20" s="10"/>
+      <c r="R20" s="10"/>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="5"/>
@@ -4107,7 +5324,12 @@
       <c r="J21" s="10"/>
       <c r="K21" s="10"/>
       <c r="L21" s="10"/>
-      <c r="M21" s="5"/>
+      <c r="M21" s="10"/>
+      <c r="N21" s="10"/>
+      <c r="O21" s="5"/>
+      <c r="P21" s="5"/>
+      <c r="Q21" s="10"/>
+      <c r="R21" s="10"/>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="5"/>
@@ -4122,7 +5344,12 @@
       <c r="J22" s="10"/>
       <c r="K22" s="10"/>
       <c r="L22" s="10"/>
-      <c r="M22" s="5"/>
+      <c r="M22" s="10"/>
+      <c r="N22" s="10"/>
+      <c r="O22" s="5"/>
+      <c r="P22" s="5"/>
+      <c r="Q22" s="10"/>
+      <c r="R22" s="10"/>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="5"/>
@@ -4137,7 +5364,12 @@
       <c r="J23" s="10"/>
       <c r="K23" s="10"/>
       <c r="L23" s="10"/>
-      <c r="M23" s="5"/>
+      <c r="M23" s="10"/>
+      <c r="N23" s="10"/>
+      <c r="O23" s="5"/>
+      <c r="P23" s="5"/>
+      <c r="Q23" s="10"/>
+      <c r="R23" s="10"/>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="5"/>
@@ -4152,7 +5384,12 @@
       <c r="J24" s="10"/>
       <c r="K24" s="10"/>
       <c r="L24" s="10"/>
-      <c r="M24" s="5"/>
+      <c r="M24" s="10"/>
+      <c r="N24" s="10"/>
+      <c r="O24" s="5"/>
+      <c r="P24" s="5"/>
+      <c r="Q24" s="10"/>
+      <c r="R24" s="10"/>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="5"/>
@@ -4167,7 +5404,12 @@
       <c r="J25" s="10"/>
       <c r="K25" s="10"/>
       <c r="L25" s="10"/>
-      <c r="M25" s="5"/>
+      <c r="M25" s="10"/>
+      <c r="N25" s="10"/>
+      <c r="O25" s="5"/>
+      <c r="P25" s="5"/>
+      <c r="Q25" s="10"/>
+      <c r="R25" s="10"/>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="5"/>
@@ -4182,7 +5424,12 @@
       <c r="J26" s="10"/>
       <c r="K26" s="10"/>
       <c r="L26" s="10"/>
-      <c r="M26" s="5"/>
+      <c r="M26" s="10"/>
+      <c r="N26" s="10"/>
+      <c r="O26" s="5"/>
+      <c r="P26" s="5"/>
+      <c r="Q26" s="10"/>
+      <c r="R26" s="10"/>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="5"/>
@@ -4197,7 +5444,12 @@
       <c r="J27" s="10"/>
       <c r="K27" s="10"/>
       <c r="L27" s="10"/>
-      <c r="M27" s="5"/>
+      <c r="M27" s="10"/>
+      <c r="N27" s="10"/>
+      <c r="O27" s="5"/>
+      <c r="P27" s="5"/>
+      <c r="Q27" s="10"/>
+      <c r="R27" s="10"/>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="5"/>
@@ -4212,7 +5464,12 @@
       <c r="J28" s="10"/>
       <c r="K28" s="10"/>
       <c r="L28" s="10"/>
-      <c r="M28" s="5"/>
+      <c r="M28" s="10"/>
+      <c r="N28" s="10"/>
+      <c r="O28" s="5"/>
+      <c r="P28" s="5"/>
+      <c r="Q28" s="10"/>
+      <c r="R28" s="10"/>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="5"/>
@@ -4227,7 +5484,12 @@
       <c r="J29" s="10"/>
       <c r="K29" s="10"/>
       <c r="L29" s="10"/>
-      <c r="M29" s="5"/>
+      <c r="M29" s="10"/>
+      <c r="N29" s="10"/>
+      <c r="O29" s="5"/>
+      <c r="P29" s="5"/>
+      <c r="Q29" s="10"/>
+      <c r="R29" s="10"/>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="5"/>
@@ -4242,7 +5504,12 @@
       <c r="J30" s="10"/>
       <c r="K30" s="10"/>
       <c r="L30" s="10"/>
-      <c r="M30" s="5"/>
+      <c r="M30" s="10"/>
+      <c r="N30" s="10"/>
+      <c r="O30" s="5"/>
+      <c r="P30" s="5"/>
+      <c r="Q30" s="10"/>
+      <c r="R30" s="10"/>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="5"/>
@@ -4257,7 +5524,12 @@
       <c r="J31" s="10"/>
       <c r="K31" s="10"/>
       <c r="L31" s="10"/>
-      <c r="M31" s="5"/>
+      <c r="M31" s="10"/>
+      <c r="N31" s="10"/>
+      <c r="O31" s="5"/>
+      <c r="P31" s="5"/>
+      <c r="Q31" s="10"/>
+      <c r="R31" s="10"/>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="5"/>
@@ -4272,7 +5544,12 @@
       <c r="J32" s="10"/>
       <c r="K32" s="10"/>
       <c r="L32" s="10"/>
-      <c r="M32" s="5"/>
+      <c r="M32" s="10"/>
+      <c r="N32" s="10"/>
+      <c r="O32" s="5"/>
+      <c r="P32" s="5"/>
+      <c r="Q32" s="10"/>
+      <c r="R32" s="10"/>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="5"/>
@@ -4287,7 +5564,12 @@
       <c r="J33" s="10"/>
       <c r="K33" s="10"/>
       <c r="L33" s="10"/>
-      <c r="M33" s="5"/>
+      <c r="M33" s="10"/>
+      <c r="N33" s="10"/>
+      <c r="O33" s="5"/>
+      <c r="P33" s="5"/>
+      <c r="Q33" s="10"/>
+      <c r="R33" s="10"/>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="5"/>
@@ -4302,7 +5584,12 @@
       <c r="J34" s="10"/>
       <c r="K34" s="10"/>
       <c r="L34" s="10"/>
-      <c r="M34" s="5"/>
+      <c r="M34" s="10"/>
+      <c r="N34" s="10"/>
+      <c r="O34" s="5"/>
+      <c r="P34" s="5"/>
+      <c r="Q34" s="10"/>
+      <c r="R34" s="10"/>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="5"/>
@@ -4317,7 +5604,12 @@
       <c r="J35" s="10"/>
       <c r="K35" s="10"/>
       <c r="L35" s="10"/>
-      <c r="M35" s="5"/>
+      <c r="M35" s="10"/>
+      <c r="N35" s="10"/>
+      <c r="O35" s="5"/>
+      <c r="P35" s="5"/>
+      <c r="Q35" s="10"/>
+      <c r="R35" s="10"/>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="5"/>
@@ -4332,7 +5624,12 @@
       <c r="J36" s="10"/>
       <c r="K36" s="10"/>
       <c r="L36" s="10"/>
-      <c r="M36" s="5"/>
+      <c r="M36" s="10"/>
+      <c r="N36" s="10"/>
+      <c r="O36" s="5"/>
+      <c r="P36" s="5"/>
+      <c r="Q36" s="10"/>
+      <c r="R36" s="10"/>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="5"/>
@@ -4347,7 +5644,12 @@
       <c r="J37" s="10"/>
       <c r="K37" s="10"/>
       <c r="L37" s="10"/>
-      <c r="M37" s="5"/>
+      <c r="M37" s="10"/>
+      <c r="N37" s="10"/>
+      <c r="O37" s="5"/>
+      <c r="P37" s="5"/>
+      <c r="Q37" s="10"/>
+      <c r="R37" s="10"/>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="5"/>
@@ -4362,7 +5664,12 @@
       <c r="J38" s="10"/>
       <c r="K38" s="10"/>
       <c r="L38" s="10"/>
-      <c r="M38" s="5"/>
+      <c r="M38" s="10"/>
+      <c r="N38" s="10"/>
+      <c r="O38" s="5"/>
+      <c r="P38" s="5"/>
+      <c r="Q38" s="10"/>
+      <c r="R38" s="10"/>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="5"/>
@@ -4377,7 +5684,12 @@
       <c r="J39" s="10"/>
       <c r="K39" s="10"/>
       <c r="L39" s="10"/>
-      <c r="M39" s="5"/>
+      <c r="M39" s="10"/>
+      <c r="N39" s="10"/>
+      <c r="O39" s="5"/>
+      <c r="P39" s="5"/>
+      <c r="Q39" s="10"/>
+      <c r="R39" s="10"/>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="5"/>
@@ -4392,7 +5704,12 @@
       <c r="J40" s="10"/>
       <c r="K40" s="10"/>
       <c r="L40" s="10"/>
-      <c r="M40" s="5"/>
+      <c r="M40" s="10"/>
+      <c r="N40" s="10"/>
+      <c r="O40" s="5"/>
+      <c r="P40" s="5"/>
+      <c r="Q40" s="10"/>
+      <c r="R40" s="10"/>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="5"/>
@@ -4407,7 +5724,12 @@
       <c r="J41" s="10"/>
       <c r="K41" s="10"/>
       <c r="L41" s="10"/>
-      <c r="M41" s="5"/>
+      <c r="M41" s="10"/>
+      <c r="N41" s="10"/>
+      <c r="O41" s="5"/>
+      <c r="P41" s="5"/>
+      <c r="Q41" s="10"/>
+      <c r="R41" s="10"/>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="5"/>
@@ -4422,7 +5744,12 @@
       <c r="J42" s="10"/>
       <c r="K42" s="10"/>
       <c r="L42" s="10"/>
-      <c r="M42" s="5"/>
+      <c r="M42" s="10"/>
+      <c r="N42" s="10"/>
+      <c r="O42" s="5"/>
+      <c r="P42" s="5"/>
+      <c r="Q42" s="10"/>
+      <c r="R42" s="10"/>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="5"/>
@@ -4437,7 +5764,12 @@
       <c r="J43" s="10"/>
       <c r="K43" s="10"/>
       <c r="L43" s="10"/>
-      <c r="M43" s="5"/>
+      <c r="M43" s="10"/>
+      <c r="N43" s="10"/>
+      <c r="O43" s="5"/>
+      <c r="P43" s="5"/>
+      <c r="Q43" s="10"/>
+      <c r="R43" s="10"/>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="5"/>
@@ -4452,7 +5784,12 @@
       <c r="J44" s="10"/>
       <c r="K44" s="10"/>
       <c r="L44" s="10"/>
-      <c r="M44" s="5"/>
+      <c r="M44" s="10"/>
+      <c r="N44" s="10"/>
+      <c r="O44" s="5"/>
+      <c r="P44" s="5"/>
+      <c r="Q44" s="10"/>
+      <c r="R44" s="10"/>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="5"/>
@@ -4467,7 +5804,12 @@
       <c r="J45" s="10"/>
       <c r="K45" s="10"/>
       <c r="L45" s="10"/>
-      <c r="M45" s="5"/>
+      <c r="M45" s="10"/>
+      <c r="N45" s="10"/>
+      <c r="O45" s="5"/>
+      <c r="P45" s="5"/>
+      <c r="Q45" s="10"/>
+      <c r="R45" s="10"/>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="5"/>
@@ -4482,7 +5824,12 @@
       <c r="J46" s="10"/>
       <c r="K46" s="10"/>
       <c r="L46" s="10"/>
-      <c r="M46" s="5"/>
+      <c r="M46" s="10"/>
+      <c r="N46" s="10"/>
+      <c r="O46" s="5"/>
+      <c r="P46" s="5"/>
+      <c r="Q46" s="10"/>
+      <c r="R46" s="10"/>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="5"/>
@@ -4497,7 +5844,12 @@
       <c r="J47" s="10"/>
       <c r="K47" s="10"/>
       <c r="L47" s="10"/>
-      <c r="M47" s="5"/>
+      <c r="M47" s="10"/>
+      <c r="N47" s="10"/>
+      <c r="O47" s="5"/>
+      <c r="P47" s="5"/>
+      <c r="Q47" s="10"/>
+      <c r="R47" s="10"/>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="5"/>
@@ -4512,7 +5864,12 @@
       <c r="J48" s="10"/>
       <c r="K48" s="10"/>
       <c r="L48" s="10"/>
-      <c r="M48" s="5"/>
+      <c r="M48" s="10"/>
+      <c r="N48" s="10"/>
+      <c r="O48" s="5"/>
+      <c r="P48" s="5"/>
+      <c r="Q48" s="10"/>
+      <c r="R48" s="10"/>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="5"/>
@@ -4527,7 +5884,12 @@
       <c r="J49" s="10"/>
       <c r="K49" s="10"/>
       <c r="L49" s="10"/>
-      <c r="M49" s="5"/>
+      <c r="M49" s="10"/>
+      <c r="N49" s="10"/>
+      <c r="O49" s="5"/>
+      <c r="P49" s="5"/>
+      <c r="Q49" s="10"/>
+      <c r="R49" s="10"/>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="5"/>
@@ -4542,7 +5904,12 @@
       <c r="J50" s="10"/>
       <c r="K50" s="10"/>
       <c r="L50" s="10"/>
-      <c r="M50" s="5"/>
+      <c r="M50" s="10"/>
+      <c r="N50" s="10"/>
+      <c r="O50" s="5"/>
+      <c r="P50" s="5"/>
+      <c r="Q50" s="10"/>
+      <c r="R50" s="10"/>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="5"/>
@@ -4557,7 +5924,12 @@
       <c r="J51" s="10"/>
       <c r="K51" s="10"/>
       <c r="L51" s="10"/>
-      <c r="M51" s="5"/>
+      <c r="M51" s="10"/>
+      <c r="N51" s="10"/>
+      <c r="O51" s="5"/>
+      <c r="P51" s="5"/>
+      <c r="Q51" s="10"/>
+      <c r="R51" s="10"/>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="5"/>
@@ -4572,7 +5944,12 @@
       <c r="J52" s="10"/>
       <c r="K52" s="10"/>
       <c r="L52" s="10"/>
-      <c r="M52" s="5"/>
+      <c r="M52" s="10"/>
+      <c r="N52" s="10"/>
+      <c r="O52" s="5"/>
+      <c r="P52" s="5"/>
+      <c r="Q52" s="10"/>
+      <c r="R52" s="10"/>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="5"/>
@@ -4587,7 +5964,12 @@
       <c r="J53" s="10"/>
       <c r="K53" s="10"/>
       <c r="L53" s="10"/>
-      <c r="M53" s="5"/>
+      <c r="M53" s="10"/>
+      <c r="N53" s="10"/>
+      <c r="O53" s="5"/>
+      <c r="P53" s="5"/>
+      <c r="Q53" s="10"/>
+      <c r="R53" s="10"/>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="5"/>
@@ -4602,7 +5984,12 @@
       <c r="J54" s="10"/>
       <c r="K54" s="10"/>
       <c r="L54" s="10"/>
-      <c r="M54" s="5"/>
+      <c r="M54" s="10"/>
+      <c r="N54" s="10"/>
+      <c r="O54" s="5"/>
+      <c r="P54" s="5"/>
+      <c r="Q54" s="10"/>
+      <c r="R54" s="10"/>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="5"/>
@@ -4617,7 +6004,12 @@
       <c r="J55" s="10"/>
       <c r="K55" s="10"/>
       <c r="L55" s="10"/>
-      <c r="M55" s="5"/>
+      <c r="M55" s="10"/>
+      <c r="N55" s="10"/>
+      <c r="O55" s="5"/>
+      <c r="P55" s="5"/>
+      <c r="Q55" s="10"/>
+      <c r="R55" s="10"/>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="5"/>
@@ -4632,7 +6024,12 @@
       <c r="J56" s="10"/>
       <c r="K56" s="10"/>
       <c r="L56" s="10"/>
-      <c r="M56" s="5"/>
+      <c r="M56" s="10"/>
+      <c r="N56" s="10"/>
+      <c r="O56" s="5"/>
+      <c r="P56" s="5"/>
+      <c r="Q56" s="10"/>
+      <c r="R56" s="10"/>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="5"/>
@@ -4647,7 +6044,12 @@
       <c r="J57" s="10"/>
       <c r="K57" s="10"/>
       <c r="L57" s="10"/>
-      <c r="M57" s="5"/>
+      <c r="M57" s="10"/>
+      <c r="N57" s="10"/>
+      <c r="O57" s="5"/>
+      <c r="P57" s="5"/>
+      <c r="Q57" s="10"/>
+      <c r="R57" s="10"/>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="5"/>
@@ -4662,7 +6064,12 @@
       <c r="J58" s="10"/>
       <c r="K58" s="10"/>
       <c r="L58" s="10"/>
-      <c r="M58" s="5"/>
+      <c r="M58" s="10"/>
+      <c r="N58" s="10"/>
+      <c r="O58" s="5"/>
+      <c r="P58" s="5"/>
+      <c r="Q58" s="10"/>
+      <c r="R58" s="10"/>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="5"/>
@@ -4677,7 +6084,12 @@
       <c r="J59" s="10"/>
       <c r="K59" s="10"/>
       <c r="L59" s="10"/>
-      <c r="M59" s="5"/>
+      <c r="M59" s="10"/>
+      <c r="N59" s="10"/>
+      <c r="O59" s="5"/>
+      <c r="P59" s="5"/>
+      <c r="Q59" s="10"/>
+      <c r="R59" s="10"/>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="5"/>
@@ -4692,7 +6104,12 @@
       <c r="J60" s="10"/>
       <c r="K60" s="10"/>
       <c r="L60" s="10"/>
-      <c r="M60" s="5"/>
+      <c r="M60" s="10"/>
+      <c r="N60" s="10"/>
+      <c r="O60" s="5"/>
+      <c r="P60" s="5"/>
+      <c r="Q60" s="10"/>
+      <c r="R60" s="10"/>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="5"/>
@@ -4707,7 +6124,12 @@
       <c r="J61" s="10"/>
       <c r="K61" s="10"/>
       <c r="L61" s="10"/>
-      <c r="M61" s="5"/>
+      <c r="M61" s="10"/>
+      <c r="N61" s="10"/>
+      <c r="O61" s="5"/>
+      <c r="P61" s="5"/>
+      <c r="Q61" s="10"/>
+      <c r="R61" s="10"/>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="5"/>
@@ -4722,7 +6144,12 @@
       <c r="J62" s="10"/>
       <c r="K62" s="10"/>
       <c r="L62" s="10"/>
-      <c r="M62" s="5"/>
+      <c r="M62" s="10"/>
+      <c r="N62" s="10"/>
+      <c r="O62" s="5"/>
+      <c r="P62" s="5"/>
+      <c r="Q62" s="10"/>
+      <c r="R62" s="10"/>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="5"/>
@@ -4737,7 +6164,12 @@
       <c r="J63" s="10"/>
       <c r="K63" s="10"/>
       <c r="L63" s="10"/>
-      <c r="M63" s="5"/>
+      <c r="M63" s="10"/>
+      <c r="N63" s="10"/>
+      <c r="O63" s="5"/>
+      <c r="P63" s="5"/>
+      <c r="Q63" s="10"/>
+      <c r="R63" s="10"/>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="5"/>
@@ -4752,7 +6184,12 @@
       <c r="J64" s="10"/>
       <c r="K64" s="10"/>
       <c r="L64" s="10"/>
-      <c r="M64" s="5"/>
+      <c r="M64" s="10"/>
+      <c r="N64" s="10"/>
+      <c r="O64" s="5"/>
+      <c r="P64" s="5"/>
+      <c r="Q64" s="10"/>
+      <c r="R64" s="10"/>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="5"/>
@@ -4767,7 +6204,12 @@
       <c r="J65" s="10"/>
       <c r="K65" s="10"/>
       <c r="L65" s="10"/>
-      <c r="M65" s="5"/>
+      <c r="M65" s="10"/>
+      <c r="N65" s="10"/>
+      <c r="O65" s="5"/>
+      <c r="P65" s="5"/>
+      <c r="Q65" s="10"/>
+      <c r="R65" s="10"/>
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="5"/>
@@ -4782,7 +6224,12 @@
       <c r="J66" s="10"/>
       <c r="K66" s="10"/>
       <c r="L66" s="10"/>
-      <c r="M66" s="5"/>
+      <c r="M66" s="10"/>
+      <c r="N66" s="10"/>
+      <c r="O66" s="5"/>
+      <c r="P66" s="5"/>
+      <c r="Q66" s="10"/>
+      <c r="R66" s="10"/>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="5"/>
@@ -4797,7 +6244,12 @@
       <c r="J67" s="10"/>
       <c r="K67" s="10"/>
       <c r="L67" s="10"/>
-      <c r="M67" s="5"/>
+      <c r="M67" s="10"/>
+      <c r="N67" s="10"/>
+      <c r="O67" s="5"/>
+      <c r="P67" s="5"/>
+      <c r="Q67" s="10"/>
+      <c r="R67" s="10"/>
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="5"/>
@@ -4812,7 +6264,12 @@
       <c r="J68" s="10"/>
       <c r="K68" s="10"/>
       <c r="L68" s="10"/>
-      <c r="M68" s="5"/>
+      <c r="M68" s="10"/>
+      <c r="N68" s="10"/>
+      <c r="O68" s="5"/>
+      <c r="P68" s="5"/>
+      <c r="Q68" s="10"/>
+      <c r="R68" s="10"/>
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="5"/>
@@ -4827,7 +6284,12 @@
       <c r="J69" s="10"/>
       <c r="K69" s="10"/>
       <c r="L69" s="10"/>
-      <c r="M69" s="5"/>
+      <c r="M69" s="10"/>
+      <c r="N69" s="10"/>
+      <c r="O69" s="5"/>
+      <c r="P69" s="5"/>
+      <c r="Q69" s="10"/>
+      <c r="R69" s="10"/>
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="5"/>
@@ -4842,7 +6304,12 @@
       <c r="J70" s="10"/>
       <c r="K70" s="10"/>
       <c r="L70" s="10"/>
-      <c r="M70" s="5"/>
+      <c r="M70" s="10"/>
+      <c r="N70" s="10"/>
+      <c r="O70" s="5"/>
+      <c r="P70" s="5"/>
+      <c r="Q70" s="10"/>
+      <c r="R70" s="10"/>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="5"/>
@@ -4857,7 +6324,12 @@
       <c r="J71" s="10"/>
       <c r="K71" s="10"/>
       <c r="L71" s="10"/>
-      <c r="M71" s="5"/>
+      <c r="M71" s="10"/>
+      <c r="N71" s="10"/>
+      <c r="O71" s="5"/>
+      <c r="P71" s="5"/>
+      <c r="Q71" s="10"/>
+      <c r="R71" s="10"/>
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="5"/>
@@ -4872,7 +6344,12 @@
       <c r="J72" s="10"/>
       <c r="K72" s="10"/>
       <c r="L72" s="10"/>
-      <c r="M72" s="5"/>
+      <c r="M72" s="10"/>
+      <c r="N72" s="10"/>
+      <c r="O72" s="5"/>
+      <c r="P72" s="5"/>
+      <c r="Q72" s="10"/>
+      <c r="R72" s="10"/>
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="5"/>
@@ -4887,7 +6364,12 @@
       <c r="J73" s="10"/>
       <c r="K73" s="10"/>
       <c r="L73" s="10"/>
-      <c r="M73" s="5"/>
+      <c r="M73" s="10"/>
+      <c r="N73" s="10"/>
+      <c r="O73" s="5"/>
+      <c r="P73" s="5"/>
+      <c r="Q73" s="10"/>
+      <c r="R73" s="10"/>
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="5"/>
@@ -4902,7 +6384,12 @@
       <c r="J74" s="10"/>
       <c r="K74" s="10"/>
       <c r="L74" s="10"/>
-      <c r="M74" s="5"/>
+      <c r="M74" s="10"/>
+      <c r="N74" s="10"/>
+      <c r="O74" s="5"/>
+      <c r="P74" s="5"/>
+      <c r="Q74" s="10"/>
+      <c r="R74" s="10"/>
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="5"/>
@@ -4917,7 +6404,12 @@
       <c r="J75" s="10"/>
       <c r="K75" s="10"/>
       <c r="L75" s="10"/>
-      <c r="M75" s="5"/>
+      <c r="M75" s="10"/>
+      <c r="N75" s="10"/>
+      <c r="O75" s="5"/>
+      <c r="P75" s="5"/>
+      <c r="Q75" s="10"/>
+      <c r="R75" s="10"/>
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="5"/>
@@ -4932,7 +6424,12 @@
       <c r="J76" s="10"/>
       <c r="K76" s="10"/>
       <c r="L76" s="10"/>
-      <c r="M76" s="5"/>
+      <c r="M76" s="10"/>
+      <c r="N76" s="10"/>
+      <c r="O76" s="5"/>
+      <c r="P76" s="5"/>
+      <c r="Q76" s="10"/>
+      <c r="R76" s="10"/>
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="5"/>
@@ -4947,7 +6444,12 @@
       <c r="J77" s="10"/>
       <c r="K77" s="10"/>
       <c r="L77" s="10"/>
-      <c r="M77" s="5"/>
+      <c r="M77" s="10"/>
+      <c r="N77" s="10"/>
+      <c r="O77" s="5"/>
+      <c r="P77" s="5"/>
+      <c r="Q77" s="10"/>
+      <c r="R77" s="10"/>
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="5"/>
@@ -4962,7 +6464,12 @@
       <c r="J78" s="10"/>
       <c r="K78" s="10"/>
       <c r="L78" s="10"/>
-      <c r="M78" s="5"/>
+      <c r="M78" s="10"/>
+      <c r="N78" s="10"/>
+      <c r="O78" s="5"/>
+      <c r="P78" s="5"/>
+      <c r="Q78" s="10"/>
+      <c r="R78" s="10"/>
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="5"/>
@@ -4977,7 +6484,12 @@
       <c r="J79" s="10"/>
       <c r="K79" s="10"/>
       <c r="L79" s="10"/>
-      <c r="M79" s="5"/>
+      <c r="M79" s="10"/>
+      <c r="N79" s="10"/>
+      <c r="O79" s="5"/>
+      <c r="P79" s="5"/>
+      <c r="Q79" s="10"/>
+      <c r="R79" s="10"/>
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="5"/>
@@ -4992,7 +6504,12 @@
       <c r="J80" s="10"/>
       <c r="K80" s="10"/>
       <c r="L80" s="10"/>
-      <c r="M80" s="5"/>
+      <c r="M80" s="10"/>
+      <c r="N80" s="10"/>
+      <c r="O80" s="5"/>
+      <c r="P80" s="5"/>
+      <c r="Q80" s="10"/>
+      <c r="R80" s="10"/>
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="5"/>
@@ -5007,7 +6524,12 @@
       <c r="J81" s="10"/>
       <c r="K81" s="10"/>
       <c r="L81" s="10"/>
-      <c r="M81" s="5"/>
+      <c r="M81" s="10"/>
+      <c r="N81" s="10"/>
+      <c r="O81" s="5"/>
+      <c r="P81" s="5"/>
+      <c r="Q81" s="10"/>
+      <c r="R81" s="10"/>
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="5"/>
@@ -5022,7 +6544,12 @@
       <c r="J82" s="10"/>
       <c r="K82" s="10"/>
       <c r="L82" s="10"/>
-      <c r="M82" s="5"/>
+      <c r="M82" s="10"/>
+      <c r="N82" s="10"/>
+      <c r="O82" s="5"/>
+      <c r="P82" s="5"/>
+      <c r="Q82" s="10"/>
+      <c r="R82" s="10"/>
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="5"/>
@@ -5037,7 +6564,12 @@
       <c r="J83" s="10"/>
       <c r="K83" s="10"/>
       <c r="L83" s="10"/>
-      <c r="M83" s="5"/>
+      <c r="M83" s="10"/>
+      <c r="N83" s="10"/>
+      <c r="O83" s="5"/>
+      <c r="P83" s="5"/>
+      <c r="Q83" s="10"/>
+      <c r="R83" s="10"/>
     </row>
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="5"/>
@@ -5052,10 +6584,15 @@
       <c r="J84" s="10"/>
       <c r="K84" s="10"/>
       <c r="L84" s="10"/>
-      <c r="M84" s="5"/>
+      <c r="M84" s="10"/>
+      <c r="N84" s="10"/>
+      <c r="O84" s="5"/>
+      <c r="P84" s="5"/>
+      <c r="Q84" s="10"/>
+      <c r="R84" s="10"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A5:M84">
+  <conditionalFormatting sqref="A5:R84">
     <cfRule type="expression" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
       <formula>$A5&lt;&gt;""</formula>
     </cfRule>
@@ -5065,7 +6602,7 @@
       <formula>$C5="P. Principal"</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="8">
+  <dataValidations count="12">
     <dataValidation allowBlank="true" error="Solo un número de 1 a 20." errorStyle="stop" errorTitle="Series" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="E5:E84" type="whole">
       <formula1>1</formula1>
       <formula2>20</formula2>
@@ -5090,12 +6627,28 @@
       <formula1>"Sí"</formula1>
       <formula2>0</formula2>
     </dataValidation>
+    <dataValidation allowBlank="true" error="Minutos del aeróbico (0,5 = 30 s)." errorStyle="stop" errorTitle="Minutos" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="M5:M84" type="decimal">
+      <formula1>0</formula1>
+      <formula2>600</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Un número de 0 a 10." errorStyle="stop" errorTitle="RPE pre" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="Q5:Q84" type="decimal">
+      <formula1>0</formula1>
+      <formula2>10</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Un número de 0 a 10." errorStyle="stop" errorTitle="RPE post" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="R5:R84" type="decimal">
+      <formula1>0</formula1>
+      <formula2>10</formula2>
+    </dataValidation>
     <dataValidation allowBlank="true" error="Elige un día del desplegable (Lunes … Domingo)." errorStyle="stop" errorTitle="Día" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="A5:A84" type="list">
       <formula1>"Lunes,Martes,Miércoles,Jueves,Viernes,Sábado,Domingo"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Elige un bloque del desplegable." errorStyle="stop" errorTitle="Bloque" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C5:C84" type="list">
-      <formula1>"Activación,P. Principal,Accesorios,Vuelta a la calma"</formula1>
+      <formula1>"Activación,P. Principal,Aeróbico,Accesorios,Vuelta a la calma"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Elige una zona del desplegable." errorStyle="stop" errorTitle="Zona" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="N5:N84" type="list">
+      <formula1>"Z1,Z2,Z3,Z4,Z5"</formula1>
       <formula2>0</formula2>
     </dataValidation>
   </dataValidations>
@@ -5114,7 +6667,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:M84"/>
+  <dimension ref="A1:R84"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="15"/>
@@ -5126,12 +6679,16 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="8" style="0" width="9"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="7"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="11" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="0" width="7"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="0" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="0" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="17" style="0" width="8"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="6" t="s">
-        <v>42</v>
+        <v>54</v>
       </c>
       <c r="B1" s="11" t="n">
         <f aca="false">'Semana 3'!B1+7</f>
@@ -5144,49 +6701,64 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="8" t="s">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="B2" s="9"/>
     </row>
     <row r="4" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="I4" s="4" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="J4" s="4" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="K4" s="4" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="L4" s="4" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="M4" s="4" t="s">
-        <v>26</v>
+        <v>28</v>
+      </c>
+      <c r="N4" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="O4" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="P4" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q4" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="R4" s="4" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5202,7 +6774,12 @@
       <c r="J5" s="10"/>
       <c r="K5" s="10"/>
       <c r="L5" s="10"/>
-      <c r="M5" s="5"/>
+      <c r="M5" s="10"/>
+      <c r="N5" s="10"/>
+      <c r="O5" s="5"/>
+      <c r="P5" s="5"/>
+      <c r="Q5" s="10"/>
+      <c r="R5" s="10"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="5"/>
@@ -5217,7 +6794,12 @@
       <c r="J6" s="10"/>
       <c r="K6" s="10"/>
       <c r="L6" s="10"/>
-      <c r="M6" s="5"/>
+      <c r="M6" s="10"/>
+      <c r="N6" s="10"/>
+      <c r="O6" s="5"/>
+      <c r="P6" s="5"/>
+      <c r="Q6" s="10"/>
+      <c r="R6" s="10"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="5"/>
@@ -5232,7 +6814,12 @@
       <c r="J7" s="10"/>
       <c r="K7" s="10"/>
       <c r="L7" s="10"/>
-      <c r="M7" s="5"/>
+      <c r="M7" s="10"/>
+      <c r="N7" s="10"/>
+      <c r="O7" s="5"/>
+      <c r="P7" s="5"/>
+      <c r="Q7" s="10"/>
+      <c r="R7" s="10"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="5"/>
@@ -5247,7 +6834,12 @@
       <c r="J8" s="10"/>
       <c r="K8" s="10"/>
       <c r="L8" s="10"/>
-      <c r="M8" s="5"/>
+      <c r="M8" s="10"/>
+      <c r="N8" s="10"/>
+      <c r="O8" s="5"/>
+      <c r="P8" s="5"/>
+      <c r="Q8" s="10"/>
+      <c r="R8" s="10"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="5"/>
@@ -5262,7 +6854,12 @@
       <c r="J9" s="10"/>
       <c r="K9" s="10"/>
       <c r="L9" s="10"/>
-      <c r="M9" s="5"/>
+      <c r="M9" s="10"/>
+      <c r="N9" s="10"/>
+      <c r="O9" s="5"/>
+      <c r="P9" s="5"/>
+      <c r="Q9" s="10"/>
+      <c r="R9" s="10"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="5"/>
@@ -5277,7 +6874,12 @@
       <c r="J10" s="10"/>
       <c r="K10" s="10"/>
       <c r="L10" s="10"/>
-      <c r="M10" s="5"/>
+      <c r="M10" s="10"/>
+      <c r="N10" s="10"/>
+      <c r="O10" s="5"/>
+      <c r="P10" s="5"/>
+      <c r="Q10" s="10"/>
+      <c r="R10" s="10"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="5"/>
@@ -5292,7 +6894,12 @@
       <c r="J11" s="10"/>
       <c r="K11" s="10"/>
       <c r="L11" s="10"/>
-      <c r="M11" s="5"/>
+      <c r="M11" s="10"/>
+      <c r="N11" s="10"/>
+      <c r="O11" s="5"/>
+      <c r="P11" s="5"/>
+      <c r="Q11" s="10"/>
+      <c r="R11" s="10"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="5"/>
@@ -5307,7 +6914,12 @@
       <c r="J12" s="10"/>
       <c r="K12" s="10"/>
       <c r="L12" s="10"/>
-      <c r="M12" s="5"/>
+      <c r="M12" s="10"/>
+      <c r="N12" s="10"/>
+      <c r="O12" s="5"/>
+      <c r="P12" s="5"/>
+      <c r="Q12" s="10"/>
+      <c r="R12" s="10"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="5"/>
@@ -5322,7 +6934,12 @@
       <c r="J13" s="10"/>
       <c r="K13" s="10"/>
       <c r="L13" s="10"/>
-      <c r="M13" s="5"/>
+      <c r="M13" s="10"/>
+      <c r="N13" s="10"/>
+      <c r="O13" s="5"/>
+      <c r="P13" s="5"/>
+      <c r="Q13" s="10"/>
+      <c r="R13" s="10"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="5"/>
@@ -5337,7 +6954,12 @@
       <c r="J14" s="10"/>
       <c r="K14" s="10"/>
       <c r="L14" s="10"/>
-      <c r="M14" s="5"/>
+      <c r="M14" s="10"/>
+      <c r="N14" s="10"/>
+      <c r="O14" s="5"/>
+      <c r="P14" s="5"/>
+      <c r="Q14" s="10"/>
+      <c r="R14" s="10"/>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="5"/>
@@ -5352,7 +6974,12 @@
       <c r="J15" s="10"/>
       <c r="K15" s="10"/>
       <c r="L15" s="10"/>
-      <c r="M15" s="5"/>
+      <c r="M15" s="10"/>
+      <c r="N15" s="10"/>
+      <c r="O15" s="5"/>
+      <c r="P15" s="5"/>
+      <c r="Q15" s="10"/>
+      <c r="R15" s="10"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="5"/>
@@ -5367,7 +6994,12 @@
       <c r="J16" s="10"/>
       <c r="K16" s="10"/>
       <c r="L16" s="10"/>
-      <c r="M16" s="5"/>
+      <c r="M16" s="10"/>
+      <c r="N16" s="10"/>
+      <c r="O16" s="5"/>
+      <c r="P16" s="5"/>
+      <c r="Q16" s="10"/>
+      <c r="R16" s="10"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="5"/>
@@ -5382,7 +7014,12 @@
       <c r="J17" s="10"/>
       <c r="K17" s="10"/>
       <c r="L17" s="10"/>
-      <c r="M17" s="5"/>
+      <c r="M17" s="10"/>
+      <c r="N17" s="10"/>
+      <c r="O17" s="5"/>
+      <c r="P17" s="5"/>
+      <c r="Q17" s="10"/>
+      <c r="R17" s="10"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="5"/>
@@ -5397,7 +7034,12 @@
       <c r="J18" s="10"/>
       <c r="K18" s="10"/>
       <c r="L18" s="10"/>
-      <c r="M18" s="5"/>
+      <c r="M18" s="10"/>
+      <c r="N18" s="10"/>
+      <c r="O18" s="5"/>
+      <c r="P18" s="5"/>
+      <c r="Q18" s="10"/>
+      <c r="R18" s="10"/>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="5"/>
@@ -5412,7 +7054,12 @@
       <c r="J19" s="10"/>
       <c r="K19" s="10"/>
       <c r="L19" s="10"/>
-      <c r="M19" s="5"/>
+      <c r="M19" s="10"/>
+      <c r="N19" s="10"/>
+      <c r="O19" s="5"/>
+      <c r="P19" s="5"/>
+      <c r="Q19" s="10"/>
+      <c r="R19" s="10"/>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="5"/>
@@ -5427,7 +7074,12 @@
       <c r="J20" s="10"/>
       <c r="K20" s="10"/>
       <c r="L20" s="10"/>
-      <c r="M20" s="5"/>
+      <c r="M20" s="10"/>
+      <c r="N20" s="10"/>
+      <c r="O20" s="5"/>
+      <c r="P20" s="5"/>
+      <c r="Q20" s="10"/>
+      <c r="R20" s="10"/>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="5"/>
@@ -5442,7 +7094,12 @@
       <c r="J21" s="10"/>
       <c r="K21" s="10"/>
       <c r="L21" s="10"/>
-      <c r="M21" s="5"/>
+      <c r="M21" s="10"/>
+      <c r="N21" s="10"/>
+      <c r="O21" s="5"/>
+      <c r="P21" s="5"/>
+      <c r="Q21" s="10"/>
+      <c r="R21" s="10"/>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="5"/>
@@ -5457,7 +7114,12 @@
       <c r="J22" s="10"/>
       <c r="K22" s="10"/>
       <c r="L22" s="10"/>
-      <c r="M22" s="5"/>
+      <c r="M22" s="10"/>
+      <c r="N22" s="10"/>
+      <c r="O22" s="5"/>
+      <c r="P22" s="5"/>
+      <c r="Q22" s="10"/>
+      <c r="R22" s="10"/>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="5"/>
@@ -5472,7 +7134,12 @@
       <c r="J23" s="10"/>
       <c r="K23" s="10"/>
       <c r="L23" s="10"/>
-      <c r="M23" s="5"/>
+      <c r="M23" s="10"/>
+      <c r="N23" s="10"/>
+      <c r="O23" s="5"/>
+      <c r="P23" s="5"/>
+      <c r="Q23" s="10"/>
+      <c r="R23" s="10"/>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="5"/>
@@ -5487,7 +7154,12 @@
       <c r="J24" s="10"/>
       <c r="K24" s="10"/>
       <c r="L24" s="10"/>
-      <c r="M24" s="5"/>
+      <c r="M24" s="10"/>
+      <c r="N24" s="10"/>
+      <c r="O24" s="5"/>
+      <c r="P24" s="5"/>
+      <c r="Q24" s="10"/>
+      <c r="R24" s="10"/>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="5"/>
@@ -5502,7 +7174,12 @@
       <c r="J25" s="10"/>
       <c r="K25" s="10"/>
       <c r="L25" s="10"/>
-      <c r="M25" s="5"/>
+      <c r="M25" s="10"/>
+      <c r="N25" s="10"/>
+      <c r="O25" s="5"/>
+      <c r="P25" s="5"/>
+      <c r="Q25" s="10"/>
+      <c r="R25" s="10"/>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="5"/>
@@ -5517,7 +7194,12 @@
       <c r="J26" s="10"/>
       <c r="K26" s="10"/>
       <c r="L26" s="10"/>
-      <c r="M26" s="5"/>
+      <c r="M26" s="10"/>
+      <c r="N26" s="10"/>
+      <c r="O26" s="5"/>
+      <c r="P26" s="5"/>
+      <c r="Q26" s="10"/>
+      <c r="R26" s="10"/>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="5"/>
@@ -5532,7 +7214,12 @@
       <c r="J27" s="10"/>
       <c r="K27" s="10"/>
       <c r="L27" s="10"/>
-      <c r="M27" s="5"/>
+      <c r="M27" s="10"/>
+      <c r="N27" s="10"/>
+      <c r="O27" s="5"/>
+      <c r="P27" s="5"/>
+      <c r="Q27" s="10"/>
+      <c r="R27" s="10"/>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="5"/>
@@ -5547,7 +7234,12 @@
       <c r="J28" s="10"/>
       <c r="K28" s="10"/>
       <c r="L28" s="10"/>
-      <c r="M28" s="5"/>
+      <c r="M28" s="10"/>
+      <c r="N28" s="10"/>
+      <c r="O28" s="5"/>
+      <c r="P28" s="5"/>
+      <c r="Q28" s="10"/>
+      <c r="R28" s="10"/>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="5"/>
@@ -5562,7 +7254,12 @@
       <c r="J29" s="10"/>
       <c r="K29" s="10"/>
       <c r="L29" s="10"/>
-      <c r="M29" s="5"/>
+      <c r="M29" s="10"/>
+      <c r="N29" s="10"/>
+      <c r="O29" s="5"/>
+      <c r="P29" s="5"/>
+      <c r="Q29" s="10"/>
+      <c r="R29" s="10"/>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="5"/>
@@ -5577,7 +7274,12 @@
       <c r="J30" s="10"/>
       <c r="K30" s="10"/>
       <c r="L30" s="10"/>
-      <c r="M30" s="5"/>
+      <c r="M30" s="10"/>
+      <c r="N30" s="10"/>
+      <c r="O30" s="5"/>
+      <c r="P30" s="5"/>
+      <c r="Q30" s="10"/>
+      <c r="R30" s="10"/>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="5"/>
@@ -5592,7 +7294,12 @@
       <c r="J31" s="10"/>
       <c r="K31" s="10"/>
       <c r="L31" s="10"/>
-      <c r="M31" s="5"/>
+      <c r="M31" s="10"/>
+      <c r="N31" s="10"/>
+      <c r="O31" s="5"/>
+      <c r="P31" s="5"/>
+      <c r="Q31" s="10"/>
+      <c r="R31" s="10"/>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="5"/>
@@ -5607,7 +7314,12 @@
       <c r="J32" s="10"/>
       <c r="K32" s="10"/>
       <c r="L32" s="10"/>
-      <c r="M32" s="5"/>
+      <c r="M32" s="10"/>
+      <c r="N32" s="10"/>
+      <c r="O32" s="5"/>
+      <c r="P32" s="5"/>
+      <c r="Q32" s="10"/>
+      <c r="R32" s="10"/>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="5"/>
@@ -5622,7 +7334,12 @@
       <c r="J33" s="10"/>
       <c r="K33" s="10"/>
       <c r="L33" s="10"/>
-      <c r="M33" s="5"/>
+      <c r="M33" s="10"/>
+      <c r="N33" s="10"/>
+      <c r="O33" s="5"/>
+      <c r="P33" s="5"/>
+      <c r="Q33" s="10"/>
+      <c r="R33" s="10"/>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="5"/>
@@ -5637,7 +7354,12 @@
       <c r="J34" s="10"/>
       <c r="K34" s="10"/>
       <c r="L34" s="10"/>
-      <c r="M34" s="5"/>
+      <c r="M34" s="10"/>
+      <c r="N34" s="10"/>
+      <c r="O34" s="5"/>
+      <c r="P34" s="5"/>
+      <c r="Q34" s="10"/>
+      <c r="R34" s="10"/>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="5"/>
@@ -5652,7 +7374,12 @@
       <c r="J35" s="10"/>
       <c r="K35" s="10"/>
       <c r="L35" s="10"/>
-      <c r="M35" s="5"/>
+      <c r="M35" s="10"/>
+      <c r="N35" s="10"/>
+      <c r="O35" s="5"/>
+      <c r="P35" s="5"/>
+      <c r="Q35" s="10"/>
+      <c r="R35" s="10"/>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="5"/>
@@ -5667,7 +7394,12 @@
       <c r="J36" s="10"/>
       <c r="K36" s="10"/>
       <c r="L36" s="10"/>
-      <c r="M36" s="5"/>
+      <c r="M36" s="10"/>
+      <c r="N36" s="10"/>
+      <c r="O36" s="5"/>
+      <c r="P36" s="5"/>
+      <c r="Q36" s="10"/>
+      <c r="R36" s="10"/>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="5"/>
@@ -5682,7 +7414,12 @@
       <c r="J37" s="10"/>
       <c r="K37" s="10"/>
       <c r="L37" s="10"/>
-      <c r="M37" s="5"/>
+      <c r="M37" s="10"/>
+      <c r="N37" s="10"/>
+      <c r="O37" s="5"/>
+      <c r="P37" s="5"/>
+      <c r="Q37" s="10"/>
+      <c r="R37" s="10"/>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="5"/>
@@ -5697,7 +7434,12 @@
       <c r="J38" s="10"/>
       <c r="K38" s="10"/>
       <c r="L38" s="10"/>
-      <c r="M38" s="5"/>
+      <c r="M38" s="10"/>
+      <c r="N38" s="10"/>
+      <c r="O38" s="5"/>
+      <c r="P38" s="5"/>
+      <c r="Q38" s="10"/>
+      <c r="R38" s="10"/>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="5"/>
@@ -5712,7 +7454,12 @@
       <c r="J39" s="10"/>
       <c r="K39" s="10"/>
       <c r="L39" s="10"/>
-      <c r="M39" s="5"/>
+      <c r="M39" s="10"/>
+      <c r="N39" s="10"/>
+      <c r="O39" s="5"/>
+      <c r="P39" s="5"/>
+      <c r="Q39" s="10"/>
+      <c r="R39" s="10"/>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="5"/>
@@ -5727,7 +7474,12 @@
       <c r="J40" s="10"/>
       <c r="K40" s="10"/>
       <c r="L40" s="10"/>
-      <c r="M40" s="5"/>
+      <c r="M40" s="10"/>
+      <c r="N40" s="10"/>
+      <c r="O40" s="5"/>
+      <c r="P40" s="5"/>
+      <c r="Q40" s="10"/>
+      <c r="R40" s="10"/>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="5"/>
@@ -5742,7 +7494,12 @@
       <c r="J41" s="10"/>
       <c r="K41" s="10"/>
       <c r="L41" s="10"/>
-      <c r="M41" s="5"/>
+      <c r="M41" s="10"/>
+      <c r="N41" s="10"/>
+      <c r="O41" s="5"/>
+      <c r="P41" s="5"/>
+      <c r="Q41" s="10"/>
+      <c r="R41" s="10"/>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="5"/>
@@ -5757,7 +7514,12 @@
       <c r="J42" s="10"/>
       <c r="K42" s="10"/>
       <c r="L42" s="10"/>
-      <c r="M42" s="5"/>
+      <c r="M42" s="10"/>
+      <c r="N42" s="10"/>
+      <c r="O42" s="5"/>
+      <c r="P42" s="5"/>
+      <c r="Q42" s="10"/>
+      <c r="R42" s="10"/>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="5"/>
@@ -5772,7 +7534,12 @@
       <c r="J43" s="10"/>
       <c r="K43" s="10"/>
       <c r="L43" s="10"/>
-      <c r="M43" s="5"/>
+      <c r="M43" s="10"/>
+      <c r="N43" s="10"/>
+      <c r="O43" s="5"/>
+      <c r="P43" s="5"/>
+      <c r="Q43" s="10"/>
+      <c r="R43" s="10"/>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="5"/>
@@ -5787,7 +7554,12 @@
       <c r="J44" s="10"/>
       <c r="K44" s="10"/>
       <c r="L44" s="10"/>
-      <c r="M44" s="5"/>
+      <c r="M44" s="10"/>
+      <c r="N44" s="10"/>
+      <c r="O44" s="5"/>
+      <c r="P44" s="5"/>
+      <c r="Q44" s="10"/>
+      <c r="R44" s="10"/>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="5"/>
@@ -5802,7 +7574,12 @@
       <c r="J45" s="10"/>
       <c r="K45" s="10"/>
       <c r="L45" s="10"/>
-      <c r="M45" s="5"/>
+      <c r="M45" s="10"/>
+      <c r="N45" s="10"/>
+      <c r="O45" s="5"/>
+      <c r="P45" s="5"/>
+      <c r="Q45" s="10"/>
+      <c r="R45" s="10"/>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="5"/>
@@ -5817,7 +7594,12 @@
       <c r="J46" s="10"/>
       <c r="K46" s="10"/>
       <c r="L46" s="10"/>
-      <c r="M46" s="5"/>
+      <c r="M46" s="10"/>
+      <c r="N46" s="10"/>
+      <c r="O46" s="5"/>
+      <c r="P46" s="5"/>
+      <c r="Q46" s="10"/>
+      <c r="R46" s="10"/>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="5"/>
@@ -5832,7 +7614,12 @@
       <c r="J47" s="10"/>
       <c r="K47" s="10"/>
       <c r="L47" s="10"/>
-      <c r="M47" s="5"/>
+      <c r="M47" s="10"/>
+      <c r="N47" s="10"/>
+      <c r="O47" s="5"/>
+      <c r="P47" s="5"/>
+      <c r="Q47" s="10"/>
+      <c r="R47" s="10"/>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="5"/>
@@ -5847,7 +7634,12 @@
       <c r="J48" s="10"/>
       <c r="K48" s="10"/>
       <c r="L48" s="10"/>
-      <c r="M48" s="5"/>
+      <c r="M48" s="10"/>
+      <c r="N48" s="10"/>
+      <c r="O48" s="5"/>
+      <c r="P48" s="5"/>
+      <c r="Q48" s="10"/>
+      <c r="R48" s="10"/>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="5"/>
@@ -5862,7 +7654,12 @@
       <c r="J49" s="10"/>
       <c r="K49" s="10"/>
       <c r="L49" s="10"/>
-      <c r="M49" s="5"/>
+      <c r="M49" s="10"/>
+      <c r="N49" s="10"/>
+      <c r="O49" s="5"/>
+      <c r="P49" s="5"/>
+      <c r="Q49" s="10"/>
+      <c r="R49" s="10"/>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="5"/>
@@ -5877,7 +7674,12 @@
       <c r="J50" s="10"/>
       <c r="K50" s="10"/>
       <c r="L50" s="10"/>
-      <c r="M50" s="5"/>
+      <c r="M50" s="10"/>
+      <c r="N50" s="10"/>
+      <c r="O50" s="5"/>
+      <c r="P50" s="5"/>
+      <c r="Q50" s="10"/>
+      <c r="R50" s="10"/>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="5"/>
@@ -5892,7 +7694,12 @@
       <c r="J51" s="10"/>
       <c r="K51" s="10"/>
       <c r="L51" s="10"/>
-      <c r="M51" s="5"/>
+      <c r="M51" s="10"/>
+      <c r="N51" s="10"/>
+      <c r="O51" s="5"/>
+      <c r="P51" s="5"/>
+      <c r="Q51" s="10"/>
+      <c r="R51" s="10"/>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="5"/>
@@ -5907,7 +7714,12 @@
       <c r="J52" s="10"/>
       <c r="K52" s="10"/>
       <c r="L52" s="10"/>
-      <c r="M52" s="5"/>
+      <c r="M52" s="10"/>
+      <c r="N52" s="10"/>
+      <c r="O52" s="5"/>
+      <c r="P52" s="5"/>
+      <c r="Q52" s="10"/>
+      <c r="R52" s="10"/>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="5"/>
@@ -5922,7 +7734,12 @@
       <c r="J53" s="10"/>
       <c r="K53" s="10"/>
       <c r="L53" s="10"/>
-      <c r="M53" s="5"/>
+      <c r="M53" s="10"/>
+      <c r="N53" s="10"/>
+      <c r="O53" s="5"/>
+      <c r="P53" s="5"/>
+      <c r="Q53" s="10"/>
+      <c r="R53" s="10"/>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="5"/>
@@ -5937,7 +7754,12 @@
       <c r="J54" s="10"/>
       <c r="K54" s="10"/>
       <c r="L54" s="10"/>
-      <c r="M54" s="5"/>
+      <c r="M54" s="10"/>
+      <c r="N54" s="10"/>
+      <c r="O54" s="5"/>
+      <c r="P54" s="5"/>
+      <c r="Q54" s="10"/>
+      <c r="R54" s="10"/>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="5"/>
@@ -5952,7 +7774,12 @@
       <c r="J55" s="10"/>
       <c r="K55" s="10"/>
       <c r="L55" s="10"/>
-      <c r="M55" s="5"/>
+      <c r="M55" s="10"/>
+      <c r="N55" s="10"/>
+      <c r="O55" s="5"/>
+      <c r="P55" s="5"/>
+      <c r="Q55" s="10"/>
+      <c r="R55" s="10"/>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="5"/>
@@ -5967,7 +7794,12 @@
       <c r="J56" s="10"/>
       <c r="K56" s="10"/>
       <c r="L56" s="10"/>
-      <c r="M56" s="5"/>
+      <c r="M56" s="10"/>
+      <c r="N56" s="10"/>
+      <c r="O56" s="5"/>
+      <c r="P56" s="5"/>
+      <c r="Q56" s="10"/>
+      <c r="R56" s="10"/>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="5"/>
@@ -5982,7 +7814,12 @@
       <c r="J57" s="10"/>
       <c r="K57" s="10"/>
       <c r="L57" s="10"/>
-      <c r="M57" s="5"/>
+      <c r="M57" s="10"/>
+      <c r="N57" s="10"/>
+      <c r="O57" s="5"/>
+      <c r="P57" s="5"/>
+      <c r="Q57" s="10"/>
+      <c r="R57" s="10"/>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="5"/>
@@ -5997,7 +7834,12 @@
       <c r="J58" s="10"/>
       <c r="K58" s="10"/>
       <c r="L58" s="10"/>
-      <c r="M58" s="5"/>
+      <c r="M58" s="10"/>
+      <c r="N58" s="10"/>
+      <c r="O58" s="5"/>
+      <c r="P58" s="5"/>
+      <c r="Q58" s="10"/>
+      <c r="R58" s="10"/>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="5"/>
@@ -6012,7 +7854,12 @@
       <c r="J59" s="10"/>
       <c r="K59" s="10"/>
       <c r="L59" s="10"/>
-      <c r="M59" s="5"/>
+      <c r="M59" s="10"/>
+      <c r="N59" s="10"/>
+      <c r="O59" s="5"/>
+      <c r="P59" s="5"/>
+      <c r="Q59" s="10"/>
+      <c r="R59" s="10"/>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="5"/>
@@ -6027,7 +7874,12 @@
       <c r="J60" s="10"/>
       <c r="K60" s="10"/>
       <c r="L60" s="10"/>
-      <c r="M60" s="5"/>
+      <c r="M60" s="10"/>
+      <c r="N60" s="10"/>
+      <c r="O60" s="5"/>
+      <c r="P60" s="5"/>
+      <c r="Q60" s="10"/>
+      <c r="R60" s="10"/>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="5"/>
@@ -6042,7 +7894,12 @@
       <c r="J61" s="10"/>
       <c r="K61" s="10"/>
       <c r="L61" s="10"/>
-      <c r="M61" s="5"/>
+      <c r="M61" s="10"/>
+      <c r="N61" s="10"/>
+      <c r="O61" s="5"/>
+      <c r="P61" s="5"/>
+      <c r="Q61" s="10"/>
+      <c r="R61" s="10"/>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="5"/>
@@ -6057,7 +7914,12 @@
       <c r="J62" s="10"/>
       <c r="K62" s="10"/>
       <c r="L62" s="10"/>
-      <c r="M62" s="5"/>
+      <c r="M62" s="10"/>
+      <c r="N62" s="10"/>
+      <c r="O62" s="5"/>
+      <c r="P62" s="5"/>
+      <c r="Q62" s="10"/>
+      <c r="R62" s="10"/>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="5"/>
@@ -6072,7 +7934,12 @@
       <c r="J63" s="10"/>
       <c r="K63" s="10"/>
       <c r="L63" s="10"/>
-      <c r="M63" s="5"/>
+      <c r="M63" s="10"/>
+      <c r="N63" s="10"/>
+      <c r="O63" s="5"/>
+      <c r="P63" s="5"/>
+      <c r="Q63" s="10"/>
+      <c r="R63" s="10"/>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="5"/>
@@ -6087,7 +7954,12 @@
       <c r="J64" s="10"/>
       <c r="K64" s="10"/>
       <c r="L64" s="10"/>
-      <c r="M64" s="5"/>
+      <c r="M64" s="10"/>
+      <c r="N64" s="10"/>
+      <c r="O64" s="5"/>
+      <c r="P64" s="5"/>
+      <c r="Q64" s="10"/>
+      <c r="R64" s="10"/>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="5"/>
@@ -6102,7 +7974,12 @@
       <c r="J65" s="10"/>
       <c r="K65" s="10"/>
       <c r="L65" s="10"/>
-      <c r="M65" s="5"/>
+      <c r="M65" s="10"/>
+      <c r="N65" s="10"/>
+      <c r="O65" s="5"/>
+      <c r="P65" s="5"/>
+      <c r="Q65" s="10"/>
+      <c r="R65" s="10"/>
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="5"/>
@@ -6117,7 +7994,12 @@
       <c r="J66" s="10"/>
       <c r="K66" s="10"/>
       <c r="L66" s="10"/>
-      <c r="M66" s="5"/>
+      <c r="M66" s="10"/>
+      <c r="N66" s="10"/>
+      <c r="O66" s="5"/>
+      <c r="P66" s="5"/>
+      <c r="Q66" s="10"/>
+      <c r="R66" s="10"/>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="5"/>
@@ -6132,7 +8014,12 @@
       <c r="J67" s="10"/>
       <c r="K67" s="10"/>
       <c r="L67" s="10"/>
-      <c r="M67" s="5"/>
+      <c r="M67" s="10"/>
+      <c r="N67" s="10"/>
+      <c r="O67" s="5"/>
+      <c r="P67" s="5"/>
+      <c r="Q67" s="10"/>
+      <c r="R67" s="10"/>
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="5"/>
@@ -6147,7 +8034,12 @@
       <c r="J68" s="10"/>
       <c r="K68" s="10"/>
       <c r="L68" s="10"/>
-      <c r="M68" s="5"/>
+      <c r="M68" s="10"/>
+      <c r="N68" s="10"/>
+      <c r="O68" s="5"/>
+      <c r="P68" s="5"/>
+      <c r="Q68" s="10"/>
+      <c r="R68" s="10"/>
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="5"/>
@@ -6162,7 +8054,12 @@
       <c r="J69" s="10"/>
       <c r="K69" s="10"/>
       <c r="L69" s="10"/>
-      <c r="M69" s="5"/>
+      <c r="M69" s="10"/>
+      <c r="N69" s="10"/>
+      <c r="O69" s="5"/>
+      <c r="P69" s="5"/>
+      <c r="Q69" s="10"/>
+      <c r="R69" s="10"/>
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="5"/>
@@ -6177,7 +8074,12 @@
       <c r="J70" s="10"/>
       <c r="K70" s="10"/>
       <c r="L70" s="10"/>
-      <c r="M70" s="5"/>
+      <c r="M70" s="10"/>
+      <c r="N70" s="10"/>
+      <c r="O70" s="5"/>
+      <c r="P70" s="5"/>
+      <c r="Q70" s="10"/>
+      <c r="R70" s="10"/>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="5"/>
@@ -6192,7 +8094,12 @@
       <c r="J71" s="10"/>
       <c r="K71" s="10"/>
       <c r="L71" s="10"/>
-      <c r="M71" s="5"/>
+      <c r="M71" s="10"/>
+      <c r="N71" s="10"/>
+      <c r="O71" s="5"/>
+      <c r="P71" s="5"/>
+      <c r="Q71" s="10"/>
+      <c r="R71" s="10"/>
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="5"/>
@@ -6207,7 +8114,12 @@
       <c r="J72" s="10"/>
       <c r="K72" s="10"/>
       <c r="L72" s="10"/>
-      <c r="M72" s="5"/>
+      <c r="M72" s="10"/>
+      <c r="N72" s="10"/>
+      <c r="O72" s="5"/>
+      <c r="P72" s="5"/>
+      <c r="Q72" s="10"/>
+      <c r="R72" s="10"/>
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="5"/>
@@ -6222,7 +8134,12 @@
       <c r="J73" s="10"/>
       <c r="K73" s="10"/>
       <c r="L73" s="10"/>
-      <c r="M73" s="5"/>
+      <c r="M73" s="10"/>
+      <c r="N73" s="10"/>
+      <c r="O73" s="5"/>
+      <c r="P73" s="5"/>
+      <c r="Q73" s="10"/>
+      <c r="R73" s="10"/>
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="5"/>
@@ -6237,7 +8154,12 @@
       <c r="J74" s="10"/>
       <c r="K74" s="10"/>
       <c r="L74" s="10"/>
-      <c r="M74" s="5"/>
+      <c r="M74" s="10"/>
+      <c r="N74" s="10"/>
+      <c r="O74" s="5"/>
+      <c r="P74" s="5"/>
+      <c r="Q74" s="10"/>
+      <c r="R74" s="10"/>
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="5"/>
@@ -6252,7 +8174,12 @@
       <c r="J75" s="10"/>
       <c r="K75" s="10"/>
       <c r="L75" s="10"/>
-      <c r="M75" s="5"/>
+      <c r="M75" s="10"/>
+      <c r="N75" s="10"/>
+      <c r="O75" s="5"/>
+      <c r="P75" s="5"/>
+      <c r="Q75" s="10"/>
+      <c r="R75" s="10"/>
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="5"/>
@@ -6267,7 +8194,12 @@
       <c r="J76" s="10"/>
       <c r="K76" s="10"/>
       <c r="L76" s="10"/>
-      <c r="M76" s="5"/>
+      <c r="M76" s="10"/>
+      <c r="N76" s="10"/>
+      <c r="O76" s="5"/>
+      <c r="P76" s="5"/>
+      <c r="Q76" s="10"/>
+      <c r="R76" s="10"/>
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="5"/>
@@ -6282,7 +8214,12 @@
       <c r="J77" s="10"/>
       <c r="K77" s="10"/>
       <c r="L77" s="10"/>
-      <c r="M77" s="5"/>
+      <c r="M77" s="10"/>
+      <c r="N77" s="10"/>
+      <c r="O77" s="5"/>
+      <c r="P77" s="5"/>
+      <c r="Q77" s="10"/>
+      <c r="R77" s="10"/>
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="5"/>
@@ -6297,7 +8234,12 @@
       <c r="J78" s="10"/>
       <c r="K78" s="10"/>
       <c r="L78" s="10"/>
-      <c r="M78" s="5"/>
+      <c r="M78" s="10"/>
+      <c r="N78" s="10"/>
+      <c r="O78" s="5"/>
+      <c r="P78" s="5"/>
+      <c r="Q78" s="10"/>
+      <c r="R78" s="10"/>
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="5"/>
@@ -6312,7 +8254,12 @@
       <c r="J79" s="10"/>
       <c r="K79" s="10"/>
       <c r="L79" s="10"/>
-      <c r="M79" s="5"/>
+      <c r="M79" s="10"/>
+      <c r="N79" s="10"/>
+      <c r="O79" s="5"/>
+      <c r="P79" s="5"/>
+      <c r="Q79" s="10"/>
+      <c r="R79" s="10"/>
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="5"/>
@@ -6327,7 +8274,12 @@
       <c r="J80" s="10"/>
       <c r="K80" s="10"/>
       <c r="L80" s="10"/>
-      <c r="M80" s="5"/>
+      <c r="M80" s="10"/>
+      <c r="N80" s="10"/>
+      <c r="O80" s="5"/>
+      <c r="P80" s="5"/>
+      <c r="Q80" s="10"/>
+      <c r="R80" s="10"/>
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="5"/>
@@ -6342,7 +8294,12 @@
       <c r="J81" s="10"/>
       <c r="K81" s="10"/>
       <c r="L81" s="10"/>
-      <c r="M81" s="5"/>
+      <c r="M81" s="10"/>
+      <c r="N81" s="10"/>
+      <c r="O81" s="5"/>
+      <c r="P81" s="5"/>
+      <c r="Q81" s="10"/>
+      <c r="R81" s="10"/>
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="5"/>
@@ -6357,7 +8314,12 @@
       <c r="J82" s="10"/>
       <c r="K82" s="10"/>
       <c r="L82" s="10"/>
-      <c r="M82" s="5"/>
+      <c r="M82" s="10"/>
+      <c r="N82" s="10"/>
+      <c r="O82" s="5"/>
+      <c r="P82" s="5"/>
+      <c r="Q82" s="10"/>
+      <c r="R82" s="10"/>
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="5"/>
@@ -6372,7 +8334,12 @@
       <c r="J83" s="10"/>
       <c r="K83" s="10"/>
       <c r="L83" s="10"/>
-      <c r="M83" s="5"/>
+      <c r="M83" s="10"/>
+      <c r="N83" s="10"/>
+      <c r="O83" s="5"/>
+      <c r="P83" s="5"/>
+      <c r="Q83" s="10"/>
+      <c r="R83" s="10"/>
     </row>
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="5"/>
@@ -6387,10 +8354,15 @@
       <c r="J84" s="10"/>
       <c r="K84" s="10"/>
       <c r="L84" s="10"/>
-      <c r="M84" s="5"/>
+      <c r="M84" s="10"/>
+      <c r="N84" s="10"/>
+      <c r="O84" s="5"/>
+      <c r="P84" s="5"/>
+      <c r="Q84" s="10"/>
+      <c r="R84" s="10"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A5:M84">
+  <conditionalFormatting sqref="A5:R84">
     <cfRule type="expression" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
       <formula>$A5&lt;&gt;""</formula>
     </cfRule>
@@ -6400,7 +8372,7 @@
       <formula>$C5="P. Principal"</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="8">
+  <dataValidations count="12">
     <dataValidation allowBlank="true" error="Solo un número de 1 a 20." errorStyle="stop" errorTitle="Series" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="E5:E84" type="whole">
       <formula1>1</formula1>
       <formula2>20</formula2>
@@ -6425,12 +8397,28 @@
       <formula1>"Sí"</formula1>
       <formula2>0</formula2>
     </dataValidation>
+    <dataValidation allowBlank="true" error="Minutos del aeróbico (0,5 = 30 s)." errorStyle="stop" errorTitle="Minutos" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="M5:M84" type="decimal">
+      <formula1>0</formula1>
+      <formula2>600</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Un número de 0 a 10." errorStyle="stop" errorTitle="RPE pre" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="Q5:Q84" type="decimal">
+      <formula1>0</formula1>
+      <formula2>10</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Un número de 0 a 10." errorStyle="stop" errorTitle="RPE post" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="R5:R84" type="decimal">
+      <formula1>0</formula1>
+      <formula2>10</formula2>
+    </dataValidation>
     <dataValidation allowBlank="true" error="Elige un día del desplegable (Lunes … Domingo)." errorStyle="stop" errorTitle="Día" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="A5:A84" type="list">
       <formula1>"Lunes,Martes,Miércoles,Jueves,Viernes,Sábado,Domingo"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Elige un bloque del desplegable." errorStyle="stop" errorTitle="Bloque" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C5:C84" type="list">
-      <formula1>"Activación,P. Principal,Accesorios,Vuelta a la calma"</formula1>
+      <formula1>"Activación,P. Principal,Aeróbico,Accesorios,Vuelta a la calma"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Elige una zona del desplegable." errorStyle="stop" errorTitle="Zona" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="N5:N84" type="list">
+      <formula1>"Z1,Z2,Z3,Z4,Z5"</formula1>
       <formula2>0</formula2>
     </dataValidation>
   </dataValidations>
@@ -6449,7 +8437,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:M84"/>
+  <dimension ref="A1:R84"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="15"/>
@@ -6461,12 +8449,16 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="8" style="0" width="9"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="7"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="11" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="0" width="7"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="0" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="0" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="17" style="0" width="8"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="6" t="s">
-        <v>42</v>
+        <v>54</v>
       </c>
       <c r="B1" s="11" t="n">
         <f aca="false">'Semana 4'!B1+7</f>
@@ -6479,49 +8471,64 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="8" t="s">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="B2" s="9"/>
     </row>
     <row r="4" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="I4" s="4" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="J4" s="4" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="K4" s="4" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="L4" s="4" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="M4" s="4" t="s">
-        <v>26</v>
+        <v>28</v>
+      </c>
+      <c r="N4" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="O4" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="P4" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q4" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="R4" s="4" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6537,7 +8544,12 @@
       <c r="J5" s="10"/>
       <c r="K5" s="10"/>
       <c r="L5" s="10"/>
-      <c r="M5" s="5"/>
+      <c r="M5" s="10"/>
+      <c r="N5" s="10"/>
+      <c r="O5" s="5"/>
+      <c r="P5" s="5"/>
+      <c r="Q5" s="10"/>
+      <c r="R5" s="10"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="5"/>
@@ -6552,7 +8564,12 @@
       <c r="J6" s="10"/>
       <c r="K6" s="10"/>
       <c r="L6" s="10"/>
-      <c r="M6" s="5"/>
+      <c r="M6" s="10"/>
+      <c r="N6" s="10"/>
+      <c r="O6" s="5"/>
+      <c r="P6" s="5"/>
+      <c r="Q6" s="10"/>
+      <c r="R6" s="10"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="5"/>
@@ -6567,7 +8584,12 @@
       <c r="J7" s="10"/>
       <c r="K7" s="10"/>
       <c r="L7" s="10"/>
-      <c r="M7" s="5"/>
+      <c r="M7" s="10"/>
+      <c r="N7" s="10"/>
+      <c r="O7" s="5"/>
+      <c r="P7" s="5"/>
+      <c r="Q7" s="10"/>
+      <c r="R7" s="10"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="5"/>
@@ -6582,7 +8604,12 @@
       <c r="J8" s="10"/>
       <c r="K8" s="10"/>
       <c r="L8" s="10"/>
-      <c r="M8" s="5"/>
+      <c r="M8" s="10"/>
+      <c r="N8" s="10"/>
+      <c r="O8" s="5"/>
+      <c r="P8" s="5"/>
+      <c r="Q8" s="10"/>
+      <c r="R8" s="10"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="5"/>
@@ -6597,7 +8624,12 @@
       <c r="J9" s="10"/>
       <c r="K9" s="10"/>
       <c r="L9" s="10"/>
-      <c r="M9" s="5"/>
+      <c r="M9" s="10"/>
+      <c r="N9" s="10"/>
+      <c r="O9" s="5"/>
+      <c r="P9" s="5"/>
+      <c r="Q9" s="10"/>
+      <c r="R9" s="10"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="5"/>
@@ -6612,7 +8644,12 @@
       <c r="J10" s="10"/>
       <c r="K10" s="10"/>
       <c r="L10" s="10"/>
-      <c r="M10" s="5"/>
+      <c r="M10" s="10"/>
+      <c r="N10" s="10"/>
+      <c r="O10" s="5"/>
+      <c r="P10" s="5"/>
+      <c r="Q10" s="10"/>
+      <c r="R10" s="10"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="5"/>
@@ -6627,7 +8664,12 @@
       <c r="J11" s="10"/>
       <c r="K11" s="10"/>
       <c r="L11" s="10"/>
-      <c r="M11" s="5"/>
+      <c r="M11" s="10"/>
+      <c r="N11" s="10"/>
+      <c r="O11" s="5"/>
+      <c r="P11" s="5"/>
+      <c r="Q11" s="10"/>
+      <c r="R11" s="10"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="5"/>
@@ -6642,7 +8684,12 @@
       <c r="J12" s="10"/>
       <c r="K12" s="10"/>
       <c r="L12" s="10"/>
-      <c r="M12" s="5"/>
+      <c r="M12" s="10"/>
+      <c r="N12" s="10"/>
+      <c r="O12" s="5"/>
+      <c r="P12" s="5"/>
+      <c r="Q12" s="10"/>
+      <c r="R12" s="10"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="5"/>
@@ -6657,7 +8704,12 @@
       <c r="J13" s="10"/>
       <c r="K13" s="10"/>
       <c r="L13" s="10"/>
-      <c r="M13" s="5"/>
+      <c r="M13" s="10"/>
+      <c r="N13" s="10"/>
+      <c r="O13" s="5"/>
+      <c r="P13" s="5"/>
+      <c r="Q13" s="10"/>
+      <c r="R13" s="10"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="5"/>
@@ -6672,7 +8724,12 @@
       <c r="J14" s="10"/>
       <c r="K14" s="10"/>
       <c r="L14" s="10"/>
-      <c r="M14" s="5"/>
+      <c r="M14" s="10"/>
+      <c r="N14" s="10"/>
+      <c r="O14" s="5"/>
+      <c r="P14" s="5"/>
+      <c r="Q14" s="10"/>
+      <c r="R14" s="10"/>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="5"/>
@@ -6687,7 +8744,12 @@
       <c r="J15" s="10"/>
       <c r="K15" s="10"/>
       <c r="L15" s="10"/>
-      <c r="M15" s="5"/>
+      <c r="M15" s="10"/>
+      <c r="N15" s="10"/>
+      <c r="O15" s="5"/>
+      <c r="P15" s="5"/>
+      <c r="Q15" s="10"/>
+      <c r="R15" s="10"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="5"/>
@@ -6702,7 +8764,12 @@
       <c r="J16" s="10"/>
       <c r="K16" s="10"/>
       <c r="L16" s="10"/>
-      <c r="M16" s="5"/>
+      <c r="M16" s="10"/>
+      <c r="N16" s="10"/>
+      <c r="O16" s="5"/>
+      <c r="P16" s="5"/>
+      <c r="Q16" s="10"/>
+      <c r="R16" s="10"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="5"/>
@@ -6717,7 +8784,12 @@
       <c r="J17" s="10"/>
       <c r="K17" s="10"/>
       <c r="L17" s="10"/>
-      <c r="M17" s="5"/>
+      <c r="M17" s="10"/>
+      <c r="N17" s="10"/>
+      <c r="O17" s="5"/>
+      <c r="P17" s="5"/>
+      <c r="Q17" s="10"/>
+      <c r="R17" s="10"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="5"/>
@@ -6732,7 +8804,12 @@
       <c r="J18" s="10"/>
       <c r="K18" s="10"/>
       <c r="L18" s="10"/>
-      <c r="M18" s="5"/>
+      <c r="M18" s="10"/>
+      <c r="N18" s="10"/>
+      <c r="O18" s="5"/>
+      <c r="P18" s="5"/>
+      <c r="Q18" s="10"/>
+      <c r="R18" s="10"/>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="5"/>
@@ -6747,7 +8824,12 @@
       <c r="J19" s="10"/>
       <c r="K19" s="10"/>
       <c r="L19" s="10"/>
-      <c r="M19" s="5"/>
+      <c r="M19" s="10"/>
+      <c r="N19" s="10"/>
+      <c r="O19" s="5"/>
+      <c r="P19" s="5"/>
+      <c r="Q19" s="10"/>
+      <c r="R19" s="10"/>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="5"/>
@@ -6762,7 +8844,12 @@
       <c r="J20" s="10"/>
       <c r="K20" s="10"/>
       <c r="L20" s="10"/>
-      <c r="M20" s="5"/>
+      <c r="M20" s="10"/>
+      <c r="N20" s="10"/>
+      <c r="O20" s="5"/>
+      <c r="P20" s="5"/>
+      <c r="Q20" s="10"/>
+      <c r="R20" s="10"/>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="5"/>
@@ -6777,7 +8864,12 @@
       <c r="J21" s="10"/>
       <c r="K21" s="10"/>
       <c r="L21" s="10"/>
-      <c r="M21" s="5"/>
+      <c r="M21" s="10"/>
+      <c r="N21" s="10"/>
+      <c r="O21" s="5"/>
+      <c r="P21" s="5"/>
+      <c r="Q21" s="10"/>
+      <c r="R21" s="10"/>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="5"/>
@@ -6792,7 +8884,12 @@
       <c r="J22" s="10"/>
       <c r="K22" s="10"/>
       <c r="L22" s="10"/>
-      <c r="M22" s="5"/>
+      <c r="M22" s="10"/>
+      <c r="N22" s="10"/>
+      <c r="O22" s="5"/>
+      <c r="P22" s="5"/>
+      <c r="Q22" s="10"/>
+      <c r="R22" s="10"/>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="5"/>
@@ -6807,7 +8904,12 @@
       <c r="J23" s="10"/>
       <c r="K23" s="10"/>
       <c r="L23" s="10"/>
-      <c r="M23" s="5"/>
+      <c r="M23" s="10"/>
+      <c r="N23" s="10"/>
+      <c r="O23" s="5"/>
+      <c r="P23" s="5"/>
+      <c r="Q23" s="10"/>
+      <c r="R23" s="10"/>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="5"/>
@@ -6822,7 +8924,12 @@
       <c r="J24" s="10"/>
       <c r="K24" s="10"/>
       <c r="L24" s="10"/>
-      <c r="M24" s="5"/>
+      <c r="M24" s="10"/>
+      <c r="N24" s="10"/>
+      <c r="O24" s="5"/>
+      <c r="P24" s="5"/>
+      <c r="Q24" s="10"/>
+      <c r="R24" s="10"/>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="5"/>
@@ -6837,7 +8944,12 @@
       <c r="J25" s="10"/>
       <c r="K25" s="10"/>
       <c r="L25" s="10"/>
-      <c r="M25" s="5"/>
+      <c r="M25" s="10"/>
+      <c r="N25" s="10"/>
+      <c r="O25" s="5"/>
+      <c r="P25" s="5"/>
+      <c r="Q25" s="10"/>
+      <c r="R25" s="10"/>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="5"/>
@@ -6852,7 +8964,12 @@
       <c r="J26" s="10"/>
       <c r="K26" s="10"/>
       <c r="L26" s="10"/>
-      <c r="M26" s="5"/>
+      <c r="M26" s="10"/>
+      <c r="N26" s="10"/>
+      <c r="O26" s="5"/>
+      <c r="P26" s="5"/>
+      <c r="Q26" s="10"/>
+      <c r="R26" s="10"/>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="5"/>
@@ -6867,7 +8984,12 @@
       <c r="J27" s="10"/>
       <c r="K27" s="10"/>
       <c r="L27" s="10"/>
-      <c r="M27" s="5"/>
+      <c r="M27" s="10"/>
+      <c r="N27" s="10"/>
+      <c r="O27" s="5"/>
+      <c r="P27" s="5"/>
+      <c r="Q27" s="10"/>
+      <c r="R27" s="10"/>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="5"/>
@@ -6882,7 +9004,12 @@
       <c r="J28" s="10"/>
       <c r="K28" s="10"/>
       <c r="L28" s="10"/>
-      <c r="M28" s="5"/>
+      <c r="M28" s="10"/>
+      <c r="N28" s="10"/>
+      <c r="O28" s="5"/>
+      <c r="P28" s="5"/>
+      <c r="Q28" s="10"/>
+      <c r="R28" s="10"/>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="5"/>
@@ -6897,7 +9024,12 @@
       <c r="J29" s="10"/>
       <c r="K29" s="10"/>
       <c r="L29" s="10"/>
-      <c r="M29" s="5"/>
+      <c r="M29" s="10"/>
+      <c r="N29" s="10"/>
+      <c r="O29" s="5"/>
+      <c r="P29" s="5"/>
+      <c r="Q29" s="10"/>
+      <c r="R29" s="10"/>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="5"/>
@@ -6912,7 +9044,12 @@
       <c r="J30" s="10"/>
       <c r="K30" s="10"/>
       <c r="L30" s="10"/>
-      <c r="M30" s="5"/>
+      <c r="M30" s="10"/>
+      <c r="N30" s="10"/>
+      <c r="O30" s="5"/>
+      <c r="P30" s="5"/>
+      <c r="Q30" s="10"/>
+      <c r="R30" s="10"/>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="5"/>
@@ -6927,7 +9064,12 @@
       <c r="J31" s="10"/>
       <c r="K31" s="10"/>
       <c r="L31" s="10"/>
-      <c r="M31" s="5"/>
+      <c r="M31" s="10"/>
+      <c r="N31" s="10"/>
+      <c r="O31" s="5"/>
+      <c r="P31" s="5"/>
+      <c r="Q31" s="10"/>
+      <c r="R31" s="10"/>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="5"/>
@@ -6942,7 +9084,12 @@
       <c r="J32" s="10"/>
       <c r="K32" s="10"/>
       <c r="L32" s="10"/>
-      <c r="M32" s="5"/>
+      <c r="M32" s="10"/>
+      <c r="N32" s="10"/>
+      <c r="O32" s="5"/>
+      <c r="P32" s="5"/>
+      <c r="Q32" s="10"/>
+      <c r="R32" s="10"/>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="5"/>
@@ -6957,7 +9104,12 @@
       <c r="J33" s="10"/>
       <c r="K33" s="10"/>
       <c r="L33" s="10"/>
-      <c r="M33" s="5"/>
+      <c r="M33" s="10"/>
+      <c r="N33" s="10"/>
+      <c r="O33" s="5"/>
+      <c r="P33" s="5"/>
+      <c r="Q33" s="10"/>
+      <c r="R33" s="10"/>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="5"/>
@@ -6972,7 +9124,12 @@
       <c r="J34" s="10"/>
       <c r="K34" s="10"/>
       <c r="L34" s="10"/>
-      <c r="M34" s="5"/>
+      <c r="M34" s="10"/>
+      <c r="N34" s="10"/>
+      <c r="O34" s="5"/>
+      <c r="P34" s="5"/>
+      <c r="Q34" s="10"/>
+      <c r="R34" s="10"/>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="5"/>
@@ -6987,7 +9144,12 @@
       <c r="J35" s="10"/>
       <c r="K35" s="10"/>
       <c r="L35" s="10"/>
-      <c r="M35" s="5"/>
+      <c r="M35" s="10"/>
+      <c r="N35" s="10"/>
+      <c r="O35" s="5"/>
+      <c r="P35" s="5"/>
+      <c r="Q35" s="10"/>
+      <c r="R35" s="10"/>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="5"/>
@@ -7002,7 +9164,12 @@
       <c r="J36" s="10"/>
       <c r="K36" s="10"/>
       <c r="L36" s="10"/>
-      <c r="M36" s="5"/>
+      <c r="M36" s="10"/>
+      <c r="N36" s="10"/>
+      <c r="O36" s="5"/>
+      <c r="P36" s="5"/>
+      <c r="Q36" s="10"/>
+      <c r="R36" s="10"/>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="5"/>
@@ -7017,7 +9184,12 @@
       <c r="J37" s="10"/>
       <c r="K37" s="10"/>
       <c r="L37" s="10"/>
-      <c r="M37" s="5"/>
+      <c r="M37" s="10"/>
+      <c r="N37" s="10"/>
+      <c r="O37" s="5"/>
+      <c r="P37" s="5"/>
+      <c r="Q37" s="10"/>
+      <c r="R37" s="10"/>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="5"/>
@@ -7032,7 +9204,12 @@
       <c r="J38" s="10"/>
       <c r="K38" s="10"/>
       <c r="L38" s="10"/>
-      <c r="M38" s="5"/>
+      <c r="M38" s="10"/>
+      <c r="N38" s="10"/>
+      <c r="O38" s="5"/>
+      <c r="P38" s="5"/>
+      <c r="Q38" s="10"/>
+      <c r="R38" s="10"/>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="5"/>
@@ -7047,7 +9224,12 @@
       <c r="J39" s="10"/>
       <c r="K39" s="10"/>
       <c r="L39" s="10"/>
-      <c r="M39" s="5"/>
+      <c r="M39" s="10"/>
+      <c r="N39" s="10"/>
+      <c r="O39" s="5"/>
+      <c r="P39" s="5"/>
+      <c r="Q39" s="10"/>
+      <c r="R39" s="10"/>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="5"/>
@@ -7062,7 +9244,12 @@
       <c r="J40" s="10"/>
       <c r="K40" s="10"/>
       <c r="L40" s="10"/>
-      <c r="M40" s="5"/>
+      <c r="M40" s="10"/>
+      <c r="N40" s="10"/>
+      <c r="O40" s="5"/>
+      <c r="P40" s="5"/>
+      <c r="Q40" s="10"/>
+      <c r="R40" s="10"/>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="5"/>
@@ -7077,7 +9264,12 @@
       <c r="J41" s="10"/>
       <c r="K41" s="10"/>
       <c r="L41" s="10"/>
-      <c r="M41" s="5"/>
+      <c r="M41" s="10"/>
+      <c r="N41" s="10"/>
+      <c r="O41" s="5"/>
+      <c r="P41" s="5"/>
+      <c r="Q41" s="10"/>
+      <c r="R41" s="10"/>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="5"/>
@@ -7092,7 +9284,12 @@
       <c r="J42" s="10"/>
       <c r="K42" s="10"/>
       <c r="L42" s="10"/>
-      <c r="M42" s="5"/>
+      <c r="M42" s="10"/>
+      <c r="N42" s="10"/>
+      <c r="O42" s="5"/>
+      <c r="P42" s="5"/>
+      <c r="Q42" s="10"/>
+      <c r="R42" s="10"/>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="5"/>
@@ -7107,7 +9304,12 @@
       <c r="J43" s="10"/>
       <c r="K43" s="10"/>
       <c r="L43" s="10"/>
-      <c r="M43" s="5"/>
+      <c r="M43" s="10"/>
+      <c r="N43" s="10"/>
+      <c r="O43" s="5"/>
+      <c r="P43" s="5"/>
+      <c r="Q43" s="10"/>
+      <c r="R43" s="10"/>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="5"/>
@@ -7122,7 +9324,12 @@
       <c r="J44" s="10"/>
       <c r="K44" s="10"/>
       <c r="L44" s="10"/>
-      <c r="M44" s="5"/>
+      <c r="M44" s="10"/>
+      <c r="N44" s="10"/>
+      <c r="O44" s="5"/>
+      <c r="P44" s="5"/>
+      <c r="Q44" s="10"/>
+      <c r="R44" s="10"/>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="5"/>
@@ -7137,7 +9344,12 @@
       <c r="J45" s="10"/>
       <c r="K45" s="10"/>
       <c r="L45" s="10"/>
-      <c r="M45" s="5"/>
+      <c r="M45" s="10"/>
+      <c r="N45" s="10"/>
+      <c r="O45" s="5"/>
+      <c r="P45" s="5"/>
+      <c r="Q45" s="10"/>
+      <c r="R45" s="10"/>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="5"/>
@@ -7152,7 +9364,12 @@
       <c r="J46" s="10"/>
       <c r="K46" s="10"/>
       <c r="L46" s="10"/>
-      <c r="M46" s="5"/>
+      <c r="M46" s="10"/>
+      <c r="N46" s="10"/>
+      <c r="O46" s="5"/>
+      <c r="P46" s="5"/>
+      <c r="Q46" s="10"/>
+      <c r="R46" s="10"/>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="5"/>
@@ -7167,7 +9384,12 @@
       <c r="J47" s="10"/>
       <c r="K47" s="10"/>
       <c r="L47" s="10"/>
-      <c r="M47" s="5"/>
+      <c r="M47" s="10"/>
+      <c r="N47" s="10"/>
+      <c r="O47" s="5"/>
+      <c r="P47" s="5"/>
+      <c r="Q47" s="10"/>
+      <c r="R47" s="10"/>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="5"/>
@@ -7182,7 +9404,12 @@
       <c r="J48" s="10"/>
       <c r="K48" s="10"/>
       <c r="L48" s="10"/>
-      <c r="M48" s="5"/>
+      <c r="M48" s="10"/>
+      <c r="N48" s="10"/>
+      <c r="O48" s="5"/>
+      <c r="P48" s="5"/>
+      <c r="Q48" s="10"/>
+      <c r="R48" s="10"/>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="5"/>
@@ -7197,7 +9424,12 @@
       <c r="J49" s="10"/>
       <c r="K49" s="10"/>
       <c r="L49" s="10"/>
-      <c r="M49" s="5"/>
+      <c r="M49" s="10"/>
+      <c r="N49" s="10"/>
+      <c r="O49" s="5"/>
+      <c r="P49" s="5"/>
+      <c r="Q49" s="10"/>
+      <c r="R49" s="10"/>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="5"/>
@@ -7212,7 +9444,12 @@
       <c r="J50" s="10"/>
       <c r="K50" s="10"/>
       <c r="L50" s="10"/>
-      <c r="M50" s="5"/>
+      <c r="M50" s="10"/>
+      <c r="N50" s="10"/>
+      <c r="O50" s="5"/>
+      <c r="P50" s="5"/>
+      <c r="Q50" s="10"/>
+      <c r="R50" s="10"/>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="5"/>
@@ -7227,7 +9464,12 @@
       <c r="J51" s="10"/>
       <c r="K51" s="10"/>
       <c r="L51" s="10"/>
-      <c r="M51" s="5"/>
+      <c r="M51" s="10"/>
+      <c r="N51" s="10"/>
+      <c r="O51" s="5"/>
+      <c r="P51" s="5"/>
+      <c r="Q51" s="10"/>
+      <c r="R51" s="10"/>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="5"/>
@@ -7242,7 +9484,12 @@
       <c r="J52" s="10"/>
       <c r="K52" s="10"/>
       <c r="L52" s="10"/>
-      <c r="M52" s="5"/>
+      <c r="M52" s="10"/>
+      <c r="N52" s="10"/>
+      <c r="O52" s="5"/>
+      <c r="P52" s="5"/>
+      <c r="Q52" s="10"/>
+      <c r="R52" s="10"/>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="5"/>
@@ -7257,7 +9504,12 @@
       <c r="J53" s="10"/>
       <c r="K53" s="10"/>
       <c r="L53" s="10"/>
-      <c r="M53" s="5"/>
+      <c r="M53" s="10"/>
+      <c r="N53" s="10"/>
+      <c r="O53" s="5"/>
+      <c r="P53" s="5"/>
+      <c r="Q53" s="10"/>
+      <c r="R53" s="10"/>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="5"/>
@@ -7272,7 +9524,12 @@
       <c r="J54" s="10"/>
       <c r="K54" s="10"/>
       <c r="L54" s="10"/>
-      <c r="M54" s="5"/>
+      <c r="M54" s="10"/>
+      <c r="N54" s="10"/>
+      <c r="O54" s="5"/>
+      <c r="P54" s="5"/>
+      <c r="Q54" s="10"/>
+      <c r="R54" s="10"/>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="5"/>
@@ -7287,7 +9544,12 @@
       <c r="J55" s="10"/>
       <c r="K55" s="10"/>
       <c r="L55" s="10"/>
-      <c r="M55" s="5"/>
+      <c r="M55" s="10"/>
+      <c r="N55" s="10"/>
+      <c r="O55" s="5"/>
+      <c r="P55" s="5"/>
+      <c r="Q55" s="10"/>
+      <c r="R55" s="10"/>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="5"/>
@@ -7302,7 +9564,12 @@
       <c r="J56" s="10"/>
       <c r="K56" s="10"/>
       <c r="L56" s="10"/>
-      <c r="M56" s="5"/>
+      <c r="M56" s="10"/>
+      <c r="N56" s="10"/>
+      <c r="O56" s="5"/>
+      <c r="P56" s="5"/>
+      <c r="Q56" s="10"/>
+      <c r="R56" s="10"/>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="5"/>
@@ -7317,7 +9584,12 @@
       <c r="J57" s="10"/>
       <c r="K57" s="10"/>
       <c r="L57" s="10"/>
-      <c r="M57" s="5"/>
+      <c r="M57" s="10"/>
+      <c r="N57" s="10"/>
+      <c r="O57" s="5"/>
+      <c r="P57" s="5"/>
+      <c r="Q57" s="10"/>
+      <c r="R57" s="10"/>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="5"/>
@@ -7332,7 +9604,12 @@
       <c r="J58" s="10"/>
       <c r="K58" s="10"/>
       <c r="L58" s="10"/>
-      <c r="M58" s="5"/>
+      <c r="M58" s="10"/>
+      <c r="N58" s="10"/>
+      <c r="O58" s="5"/>
+      <c r="P58" s="5"/>
+      <c r="Q58" s="10"/>
+      <c r="R58" s="10"/>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="5"/>
@@ -7347,7 +9624,12 @@
       <c r="J59" s="10"/>
       <c r="K59" s="10"/>
       <c r="L59" s="10"/>
-      <c r="M59" s="5"/>
+      <c r="M59" s="10"/>
+      <c r="N59" s="10"/>
+      <c r="O59" s="5"/>
+      <c r="P59" s="5"/>
+      <c r="Q59" s="10"/>
+      <c r="R59" s="10"/>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="5"/>
@@ -7362,7 +9644,12 @@
       <c r="J60" s="10"/>
       <c r="K60" s="10"/>
       <c r="L60" s="10"/>
-      <c r="M60" s="5"/>
+      <c r="M60" s="10"/>
+      <c r="N60" s="10"/>
+      <c r="O60" s="5"/>
+      <c r="P60" s="5"/>
+      <c r="Q60" s="10"/>
+      <c r="R60" s="10"/>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="5"/>
@@ -7377,7 +9664,12 @@
       <c r="J61" s="10"/>
       <c r="K61" s="10"/>
       <c r="L61" s="10"/>
-      <c r="M61" s="5"/>
+      <c r="M61" s="10"/>
+      <c r="N61" s="10"/>
+      <c r="O61" s="5"/>
+      <c r="P61" s="5"/>
+      <c r="Q61" s="10"/>
+      <c r="R61" s="10"/>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="5"/>
@@ -7392,7 +9684,12 @@
       <c r="J62" s="10"/>
       <c r="K62" s="10"/>
       <c r="L62" s="10"/>
-      <c r="M62" s="5"/>
+      <c r="M62" s="10"/>
+      <c r="N62" s="10"/>
+      <c r="O62" s="5"/>
+      <c r="P62" s="5"/>
+      <c r="Q62" s="10"/>
+      <c r="R62" s="10"/>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="5"/>
@@ -7407,7 +9704,12 @@
       <c r="J63" s="10"/>
       <c r="K63" s="10"/>
       <c r="L63" s="10"/>
-      <c r="M63" s="5"/>
+      <c r="M63" s="10"/>
+      <c r="N63" s="10"/>
+      <c r="O63" s="5"/>
+      <c r="P63" s="5"/>
+      <c r="Q63" s="10"/>
+      <c r="R63" s="10"/>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="5"/>
@@ -7422,7 +9724,12 @@
       <c r="J64" s="10"/>
       <c r="K64" s="10"/>
       <c r="L64" s="10"/>
-      <c r="M64" s="5"/>
+      <c r="M64" s="10"/>
+      <c r="N64" s="10"/>
+      <c r="O64" s="5"/>
+      <c r="P64" s="5"/>
+      <c r="Q64" s="10"/>
+      <c r="R64" s="10"/>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="5"/>
@@ -7437,7 +9744,12 @@
       <c r="J65" s="10"/>
       <c r="K65" s="10"/>
       <c r="L65" s="10"/>
-      <c r="M65" s="5"/>
+      <c r="M65" s="10"/>
+      <c r="N65" s="10"/>
+      <c r="O65" s="5"/>
+      <c r="P65" s="5"/>
+      <c r="Q65" s="10"/>
+      <c r="R65" s="10"/>
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="5"/>
@@ -7452,7 +9764,12 @@
       <c r="J66" s="10"/>
       <c r="K66" s="10"/>
       <c r="L66" s="10"/>
-      <c r="M66" s="5"/>
+      <c r="M66" s="10"/>
+      <c r="N66" s="10"/>
+      <c r="O66" s="5"/>
+      <c r="P66" s="5"/>
+      <c r="Q66" s="10"/>
+      <c r="R66" s="10"/>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="5"/>
@@ -7467,7 +9784,12 @@
       <c r="J67" s="10"/>
       <c r="K67" s="10"/>
       <c r="L67" s="10"/>
-      <c r="M67" s="5"/>
+      <c r="M67" s="10"/>
+      <c r="N67" s="10"/>
+      <c r="O67" s="5"/>
+      <c r="P67" s="5"/>
+      <c r="Q67" s="10"/>
+      <c r="R67" s="10"/>
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="5"/>
@@ -7482,7 +9804,12 @@
       <c r="J68" s="10"/>
       <c r="K68" s="10"/>
       <c r="L68" s="10"/>
-      <c r="M68" s="5"/>
+      <c r="M68" s="10"/>
+      <c r="N68" s="10"/>
+      <c r="O68" s="5"/>
+      <c r="P68" s="5"/>
+      <c r="Q68" s="10"/>
+      <c r="R68" s="10"/>
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="5"/>
@@ -7497,7 +9824,12 @@
       <c r="J69" s="10"/>
       <c r="K69" s="10"/>
       <c r="L69" s="10"/>
-      <c r="M69" s="5"/>
+      <c r="M69" s="10"/>
+      <c r="N69" s="10"/>
+      <c r="O69" s="5"/>
+      <c r="P69" s="5"/>
+      <c r="Q69" s="10"/>
+      <c r="R69" s="10"/>
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="5"/>
@@ -7512,7 +9844,12 @@
       <c r="J70" s="10"/>
       <c r="K70" s="10"/>
       <c r="L70" s="10"/>
-      <c r="M70" s="5"/>
+      <c r="M70" s="10"/>
+      <c r="N70" s="10"/>
+      <c r="O70" s="5"/>
+      <c r="P70" s="5"/>
+      <c r="Q70" s="10"/>
+      <c r="R70" s="10"/>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="5"/>
@@ -7527,7 +9864,12 @@
       <c r="J71" s="10"/>
       <c r="K71" s="10"/>
       <c r="L71" s="10"/>
-      <c r="M71" s="5"/>
+      <c r="M71" s="10"/>
+      <c r="N71" s="10"/>
+      <c r="O71" s="5"/>
+      <c r="P71" s="5"/>
+      <c r="Q71" s="10"/>
+      <c r="R71" s="10"/>
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="5"/>
@@ -7542,7 +9884,12 @@
       <c r="J72" s="10"/>
       <c r="K72" s="10"/>
       <c r="L72" s="10"/>
-      <c r="M72" s="5"/>
+      <c r="M72" s="10"/>
+      <c r="N72" s="10"/>
+      <c r="O72" s="5"/>
+      <c r="P72" s="5"/>
+      <c r="Q72" s="10"/>
+      <c r="R72" s="10"/>
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="5"/>
@@ -7557,7 +9904,12 @@
       <c r="J73" s="10"/>
       <c r="K73" s="10"/>
       <c r="L73" s="10"/>
-      <c r="M73" s="5"/>
+      <c r="M73" s="10"/>
+      <c r="N73" s="10"/>
+      <c r="O73" s="5"/>
+      <c r="P73" s="5"/>
+      <c r="Q73" s="10"/>
+      <c r="R73" s="10"/>
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="5"/>
@@ -7572,7 +9924,12 @@
       <c r="J74" s="10"/>
       <c r="K74" s="10"/>
       <c r="L74" s="10"/>
-      <c r="M74" s="5"/>
+      <c r="M74" s="10"/>
+      <c r="N74" s="10"/>
+      <c r="O74" s="5"/>
+      <c r="P74" s="5"/>
+      <c r="Q74" s="10"/>
+      <c r="R74" s="10"/>
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="5"/>
@@ -7587,7 +9944,12 @@
       <c r="J75" s="10"/>
       <c r="K75" s="10"/>
       <c r="L75" s="10"/>
-      <c r="M75" s="5"/>
+      <c r="M75" s="10"/>
+      <c r="N75" s="10"/>
+      <c r="O75" s="5"/>
+      <c r="P75" s="5"/>
+      <c r="Q75" s="10"/>
+      <c r="R75" s="10"/>
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="5"/>
@@ -7602,7 +9964,12 @@
       <c r="J76" s="10"/>
       <c r="K76" s="10"/>
       <c r="L76" s="10"/>
-      <c r="M76" s="5"/>
+      <c r="M76" s="10"/>
+      <c r="N76" s="10"/>
+      <c r="O76" s="5"/>
+      <c r="P76" s="5"/>
+      <c r="Q76" s="10"/>
+      <c r="R76" s="10"/>
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="5"/>
@@ -7617,7 +9984,12 @@
       <c r="J77" s="10"/>
       <c r="K77" s="10"/>
       <c r="L77" s="10"/>
-      <c r="M77" s="5"/>
+      <c r="M77" s="10"/>
+      <c r="N77" s="10"/>
+      <c r="O77" s="5"/>
+      <c r="P77" s="5"/>
+      <c r="Q77" s="10"/>
+      <c r="R77" s="10"/>
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="5"/>
@@ -7632,7 +10004,12 @@
       <c r="J78" s="10"/>
       <c r="K78" s="10"/>
       <c r="L78" s="10"/>
-      <c r="M78" s="5"/>
+      <c r="M78" s="10"/>
+      <c r="N78" s="10"/>
+      <c r="O78" s="5"/>
+      <c r="P78" s="5"/>
+      <c r="Q78" s="10"/>
+      <c r="R78" s="10"/>
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="5"/>
@@ -7647,7 +10024,12 @@
       <c r="J79" s="10"/>
       <c r="K79" s="10"/>
       <c r="L79" s="10"/>
-      <c r="M79" s="5"/>
+      <c r="M79" s="10"/>
+      <c r="N79" s="10"/>
+      <c r="O79" s="5"/>
+      <c r="P79" s="5"/>
+      <c r="Q79" s="10"/>
+      <c r="R79" s="10"/>
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="5"/>
@@ -7662,7 +10044,12 @@
       <c r="J80" s="10"/>
       <c r="K80" s="10"/>
       <c r="L80" s="10"/>
-      <c r="M80" s="5"/>
+      <c r="M80" s="10"/>
+      <c r="N80" s="10"/>
+      <c r="O80" s="5"/>
+      <c r="P80" s="5"/>
+      <c r="Q80" s="10"/>
+      <c r="R80" s="10"/>
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="5"/>
@@ -7677,7 +10064,12 @@
       <c r="J81" s="10"/>
       <c r="K81" s="10"/>
       <c r="L81" s="10"/>
-      <c r="M81" s="5"/>
+      <c r="M81" s="10"/>
+      <c r="N81" s="10"/>
+      <c r="O81" s="5"/>
+      <c r="P81" s="5"/>
+      <c r="Q81" s="10"/>
+      <c r="R81" s="10"/>
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="5"/>
@@ -7692,7 +10084,12 @@
       <c r="J82" s="10"/>
       <c r="K82" s="10"/>
       <c r="L82" s="10"/>
-      <c r="M82" s="5"/>
+      <c r="M82" s="10"/>
+      <c r="N82" s="10"/>
+      <c r="O82" s="5"/>
+      <c r="P82" s="5"/>
+      <c r="Q82" s="10"/>
+      <c r="R82" s="10"/>
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="5"/>
@@ -7707,7 +10104,12 @@
       <c r="J83" s="10"/>
       <c r="K83" s="10"/>
       <c r="L83" s="10"/>
-      <c r="M83" s="5"/>
+      <c r="M83" s="10"/>
+      <c r="N83" s="10"/>
+      <c r="O83" s="5"/>
+      <c r="P83" s="5"/>
+      <c r="Q83" s="10"/>
+      <c r="R83" s="10"/>
     </row>
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="5"/>
@@ -7722,10 +10124,15 @@
       <c r="J84" s="10"/>
       <c r="K84" s="10"/>
       <c r="L84" s="10"/>
-      <c r="M84" s="5"/>
+      <c r="M84" s="10"/>
+      <c r="N84" s="10"/>
+      <c r="O84" s="5"/>
+      <c r="P84" s="5"/>
+      <c r="Q84" s="10"/>
+      <c r="R84" s="10"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A5:M84">
+  <conditionalFormatting sqref="A5:R84">
     <cfRule type="expression" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
       <formula>$A5&lt;&gt;""</formula>
     </cfRule>
@@ -7735,7 +10142,7 @@
       <formula>$C5="P. Principal"</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="8">
+  <dataValidations count="12">
     <dataValidation allowBlank="true" error="Solo un número de 1 a 20." errorStyle="stop" errorTitle="Series" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="E5:E84" type="whole">
       <formula1>1</formula1>
       <formula2>20</formula2>
@@ -7760,12 +10167,28 @@
       <formula1>"Sí"</formula1>
       <formula2>0</formula2>
     </dataValidation>
+    <dataValidation allowBlank="true" error="Minutos del aeróbico (0,5 = 30 s)." errorStyle="stop" errorTitle="Minutos" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="M5:M84" type="decimal">
+      <formula1>0</formula1>
+      <formula2>600</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Un número de 0 a 10." errorStyle="stop" errorTitle="RPE pre" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="Q5:Q84" type="decimal">
+      <formula1>0</formula1>
+      <formula2>10</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Un número de 0 a 10." errorStyle="stop" errorTitle="RPE post" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="R5:R84" type="decimal">
+      <formula1>0</formula1>
+      <formula2>10</formula2>
+    </dataValidation>
     <dataValidation allowBlank="true" error="Elige un día del desplegable (Lunes … Domingo)." errorStyle="stop" errorTitle="Día" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="A5:A84" type="list">
       <formula1>"Lunes,Martes,Miércoles,Jueves,Viernes,Sábado,Domingo"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Elige un bloque del desplegable." errorStyle="stop" errorTitle="Bloque" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C5:C84" type="list">
-      <formula1>"Activación,P. Principal,Accesorios,Vuelta a la calma"</formula1>
+      <formula1>"Activación,P. Principal,Aeróbico,Accesorios,Vuelta a la calma"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Elige una zona del desplegable." errorStyle="stop" errorTitle="Zona" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="N5:N84" type="list">
+      <formula1>"Z1,Z2,Z3,Z4,Z5"</formula1>
       <formula2>0</formula2>
     </dataValidation>
   </dataValidations>

--- a/plantillas/PLANTILLA_PAREJA.xlsx
+++ b/plantillas/PLANTILLA_PAREJA.xlsx
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="432" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="349" uniqueCount="47">
   <si>
     <t xml:space="preserve">Cómo se rellena esta plantilla</t>
   </si>
@@ -82,7 +82,7 @@
     <t xml:space="preserve">10. Peso O / Peso S: un peso por cliente. Cambia la letra del título por la inicial de cada uno (Peso A, Peso M…) y usa esas mismas letras en la pestaña «fuentes» de Google (por ejemplo «O: apodo de uno, S: apodo del otro»).</t>
   </si>
   <si>
-    <t xml:space="preserve">11. Aeróbico (al final de la sesión): Bloque «Aeróbico», Ejercicio = Carrera, Bicicleta…, y Minutos + Zona o Intervalos («10 Z2, 3 Z4, 10 Z2»). Una fila por sesión.</t>
+    <t xml:space="preserve">11. Aeróbico (al final de la sesión): Bloque «Aeróbico», Ejercicio = Carrera, Bicicleta…, y en Observaciones el tiempo y la zona: «20 min Z2» o, por intervalos, «10 Z2, 3 Z4, 10 Z2». Una fila por sesión.</t>
   </si>
   <si>
     <t xml:space="preserve">12. No cambies los títulos de las tablas ni la celda «SEMANA DEL». Puedes añadir más pestañas (ANUAL, RM…): se ignoran.</t>
@@ -124,15 +124,6 @@
     <t xml:space="preserve">Pliometría</t>
   </si>
   <si>
-    <t xml:space="preserve">Minutos</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zona</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Intervalos</t>
-  </si>
-  <si>
     <t xml:space="preserve">Observaciones</t>
   </si>
   <si>
@@ -169,7 +160,7 @@
     <t xml:space="preserve">Bicicleta</t>
   </si>
   <si>
-    <t xml:space="preserve">Z2</t>
+    <t xml:space="preserve">15 min Z2</t>
   </si>
   <si>
     <t xml:space="preserve">SEMANA DEL</t>
@@ -187,10 +178,7 @@
     <t xml:space="preserve">Nombre:</t>
   </si>
   <si>
-    <t xml:space="preserve">RPE pre:</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RPE post:</t>
+    <t xml:space="preserve">RPE pre / post:</t>
   </si>
   <si>
     <t xml:space="preserve">SESIÓN 2</t>
@@ -266,7 +254,7 @@
     </font>
     <font>
       <b val="true"/>
-      <sz val="13"/>
+      <sz val="12"/>
       <color rgb="FF1F4E79"/>
       <name val="Arial"/>
       <family val="0"/>
@@ -312,15 +300,15 @@
     <font>
       <b val="true"/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color rgb="FF1B2A38"/>
       <name val="Arial"/>
       <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
       <b val="true"/>
-      <sz val="11"/>
-      <color rgb="FF1B2A38"/>
+      <sz val="9"/>
+      <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
       <family val="0"/>
       <charset val="1"/>
@@ -530,16 +518,16 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="14" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="15" fillId="4" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="14" fillId="4" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="5" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="164" fontId="15" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="165" fontId="9" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
@@ -840,20 +828,18 @@
     <tabColor rgb="FF1F4E79"/>
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:N23"/>
+  <dimension ref="A1:K23"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="17"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="34"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="0" width="8"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="13"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="6" style="0" width="9"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="7"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="9" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="7"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="20"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="0" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="40"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="18.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -875,9 +861,6 @@
       <c r="I3" s="2"/>
       <c r="J3" s="2"/>
       <c r="K3" s="2"/>
-      <c r="L3" s="2"/>
-      <c r="M3" s="2"/>
-      <c r="N3" s="2"/>
     </row>
     <row r="4" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
@@ -893,9 +876,6 @@
       <c r="I4" s="3"/>
       <c r="J4" s="3"/>
       <c r="K4" s="3"/>
-      <c r="L4" s="3"/>
-      <c r="M4" s="3"/>
-      <c r="N4" s="3"/>
     </row>
     <row r="5" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="s">
@@ -911,9 +891,6 @@
       <c r="I5" s="2"/>
       <c r="J5" s="2"/>
       <c r="K5" s="2"/>
-      <c r="L5" s="2"/>
-      <c r="M5" s="2"/>
-      <c r="N5" s="2"/>
     </row>
     <row r="6" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="3" t="s">
@@ -929,9 +906,6 @@
       <c r="I6" s="3"/>
       <c r="J6" s="3"/>
       <c r="K6" s="3"/>
-      <c r="L6" s="3"/>
-      <c r="M6" s="3"/>
-      <c r="N6" s="3"/>
     </row>
     <row r="7" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="2" t="s">
@@ -947,9 +921,6 @@
       <c r="I7" s="2"/>
       <c r="J7" s="2"/>
       <c r="K7" s="2"/>
-      <c r="L7" s="2"/>
-      <c r="M7" s="2"/>
-      <c r="N7" s="2"/>
     </row>
     <row r="8" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="3" t="s">
@@ -965,9 +936,6 @@
       <c r="I8" s="3"/>
       <c r="J8" s="3"/>
       <c r="K8" s="3"/>
-      <c r="L8" s="3"/>
-      <c r="M8" s="3"/>
-      <c r="N8" s="3"/>
     </row>
     <row r="9" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="2" t="s">
@@ -983,9 +951,6 @@
       <c r="I9" s="2"/>
       <c r="J9" s="2"/>
       <c r="K9" s="2"/>
-      <c r="L9" s="2"/>
-      <c r="M9" s="2"/>
-      <c r="N9" s="2"/>
     </row>
     <row r="10" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="3" t="s">
@@ -1001,9 +966,6 @@
       <c r="I10" s="3"/>
       <c r="J10" s="3"/>
       <c r="K10" s="3"/>
-      <c r="L10" s="3"/>
-      <c r="M10" s="3"/>
-      <c r="N10" s="3"/>
     </row>
     <row r="11" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="2" t="s">
@@ -1019,9 +981,6 @@
       <c r="I11" s="2"/>
       <c r="J11" s="2"/>
       <c r="K11" s="2"/>
-      <c r="L11" s="2"/>
-      <c r="M11" s="2"/>
-      <c r="N11" s="2"/>
     </row>
     <row r="12" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="3" t="s">
@@ -1037,9 +996,6 @@
       <c r="I12" s="3"/>
       <c r="J12" s="3"/>
       <c r="K12" s="3"/>
-      <c r="L12" s="3"/>
-      <c r="M12" s="3"/>
-      <c r="N12" s="3"/>
     </row>
     <row r="13" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="2" t="s">
@@ -1055,9 +1011,6 @@
       <c r="I13" s="2"/>
       <c r="J13" s="2"/>
       <c r="K13" s="2"/>
-      <c r="L13" s="2"/>
-      <c r="M13" s="2"/>
-      <c r="N13" s="2"/>
     </row>
     <row r="14" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="3" t="s">
@@ -1073,9 +1026,6 @@
       <c r="I14" s="3"/>
       <c r="J14" s="3"/>
       <c r="K14" s="3"/>
-      <c r="L14" s="3"/>
-      <c r="M14" s="3"/>
-      <c r="N14" s="3"/>
     </row>
     <row r="15" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="2" t="s">
@@ -1091,9 +1041,6 @@
       <c r="I15" s="2"/>
       <c r="J15" s="2"/>
       <c r="K15" s="2"/>
-      <c r="L15" s="2"/>
-      <c r="M15" s="2"/>
-      <c r="N15" s="2"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="4" t="s">
@@ -1134,22 +1081,13 @@
       <c r="K18" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="L18" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="M18" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="N18" s="5" t="s">
-        <v>28</v>
-      </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="6" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="B19" s="7" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="C19" s="8" t="n">
         <v>2</v>
@@ -1163,17 +1101,14 @@
       <c r="H19" s="8"/>
       <c r="I19" s="8"/>
       <c r="J19" s="8"/>
-      <c r="K19" s="8"/>
-      <c r="L19" s="8"/>
-      <c r="M19" s="7"/>
-      <c r="N19" s="9"/>
+      <c r="K19" s="9"/>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="10" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="B20" s="11" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="C20" s="12" t="n">
         <v>3</v>
@@ -1182,7 +1117,7 @@
         <v>8</v>
       </c>
       <c r="E20" s="11" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="F20" s="12" t="n">
         <v>24</v>
@@ -1195,15 +1130,12 @@
       </c>
       <c r="I20" s="12"/>
       <c r="J20" s="12"/>
-      <c r="K20" s="12"/>
-      <c r="L20" s="12"/>
-      <c r="M20" s="11"/>
-      <c r="N20" s="13"/>
+      <c r="K20" s="13"/>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="6"/>
       <c r="B21" s="7" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="C21" s="8" t="n">
         <v>3</v>
@@ -1212,7 +1144,7 @@
         <v>8</v>
       </c>
       <c r="E21" s="7" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="F21" s="8" t="n">
         <v>10</v>
@@ -1222,18 +1154,15 @@
       </c>
       <c r="H21" s="8"/>
       <c r="I21" s="8" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="J21" s="8"/>
-      <c r="K21" s="8"/>
-      <c r="L21" s="8"/>
-      <c r="M21" s="7"/>
-      <c r="N21" s="9"/>
+      <c r="K21" s="9"/>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="10"/>
       <c r="B22" s="11" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="C22" s="12" t="n">
         <v>3</v>
@@ -1247,19 +1176,16 @@
       <c r="H22" s="12"/>
       <c r="I22" s="12"/>
       <c r="J22" s="12" t="s">
-        <v>36</v>
-      </c>
-      <c r="K22" s="12"/>
-      <c r="L22" s="12"/>
-      <c r="M22" s="11"/>
-      <c r="N22" s="13"/>
+        <v>33</v>
+      </c>
+      <c r="K22" s="13"/>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="6" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="B23" s="7" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="C23" s="8"/>
       <c r="D23" s="8"/>
@@ -1269,30 +1195,25 @@
       <c r="H23" s="8"/>
       <c r="I23" s="8"/>
       <c r="J23" s="8"/>
-      <c r="K23" s="8" t="n">
-        <v>15</v>
-      </c>
-      <c r="L23" s="8" t="s">
-        <v>40</v>
-      </c>
-      <c r="M23" s="7"/>
-      <c r="N23" s="9"/>
+      <c r="K23" s="9" t="s">
+        <v>37</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="13">
-    <mergeCell ref="A3:N3"/>
-    <mergeCell ref="A4:N4"/>
-    <mergeCell ref="A5:N5"/>
-    <mergeCell ref="A6:N6"/>
-    <mergeCell ref="A7:N7"/>
-    <mergeCell ref="A8:N8"/>
-    <mergeCell ref="A9:N9"/>
-    <mergeCell ref="A10:N10"/>
-    <mergeCell ref="A11:N11"/>
-    <mergeCell ref="A12:N12"/>
-    <mergeCell ref="A13:N13"/>
-    <mergeCell ref="A14:N14"/>
-    <mergeCell ref="A15:N15"/>
+    <mergeCell ref="A3:K3"/>
+    <mergeCell ref="A4:K4"/>
+    <mergeCell ref="A5:K5"/>
+    <mergeCell ref="A6:K6"/>
+    <mergeCell ref="A7:K7"/>
+    <mergeCell ref="A8:K8"/>
+    <mergeCell ref="A9:K9"/>
+    <mergeCell ref="A10:K10"/>
+    <mergeCell ref="A11:K11"/>
+    <mergeCell ref="A12:K12"/>
+    <mergeCell ref="A13:K13"/>
+    <mergeCell ref="A14:K14"/>
+    <mergeCell ref="A15:K15"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -1310,25 +1231,23 @@
     <tabColor rgb="FF2E8B6E"/>
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:N76"/>
+  <dimension ref="A1:K76"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="17"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="34"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="0" width="8"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="13"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="6" style="0" width="9"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="7"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="9" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="7"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="20"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="0" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="40"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="14" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="B1" s="15" t="n">
         <v>46328</v>
@@ -1338,7 +1257,7 @@
         <v>al 08/11</v>
       </c>
       <c r="E1" s="17" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="F1" s="18"/>
       <c r="G1" s="18"/>
@@ -1346,29 +1265,24 @@
     </row>
     <row r="3" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="19" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="B3" s="20" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="C3" s="21"/>
       <c r="D3" s="21"/>
       <c r="E3" s="20" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="F3" s="21"/>
       <c r="G3" s="21"/>
       <c r="H3" s="21"/>
-      <c r="I3" s="21"/>
-      <c r="J3" s="22"/>
-      <c r="K3" s="20" t="s">
-        <v>46</v>
-      </c>
-      <c r="L3" s="21"/>
-      <c r="M3" s="20" t="s">
-        <v>47</v>
-      </c>
-      <c r="N3" s="21"/>
+      <c r="I3" s="22" t="s">
+        <v>43</v>
+      </c>
+      <c r="J3" s="21"/>
+      <c r="K3" s="21"/>
     </row>
     <row r="4" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="5" t="s">
@@ -1403,15 +1317,6 @@
       </c>
       <c r="K4" s="5" t="s">
         <v>25</v>
-      </c>
-      <c r="L4" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="M4" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="N4" s="5" t="s">
-        <v>28</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1425,10 +1330,7 @@
       <c r="H5" s="8"/>
       <c r="I5" s="8"/>
       <c r="J5" s="8"/>
-      <c r="K5" s="8"/>
-      <c r="L5" s="8"/>
-      <c r="M5" s="7"/>
-      <c r="N5" s="9"/>
+      <c r="K5" s="9"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="10"/>
@@ -1441,10 +1343,7 @@
       <c r="H6" s="12"/>
       <c r="I6" s="12"/>
       <c r="J6" s="12"/>
-      <c r="K6" s="12"/>
-      <c r="L6" s="12"/>
-      <c r="M6" s="11"/>
-      <c r="N6" s="13"/>
+      <c r="K6" s="13"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="6"/>
@@ -1457,10 +1356,7 @@
       <c r="H7" s="8"/>
       <c r="I7" s="8"/>
       <c r="J7" s="8"/>
-      <c r="K7" s="8"/>
-      <c r="L7" s="8"/>
-      <c r="M7" s="7"/>
-      <c r="N7" s="9"/>
+      <c r="K7" s="9"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="10"/>
@@ -1473,10 +1369,7 @@
       <c r="H8" s="12"/>
       <c r="I8" s="12"/>
       <c r="J8" s="12"/>
-      <c r="K8" s="12"/>
-      <c r="L8" s="12"/>
-      <c r="M8" s="11"/>
-      <c r="N8" s="13"/>
+      <c r="K8" s="13"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="6"/>
@@ -1489,10 +1382,7 @@
       <c r="H9" s="8"/>
       <c r="I9" s="8"/>
       <c r="J9" s="8"/>
-      <c r="K9" s="8"/>
-      <c r="L9" s="8"/>
-      <c r="M9" s="7"/>
-      <c r="N9" s="9"/>
+      <c r="K9" s="9"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="10"/>
@@ -1505,10 +1395,7 @@
       <c r="H10" s="12"/>
       <c r="I10" s="12"/>
       <c r="J10" s="12"/>
-      <c r="K10" s="12"/>
-      <c r="L10" s="12"/>
-      <c r="M10" s="11"/>
-      <c r="N10" s="13"/>
+      <c r="K10" s="13"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="6"/>
@@ -1521,10 +1408,7 @@
       <c r="H11" s="8"/>
       <c r="I11" s="8"/>
       <c r="J11" s="8"/>
-      <c r="K11" s="8"/>
-      <c r="L11" s="8"/>
-      <c r="M11" s="7"/>
-      <c r="N11" s="9"/>
+      <c r="K11" s="9"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="10"/>
@@ -1537,10 +1421,7 @@
       <c r="H12" s="12"/>
       <c r="I12" s="12"/>
       <c r="J12" s="12"/>
-      <c r="K12" s="12"/>
-      <c r="L12" s="12"/>
-      <c r="M12" s="11"/>
-      <c r="N12" s="13"/>
+      <c r="K12" s="13"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="6"/>
@@ -1553,10 +1434,7 @@
       <c r="H13" s="8"/>
       <c r="I13" s="8"/>
       <c r="J13" s="8"/>
-      <c r="K13" s="8"/>
-      <c r="L13" s="8"/>
-      <c r="M13" s="7"/>
-      <c r="N13" s="9"/>
+      <c r="K13" s="9"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="10"/>
@@ -1569,10 +1447,7 @@
       <c r="H14" s="12"/>
       <c r="I14" s="12"/>
       <c r="J14" s="12"/>
-      <c r="K14" s="12"/>
-      <c r="L14" s="12"/>
-      <c r="M14" s="11"/>
-      <c r="N14" s="13"/>
+      <c r="K14" s="13"/>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="6"/>
@@ -1585,10 +1460,7 @@
       <c r="H15" s="8"/>
       <c r="I15" s="8"/>
       <c r="J15" s="8"/>
-      <c r="K15" s="8"/>
-      <c r="L15" s="8"/>
-      <c r="M15" s="7"/>
-      <c r="N15" s="9"/>
+      <c r="K15" s="9"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="10"/>
@@ -1601,10 +1473,7 @@
       <c r="H16" s="12"/>
       <c r="I16" s="12"/>
       <c r="J16" s="12"/>
-      <c r="K16" s="12"/>
-      <c r="L16" s="12"/>
-      <c r="M16" s="11"/>
-      <c r="N16" s="13"/>
+      <c r="K16" s="13"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="6"/>
@@ -1617,10 +1486,7 @@
       <c r="H17" s="8"/>
       <c r="I17" s="8"/>
       <c r="J17" s="8"/>
-      <c r="K17" s="8"/>
-      <c r="L17" s="8"/>
-      <c r="M17" s="7"/>
-      <c r="N17" s="9"/>
+      <c r="K17" s="9"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="10"/>
@@ -1633,10 +1499,7 @@
       <c r="H18" s="12"/>
       <c r="I18" s="12"/>
       <c r="J18" s="12"/>
-      <c r="K18" s="12"/>
-      <c r="L18" s="12"/>
-      <c r="M18" s="11"/>
-      <c r="N18" s="13"/>
+      <c r="K18" s="13"/>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="6"/>
@@ -1649,36 +1512,28 @@
       <c r="H19" s="8"/>
       <c r="I19" s="8"/>
       <c r="J19" s="8"/>
-      <c r="K19" s="8"/>
-      <c r="L19" s="8"/>
-      <c r="M19" s="7"/>
-      <c r="N19" s="9"/>
+      <c r="K19" s="9"/>
     </row>
     <row r="22" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="19" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="B22" s="20" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="C22" s="21"/>
       <c r="D22" s="21"/>
       <c r="E22" s="20" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="F22" s="21"/>
       <c r="G22" s="21"/>
       <c r="H22" s="21"/>
-      <c r="I22" s="21"/>
-      <c r="J22" s="22"/>
-      <c r="K22" s="20" t="s">
-        <v>46</v>
-      </c>
-      <c r="L22" s="21"/>
-      <c r="M22" s="20" t="s">
-        <v>47</v>
-      </c>
-      <c r="N22" s="21"/>
+      <c r="I22" s="22" t="s">
+        <v>43</v>
+      </c>
+      <c r="J22" s="21"/>
+      <c r="K22" s="21"/>
     </row>
     <row r="23" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="5" t="s">
@@ -1713,15 +1568,6 @@
       </c>
       <c r="K23" s="5" t="s">
         <v>25</v>
-      </c>
-      <c r="L23" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="M23" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="N23" s="5" t="s">
-        <v>28</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1735,10 +1581,7 @@
       <c r="H24" s="8"/>
       <c r="I24" s="8"/>
       <c r="J24" s="8"/>
-      <c r="K24" s="8"/>
-      <c r="L24" s="8"/>
-      <c r="M24" s="7"/>
-      <c r="N24" s="9"/>
+      <c r="K24" s="9"/>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="10"/>
@@ -1751,10 +1594,7 @@
       <c r="H25" s="12"/>
       <c r="I25" s="12"/>
       <c r="J25" s="12"/>
-      <c r="K25" s="12"/>
-      <c r="L25" s="12"/>
-      <c r="M25" s="11"/>
-      <c r="N25" s="13"/>
+      <c r="K25" s="13"/>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="6"/>
@@ -1767,10 +1607,7 @@
       <c r="H26" s="8"/>
       <c r="I26" s="8"/>
       <c r="J26" s="8"/>
-      <c r="K26" s="8"/>
-      <c r="L26" s="8"/>
-      <c r="M26" s="7"/>
-      <c r="N26" s="9"/>
+      <c r="K26" s="9"/>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="10"/>
@@ -1783,10 +1620,7 @@
       <c r="H27" s="12"/>
       <c r="I27" s="12"/>
       <c r="J27" s="12"/>
-      <c r="K27" s="12"/>
-      <c r="L27" s="12"/>
-      <c r="M27" s="11"/>
-      <c r="N27" s="13"/>
+      <c r="K27" s="13"/>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="6"/>
@@ -1799,10 +1633,7 @@
       <c r="H28" s="8"/>
       <c r="I28" s="8"/>
       <c r="J28" s="8"/>
-      <c r="K28" s="8"/>
-      <c r="L28" s="8"/>
-      <c r="M28" s="7"/>
-      <c r="N28" s="9"/>
+      <c r="K28" s="9"/>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="10"/>
@@ -1815,10 +1646,7 @@
       <c r="H29" s="12"/>
       <c r="I29" s="12"/>
       <c r="J29" s="12"/>
-      <c r="K29" s="12"/>
-      <c r="L29" s="12"/>
-      <c r="M29" s="11"/>
-      <c r="N29" s="13"/>
+      <c r="K29" s="13"/>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="6"/>
@@ -1831,10 +1659,7 @@
       <c r="H30" s="8"/>
       <c r="I30" s="8"/>
       <c r="J30" s="8"/>
-      <c r="K30" s="8"/>
-      <c r="L30" s="8"/>
-      <c r="M30" s="7"/>
-      <c r="N30" s="9"/>
+      <c r="K30" s="9"/>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="10"/>
@@ -1847,10 +1672,7 @@
       <c r="H31" s="12"/>
       <c r="I31" s="12"/>
       <c r="J31" s="12"/>
-      <c r="K31" s="12"/>
-      <c r="L31" s="12"/>
-      <c r="M31" s="11"/>
-      <c r="N31" s="13"/>
+      <c r="K31" s="13"/>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="6"/>
@@ -1863,10 +1685,7 @@
       <c r="H32" s="8"/>
       <c r="I32" s="8"/>
       <c r="J32" s="8"/>
-      <c r="K32" s="8"/>
-      <c r="L32" s="8"/>
-      <c r="M32" s="7"/>
-      <c r="N32" s="9"/>
+      <c r="K32" s="9"/>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="10"/>
@@ -1879,10 +1698,7 @@
       <c r="H33" s="12"/>
       <c r="I33" s="12"/>
       <c r="J33" s="12"/>
-      <c r="K33" s="12"/>
-      <c r="L33" s="12"/>
-      <c r="M33" s="11"/>
-      <c r="N33" s="13"/>
+      <c r="K33" s="13"/>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="6"/>
@@ -1895,10 +1711,7 @@
       <c r="H34" s="8"/>
       <c r="I34" s="8"/>
       <c r="J34" s="8"/>
-      <c r="K34" s="8"/>
-      <c r="L34" s="8"/>
-      <c r="M34" s="7"/>
-      <c r="N34" s="9"/>
+      <c r="K34" s="9"/>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="10"/>
@@ -1911,10 +1724,7 @@
       <c r="H35" s="12"/>
       <c r="I35" s="12"/>
       <c r="J35" s="12"/>
-      <c r="K35" s="12"/>
-      <c r="L35" s="12"/>
-      <c r="M35" s="11"/>
-      <c r="N35" s="13"/>
+      <c r="K35" s="13"/>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="6"/>
@@ -1927,10 +1737,7 @@
       <c r="H36" s="8"/>
       <c r="I36" s="8"/>
       <c r="J36" s="8"/>
-      <c r="K36" s="8"/>
-      <c r="L36" s="8"/>
-      <c r="M36" s="7"/>
-      <c r="N36" s="9"/>
+      <c r="K36" s="9"/>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="10"/>
@@ -1943,10 +1750,7 @@
       <c r="H37" s="12"/>
       <c r="I37" s="12"/>
       <c r="J37" s="12"/>
-      <c r="K37" s="12"/>
-      <c r="L37" s="12"/>
-      <c r="M37" s="11"/>
-      <c r="N37" s="13"/>
+      <c r="K37" s="13"/>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="6"/>
@@ -1959,36 +1763,28 @@
       <c r="H38" s="8"/>
       <c r="I38" s="8"/>
       <c r="J38" s="8"/>
-      <c r="K38" s="8"/>
-      <c r="L38" s="8"/>
-      <c r="M38" s="7"/>
-      <c r="N38" s="9"/>
+      <c r="K38" s="9"/>
     </row>
     <row r="41" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="19" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="B41" s="20" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="C41" s="21"/>
       <c r="D41" s="21"/>
       <c r="E41" s="20" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="F41" s="21"/>
       <c r="G41" s="21"/>
       <c r="H41" s="21"/>
-      <c r="I41" s="21"/>
-      <c r="J41" s="22"/>
-      <c r="K41" s="20" t="s">
-        <v>46</v>
-      </c>
-      <c r="L41" s="21"/>
-      <c r="M41" s="20" t="s">
-        <v>47</v>
-      </c>
-      <c r="N41" s="21"/>
+      <c r="I41" s="22" t="s">
+        <v>43</v>
+      </c>
+      <c r="J41" s="21"/>
+      <c r="K41" s="21"/>
     </row>
     <row r="42" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="5" t="s">
@@ -2023,15 +1819,6 @@
       </c>
       <c r="K42" s="5" t="s">
         <v>25</v>
-      </c>
-      <c r="L42" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="M42" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="N42" s="5" t="s">
-        <v>28</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2045,10 +1832,7 @@
       <c r="H43" s="8"/>
       <c r="I43" s="8"/>
       <c r="J43" s="8"/>
-      <c r="K43" s="8"/>
-      <c r="L43" s="8"/>
-      <c r="M43" s="7"/>
-      <c r="N43" s="9"/>
+      <c r="K43" s="9"/>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="10"/>
@@ -2061,10 +1845,7 @@
       <c r="H44" s="12"/>
       <c r="I44" s="12"/>
       <c r="J44" s="12"/>
-      <c r="K44" s="12"/>
-      <c r="L44" s="12"/>
-      <c r="M44" s="11"/>
-      <c r="N44" s="13"/>
+      <c r="K44" s="13"/>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="6"/>
@@ -2077,10 +1858,7 @@
       <c r="H45" s="8"/>
       <c r="I45" s="8"/>
       <c r="J45" s="8"/>
-      <c r="K45" s="8"/>
-      <c r="L45" s="8"/>
-      <c r="M45" s="7"/>
-      <c r="N45" s="9"/>
+      <c r="K45" s="9"/>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="10"/>
@@ -2093,10 +1871,7 @@
       <c r="H46" s="12"/>
       <c r="I46" s="12"/>
       <c r="J46" s="12"/>
-      <c r="K46" s="12"/>
-      <c r="L46" s="12"/>
-      <c r="M46" s="11"/>
-      <c r="N46" s="13"/>
+      <c r="K46" s="13"/>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="6"/>
@@ -2109,10 +1884,7 @@
       <c r="H47" s="8"/>
       <c r="I47" s="8"/>
       <c r="J47" s="8"/>
-      <c r="K47" s="8"/>
-      <c r="L47" s="8"/>
-      <c r="M47" s="7"/>
-      <c r="N47" s="9"/>
+      <c r="K47" s="9"/>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="10"/>
@@ -2125,10 +1897,7 @@
       <c r="H48" s="12"/>
       <c r="I48" s="12"/>
       <c r="J48" s="12"/>
-      <c r="K48" s="12"/>
-      <c r="L48" s="12"/>
-      <c r="M48" s="11"/>
-      <c r="N48" s="13"/>
+      <c r="K48" s="13"/>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="6"/>
@@ -2141,10 +1910,7 @@
       <c r="H49" s="8"/>
       <c r="I49" s="8"/>
       <c r="J49" s="8"/>
-      <c r="K49" s="8"/>
-      <c r="L49" s="8"/>
-      <c r="M49" s="7"/>
-      <c r="N49" s="9"/>
+      <c r="K49" s="9"/>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="10"/>
@@ -2157,10 +1923,7 @@
       <c r="H50" s="12"/>
       <c r="I50" s="12"/>
       <c r="J50" s="12"/>
-      <c r="K50" s="12"/>
-      <c r="L50" s="12"/>
-      <c r="M50" s="11"/>
-      <c r="N50" s="13"/>
+      <c r="K50" s="13"/>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="6"/>
@@ -2173,10 +1936,7 @@
       <c r="H51" s="8"/>
       <c r="I51" s="8"/>
       <c r="J51" s="8"/>
-      <c r="K51" s="8"/>
-      <c r="L51" s="8"/>
-      <c r="M51" s="7"/>
-      <c r="N51" s="9"/>
+      <c r="K51" s="9"/>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="10"/>
@@ -2189,10 +1949,7 @@
       <c r="H52" s="12"/>
       <c r="I52" s="12"/>
       <c r="J52" s="12"/>
-      <c r="K52" s="12"/>
-      <c r="L52" s="12"/>
-      <c r="M52" s="11"/>
-      <c r="N52" s="13"/>
+      <c r="K52" s="13"/>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="6"/>
@@ -2205,10 +1962,7 @@
       <c r="H53" s="8"/>
       <c r="I53" s="8"/>
       <c r="J53" s="8"/>
-      <c r="K53" s="8"/>
-      <c r="L53" s="8"/>
-      <c r="M53" s="7"/>
-      <c r="N53" s="9"/>
+      <c r="K53" s="9"/>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="10"/>
@@ -2221,10 +1975,7 @@
       <c r="H54" s="12"/>
       <c r="I54" s="12"/>
       <c r="J54" s="12"/>
-      <c r="K54" s="12"/>
-      <c r="L54" s="12"/>
-      <c r="M54" s="11"/>
-      <c r="N54" s="13"/>
+      <c r="K54" s="13"/>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="6"/>
@@ -2237,10 +1988,7 @@
       <c r="H55" s="8"/>
       <c r="I55" s="8"/>
       <c r="J55" s="8"/>
-      <c r="K55" s="8"/>
-      <c r="L55" s="8"/>
-      <c r="M55" s="7"/>
-      <c r="N55" s="9"/>
+      <c r="K55" s="9"/>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="10"/>
@@ -2253,10 +2001,7 @@
       <c r="H56" s="12"/>
       <c r="I56" s="12"/>
       <c r="J56" s="12"/>
-      <c r="K56" s="12"/>
-      <c r="L56" s="12"/>
-      <c r="M56" s="11"/>
-      <c r="N56" s="13"/>
+      <c r="K56" s="13"/>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="6"/>
@@ -2269,36 +2014,28 @@
       <c r="H57" s="8"/>
       <c r="I57" s="8"/>
       <c r="J57" s="8"/>
-      <c r="K57" s="8"/>
-      <c r="L57" s="8"/>
-      <c r="M57" s="7"/>
-      <c r="N57" s="9"/>
+      <c r="K57" s="9"/>
     </row>
     <row r="60" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A60" s="19" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="B60" s="20" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="C60" s="21"/>
       <c r="D60" s="21"/>
       <c r="E60" s="20" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="F60" s="21"/>
       <c r="G60" s="21"/>
       <c r="H60" s="21"/>
-      <c r="I60" s="21"/>
-      <c r="J60" s="22"/>
-      <c r="K60" s="20" t="s">
-        <v>46</v>
-      </c>
-      <c r="L60" s="21"/>
-      <c r="M60" s="20" t="s">
-        <v>47</v>
-      </c>
-      <c r="N60" s="21"/>
+      <c r="I60" s="22" t="s">
+        <v>43</v>
+      </c>
+      <c r="J60" s="21"/>
+      <c r="K60" s="21"/>
     </row>
     <row r="61" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A61" s="5" t="s">
@@ -2333,15 +2070,6 @@
       </c>
       <c r="K61" s="5" t="s">
         <v>25</v>
-      </c>
-      <c r="L61" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="M61" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="N61" s="5" t="s">
-        <v>28</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2355,10 +2083,7 @@
       <c r="H62" s="8"/>
       <c r="I62" s="8"/>
       <c r="J62" s="8"/>
-      <c r="K62" s="8"/>
-      <c r="L62" s="8"/>
-      <c r="M62" s="7"/>
-      <c r="N62" s="9"/>
+      <c r="K62" s="9"/>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="10"/>
@@ -2371,10 +2096,7 @@
       <c r="H63" s="12"/>
       <c r="I63" s="12"/>
       <c r="J63" s="12"/>
-      <c r="K63" s="12"/>
-      <c r="L63" s="12"/>
-      <c r="M63" s="11"/>
-      <c r="N63" s="13"/>
+      <c r="K63" s="13"/>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="6"/>
@@ -2387,10 +2109,7 @@
       <c r="H64" s="8"/>
       <c r="I64" s="8"/>
       <c r="J64" s="8"/>
-      <c r="K64" s="8"/>
-      <c r="L64" s="8"/>
-      <c r="M64" s="7"/>
-      <c r="N64" s="9"/>
+      <c r="K64" s="9"/>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="10"/>
@@ -2403,10 +2122,7 @@
       <c r="H65" s="12"/>
       <c r="I65" s="12"/>
       <c r="J65" s="12"/>
-      <c r="K65" s="12"/>
-      <c r="L65" s="12"/>
-      <c r="M65" s="11"/>
-      <c r="N65" s="13"/>
+      <c r="K65" s="13"/>
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="6"/>
@@ -2419,10 +2135,7 @@
       <c r="H66" s="8"/>
       <c r="I66" s="8"/>
       <c r="J66" s="8"/>
-      <c r="K66" s="8"/>
-      <c r="L66" s="8"/>
-      <c r="M66" s="7"/>
-      <c r="N66" s="9"/>
+      <c r="K66" s="9"/>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="10"/>
@@ -2435,10 +2148,7 @@
       <c r="H67" s="12"/>
       <c r="I67" s="12"/>
       <c r="J67" s="12"/>
-      <c r="K67" s="12"/>
-      <c r="L67" s="12"/>
-      <c r="M67" s="11"/>
-      <c r="N67" s="13"/>
+      <c r="K67" s="13"/>
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="6"/>
@@ -2451,10 +2161,7 @@
       <c r="H68" s="8"/>
       <c r="I68" s="8"/>
       <c r="J68" s="8"/>
-      <c r="K68" s="8"/>
-      <c r="L68" s="8"/>
-      <c r="M68" s="7"/>
-      <c r="N68" s="9"/>
+      <c r="K68" s="9"/>
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="10"/>
@@ -2467,10 +2174,7 @@
       <c r="H69" s="12"/>
       <c r="I69" s="12"/>
       <c r="J69" s="12"/>
-      <c r="K69" s="12"/>
-      <c r="L69" s="12"/>
-      <c r="M69" s="11"/>
-      <c r="N69" s="13"/>
+      <c r="K69" s="13"/>
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="6"/>
@@ -2483,10 +2187,7 @@
       <c r="H70" s="8"/>
       <c r="I70" s="8"/>
       <c r="J70" s="8"/>
-      <c r="K70" s="8"/>
-      <c r="L70" s="8"/>
-      <c r="M70" s="7"/>
-      <c r="N70" s="9"/>
+      <c r="K70" s="9"/>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="10"/>
@@ -2499,10 +2200,7 @@
       <c r="H71" s="12"/>
       <c r="I71" s="12"/>
       <c r="J71" s="12"/>
-      <c r="K71" s="12"/>
-      <c r="L71" s="12"/>
-      <c r="M71" s="11"/>
-      <c r="N71" s="13"/>
+      <c r="K71" s="13"/>
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="6"/>
@@ -2515,10 +2213,7 @@
       <c r="H72" s="8"/>
       <c r="I72" s="8"/>
       <c r="J72" s="8"/>
-      <c r="K72" s="8"/>
-      <c r="L72" s="8"/>
-      <c r="M72" s="7"/>
-      <c r="N72" s="9"/>
+      <c r="K72" s="9"/>
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="10"/>
@@ -2531,10 +2226,7 @@
       <c r="H73" s="12"/>
       <c r="I73" s="12"/>
       <c r="J73" s="12"/>
-      <c r="K73" s="12"/>
-      <c r="L73" s="12"/>
-      <c r="M73" s="11"/>
-      <c r="N73" s="13"/>
+      <c r="K73" s="13"/>
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="6"/>
@@ -2547,10 +2239,7 @@
       <c r="H74" s="8"/>
       <c r="I74" s="8"/>
       <c r="J74" s="8"/>
-      <c r="K74" s="8"/>
-      <c r="L74" s="8"/>
-      <c r="M74" s="7"/>
-      <c r="N74" s="9"/>
+      <c r="K74" s="9"/>
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="10"/>
@@ -2563,10 +2252,7 @@
       <c r="H75" s="12"/>
       <c r="I75" s="12"/>
       <c r="J75" s="12"/>
-      <c r="K75" s="12"/>
-      <c r="L75" s="12"/>
-      <c r="M75" s="11"/>
-      <c r="N75" s="13"/>
+      <c r="K75" s="13"/>
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="6"/>
@@ -2579,22 +2265,19 @@
       <c r="H76" s="8"/>
       <c r="I76" s="8"/>
       <c r="J76" s="8"/>
-      <c r="K76" s="8"/>
-      <c r="L76" s="8"/>
-      <c r="M76" s="7"/>
-      <c r="N76" s="9"/>
+      <c r="K76" s="9"/>
     </row>
   </sheetData>
   <mergeCells count="9">
     <mergeCell ref="F1:H1"/>
     <mergeCell ref="C3:D3"/>
-    <mergeCell ref="F3:I3"/>
+    <mergeCell ref="F3:H3"/>
     <mergeCell ref="C22:D22"/>
-    <mergeCell ref="F22:I22"/>
+    <mergeCell ref="F22:H22"/>
     <mergeCell ref="C41:D41"/>
-    <mergeCell ref="F41:I41"/>
+    <mergeCell ref="F41:H41"/>
     <mergeCell ref="C60:D60"/>
-    <mergeCell ref="F60:I60"/>
+    <mergeCell ref="F60:H60"/>
   </mergeCells>
   <conditionalFormatting sqref="A5:A19">
     <cfRule type="expression" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
@@ -2652,12 +2335,12 @@
       <formula>OR($A62="Accesorios",$A62="Vuelta a la calma")</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="20">
+  <dataValidations count="15">
     <dataValidation allowBlank="true" error="Elige un día del desplegable." errorStyle="stop" errorTitle="Día" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C3" type="list">
       <formula1>"Lunes,Martes,Miércoles,Jueves,Viernes,Sábado,Domingo"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" error="Un número de 0 a 10." errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="L3 N3 L22 N22 L41 N41 L60 N60" type="decimal">
+    <dataValidation allowBlank="true" error="Un número de 0 a 10." errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="J3:K3 J22:K22 J41:K41 J60:K60" type="decimal">
       <formula1>0</formula1>
       <formula2>10</formula2>
     </dataValidation>
@@ -2689,14 +2372,6 @@
       <formula1>"Sí"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" error="Minutos del aeróbico (0,5 = 30 s)." errorStyle="stop" errorTitle="Minutos" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="K5:K19 K24:K38 K43:K57 K62:K76" type="decimal">
-      <formula1>0</formula1>
-      <formula2>600</formula2>
-    </dataValidation>
-    <dataValidation allowBlank="true" error="Elige una zona del desplegable." errorStyle="stop" errorTitle="Zona" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="L5:L19" type="list">
-      <formula1>"Z1,Z2,Z3,Z4,Z5"</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
     <dataValidation allowBlank="true" error="Elige un día del desplegable." errorStyle="stop" errorTitle="Día" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C22" type="list">
       <formula1>"Lunes,Martes,Miércoles,Jueves,Viernes,Sábado,Domingo"</formula1>
       <formula2>0</formula2>
@@ -2705,10 +2380,6 @@
       <formula1>"Activación,P. Principal,Aeróbico,Accesorios,Vuelta a la calma"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" error="Elige una zona del desplegable." errorStyle="stop" errorTitle="Zona" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="L24:L38" type="list">
-      <formula1>"Z1,Z2,Z3,Z4,Z5"</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
     <dataValidation allowBlank="true" error="Elige un día del desplegable." errorStyle="stop" errorTitle="Día" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C41" type="list">
       <formula1>"Lunes,Martes,Miércoles,Jueves,Viernes,Sábado,Domingo"</formula1>
       <formula2>0</formula2>
@@ -2717,20 +2388,12 @@
       <formula1>"Activación,P. Principal,Aeróbico,Accesorios,Vuelta a la calma"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" error="Elige una zona del desplegable." errorStyle="stop" errorTitle="Zona" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="L43:L57" type="list">
-      <formula1>"Z1,Z2,Z3,Z4,Z5"</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
     <dataValidation allowBlank="true" error="Elige un día del desplegable." errorStyle="stop" errorTitle="Día" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C60" type="list">
       <formula1>"Lunes,Martes,Miércoles,Jueves,Viernes,Sábado,Domingo"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Elige un bloque del desplegable." errorStyle="stop" errorTitle="Bloque" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="A62:A76" type="list">
       <formula1>"Activación,P. Principal,Aeróbico,Accesorios,Vuelta a la calma"</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-    <dataValidation allowBlank="true" error="Elige una zona del desplegable." errorStyle="stop" errorTitle="Zona" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="L62:L76" type="list">
-      <formula1>"Z1,Z2,Z3,Z4,Z5"</formula1>
       <formula2>0</formula2>
     </dataValidation>
   </dataValidations>
@@ -2751,25 +2414,23 @@
     <tabColor rgb="FF2F6F9F"/>
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:N76"/>
+  <dimension ref="A1:K76"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="17"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="34"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="0" width="8"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="13"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="6" style="0" width="9"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="7"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="9" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="7"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="20"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="0" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="40"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="14" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="B1" s="23" t="n">
         <f aca="false">'Semana 1'!B1+7</f>
@@ -2780,7 +2441,7 @@
         <v>al 15/11</v>
       </c>
       <c r="E1" s="17" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="F1" s="18"/>
       <c r="G1" s="18"/>
@@ -2788,29 +2449,24 @@
     </row>
     <row r="3" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="19" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="B3" s="20" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="C3" s="21"/>
       <c r="D3" s="21"/>
       <c r="E3" s="20" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="F3" s="21"/>
       <c r="G3" s="21"/>
       <c r="H3" s="21"/>
-      <c r="I3" s="21"/>
-      <c r="J3" s="22"/>
-      <c r="K3" s="20" t="s">
-        <v>46</v>
-      </c>
-      <c r="L3" s="21"/>
-      <c r="M3" s="20" t="s">
-        <v>47</v>
-      </c>
-      <c r="N3" s="21"/>
+      <c r="I3" s="22" t="s">
+        <v>43</v>
+      </c>
+      <c r="J3" s="21"/>
+      <c r="K3" s="21"/>
     </row>
     <row r="4" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="5" t="s">
@@ -2845,15 +2501,6 @@
       </c>
       <c r="K4" s="5" t="s">
         <v>25</v>
-      </c>
-      <c r="L4" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="M4" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="N4" s="5" t="s">
-        <v>28</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2867,10 +2514,7 @@
       <c r="H5" s="8"/>
       <c r="I5" s="8"/>
       <c r="J5" s="8"/>
-      <c r="K5" s="8"/>
-      <c r="L5" s="8"/>
-      <c r="M5" s="7"/>
-      <c r="N5" s="9"/>
+      <c r="K5" s="9"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="10"/>
@@ -2883,10 +2527,7 @@
       <c r="H6" s="12"/>
       <c r="I6" s="12"/>
       <c r="J6" s="12"/>
-      <c r="K6" s="12"/>
-      <c r="L6" s="12"/>
-      <c r="M6" s="11"/>
-      <c r="N6" s="13"/>
+      <c r="K6" s="13"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="6"/>
@@ -2899,10 +2540,7 @@
       <c r="H7" s="8"/>
       <c r="I7" s="8"/>
       <c r="J7" s="8"/>
-      <c r="K7" s="8"/>
-      <c r="L7" s="8"/>
-      <c r="M7" s="7"/>
-      <c r="N7" s="9"/>
+      <c r="K7" s="9"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="10"/>
@@ -2915,10 +2553,7 @@
       <c r="H8" s="12"/>
       <c r="I8" s="12"/>
       <c r="J8" s="12"/>
-      <c r="K8" s="12"/>
-      <c r="L8" s="12"/>
-      <c r="M8" s="11"/>
-      <c r="N8" s="13"/>
+      <c r="K8" s="13"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="6"/>
@@ -2931,10 +2566,7 @@
       <c r="H9" s="8"/>
       <c r="I9" s="8"/>
       <c r="J9" s="8"/>
-      <c r="K9" s="8"/>
-      <c r="L9" s="8"/>
-      <c r="M9" s="7"/>
-      <c r="N9" s="9"/>
+      <c r="K9" s="9"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="10"/>
@@ -2947,10 +2579,7 @@
       <c r="H10" s="12"/>
       <c r="I10" s="12"/>
       <c r="J10" s="12"/>
-      <c r="K10" s="12"/>
-      <c r="L10" s="12"/>
-      <c r="M10" s="11"/>
-      <c r="N10" s="13"/>
+      <c r="K10" s="13"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="6"/>
@@ -2963,10 +2592,7 @@
       <c r="H11" s="8"/>
       <c r="I11" s="8"/>
       <c r="J11" s="8"/>
-      <c r="K11" s="8"/>
-      <c r="L11" s="8"/>
-      <c r="M11" s="7"/>
-      <c r="N11" s="9"/>
+      <c r="K11" s="9"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="10"/>
@@ -2979,10 +2605,7 @@
       <c r="H12" s="12"/>
       <c r="I12" s="12"/>
       <c r="J12" s="12"/>
-      <c r="K12" s="12"/>
-      <c r="L12" s="12"/>
-      <c r="M12" s="11"/>
-      <c r="N12" s="13"/>
+      <c r="K12" s="13"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="6"/>
@@ -2995,10 +2618,7 @@
       <c r="H13" s="8"/>
       <c r="I13" s="8"/>
       <c r="J13" s="8"/>
-      <c r="K13" s="8"/>
-      <c r="L13" s="8"/>
-      <c r="M13" s="7"/>
-      <c r="N13" s="9"/>
+      <c r="K13" s="9"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="10"/>
@@ -3011,10 +2631,7 @@
       <c r="H14" s="12"/>
       <c r="I14" s="12"/>
       <c r="J14" s="12"/>
-      <c r="K14" s="12"/>
-      <c r="L14" s="12"/>
-      <c r="M14" s="11"/>
-      <c r="N14" s="13"/>
+      <c r="K14" s="13"/>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="6"/>
@@ -3027,10 +2644,7 @@
       <c r="H15" s="8"/>
       <c r="I15" s="8"/>
       <c r="J15" s="8"/>
-      <c r="K15" s="8"/>
-      <c r="L15" s="8"/>
-      <c r="M15" s="7"/>
-      <c r="N15" s="9"/>
+      <c r="K15" s="9"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="10"/>
@@ -3043,10 +2657,7 @@
       <c r="H16" s="12"/>
       <c r="I16" s="12"/>
       <c r="J16" s="12"/>
-      <c r="K16" s="12"/>
-      <c r="L16" s="12"/>
-      <c r="M16" s="11"/>
-      <c r="N16" s="13"/>
+      <c r="K16" s="13"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="6"/>
@@ -3059,10 +2670,7 @@
       <c r="H17" s="8"/>
       <c r="I17" s="8"/>
       <c r="J17" s="8"/>
-      <c r="K17" s="8"/>
-      <c r="L17" s="8"/>
-      <c r="M17" s="7"/>
-      <c r="N17" s="9"/>
+      <c r="K17" s="9"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="10"/>
@@ -3075,10 +2683,7 @@
       <c r="H18" s="12"/>
       <c r="I18" s="12"/>
       <c r="J18" s="12"/>
-      <c r="K18" s="12"/>
-      <c r="L18" s="12"/>
-      <c r="M18" s="11"/>
-      <c r="N18" s="13"/>
+      <c r="K18" s="13"/>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="6"/>
@@ -3091,36 +2696,28 @@
       <c r="H19" s="8"/>
       <c r="I19" s="8"/>
       <c r="J19" s="8"/>
-      <c r="K19" s="8"/>
-      <c r="L19" s="8"/>
-      <c r="M19" s="7"/>
-      <c r="N19" s="9"/>
+      <c r="K19" s="9"/>
     </row>
     <row r="22" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="19" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="B22" s="20" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="C22" s="21"/>
       <c r="D22" s="21"/>
       <c r="E22" s="20" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="F22" s="21"/>
       <c r="G22" s="21"/>
       <c r="H22" s="21"/>
-      <c r="I22" s="21"/>
-      <c r="J22" s="22"/>
-      <c r="K22" s="20" t="s">
-        <v>46</v>
-      </c>
-      <c r="L22" s="21"/>
-      <c r="M22" s="20" t="s">
-        <v>47</v>
-      </c>
-      <c r="N22" s="21"/>
+      <c r="I22" s="22" t="s">
+        <v>43</v>
+      </c>
+      <c r="J22" s="21"/>
+      <c r="K22" s="21"/>
     </row>
     <row r="23" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="5" t="s">
@@ -3155,15 +2752,6 @@
       </c>
       <c r="K23" s="5" t="s">
         <v>25</v>
-      </c>
-      <c r="L23" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="M23" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="N23" s="5" t="s">
-        <v>28</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3177,10 +2765,7 @@
       <c r="H24" s="8"/>
       <c r="I24" s="8"/>
       <c r="J24" s="8"/>
-      <c r="K24" s="8"/>
-      <c r="L24" s="8"/>
-      <c r="M24" s="7"/>
-      <c r="N24" s="9"/>
+      <c r="K24" s="9"/>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="10"/>
@@ -3193,10 +2778,7 @@
       <c r="H25" s="12"/>
       <c r="I25" s="12"/>
       <c r="J25" s="12"/>
-      <c r="K25" s="12"/>
-      <c r="L25" s="12"/>
-      <c r="M25" s="11"/>
-      <c r="N25" s="13"/>
+      <c r="K25" s="13"/>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="6"/>
@@ -3209,10 +2791,7 @@
       <c r="H26" s="8"/>
       <c r="I26" s="8"/>
       <c r="J26" s="8"/>
-      <c r="K26" s="8"/>
-      <c r="L26" s="8"/>
-      <c r="M26" s="7"/>
-      <c r="N26" s="9"/>
+      <c r="K26" s="9"/>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="10"/>
@@ -3225,10 +2804,7 @@
       <c r="H27" s="12"/>
       <c r="I27" s="12"/>
       <c r="J27" s="12"/>
-      <c r="K27" s="12"/>
-      <c r="L27" s="12"/>
-      <c r="M27" s="11"/>
-      <c r="N27" s="13"/>
+      <c r="K27" s="13"/>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="6"/>
@@ -3241,10 +2817,7 @@
       <c r="H28" s="8"/>
       <c r="I28" s="8"/>
       <c r="J28" s="8"/>
-      <c r="K28" s="8"/>
-      <c r="L28" s="8"/>
-      <c r="M28" s="7"/>
-      <c r="N28" s="9"/>
+      <c r="K28" s="9"/>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="10"/>
@@ -3257,10 +2830,7 @@
       <c r="H29" s="12"/>
       <c r="I29" s="12"/>
       <c r="J29" s="12"/>
-      <c r="K29" s="12"/>
-      <c r="L29" s="12"/>
-      <c r="M29" s="11"/>
-      <c r="N29" s="13"/>
+      <c r="K29" s="13"/>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="6"/>
@@ -3273,10 +2843,7 @@
       <c r="H30" s="8"/>
       <c r="I30" s="8"/>
       <c r="J30" s="8"/>
-      <c r="K30" s="8"/>
-      <c r="L30" s="8"/>
-      <c r="M30" s="7"/>
-      <c r="N30" s="9"/>
+      <c r="K30" s="9"/>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="10"/>
@@ -3289,10 +2856,7 @@
       <c r="H31" s="12"/>
       <c r="I31" s="12"/>
       <c r="J31" s="12"/>
-      <c r="K31" s="12"/>
-      <c r="L31" s="12"/>
-      <c r="M31" s="11"/>
-      <c r="N31" s="13"/>
+      <c r="K31" s="13"/>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="6"/>
@@ -3305,10 +2869,7 @@
       <c r="H32" s="8"/>
       <c r="I32" s="8"/>
       <c r="J32" s="8"/>
-      <c r="K32" s="8"/>
-      <c r="L32" s="8"/>
-      <c r="M32" s="7"/>
-      <c r="N32" s="9"/>
+      <c r="K32" s="9"/>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="10"/>
@@ -3321,10 +2882,7 @@
       <c r="H33" s="12"/>
       <c r="I33" s="12"/>
       <c r="J33" s="12"/>
-      <c r="K33" s="12"/>
-      <c r="L33" s="12"/>
-      <c r="M33" s="11"/>
-      <c r="N33" s="13"/>
+      <c r="K33" s="13"/>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="6"/>
@@ -3337,10 +2895,7 @@
       <c r="H34" s="8"/>
       <c r="I34" s="8"/>
       <c r="J34" s="8"/>
-      <c r="K34" s="8"/>
-      <c r="L34" s="8"/>
-      <c r="M34" s="7"/>
-      <c r="N34" s="9"/>
+      <c r="K34" s="9"/>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="10"/>
@@ -3353,10 +2908,7 @@
       <c r="H35" s="12"/>
       <c r="I35" s="12"/>
       <c r="J35" s="12"/>
-      <c r="K35" s="12"/>
-      <c r="L35" s="12"/>
-      <c r="M35" s="11"/>
-      <c r="N35" s="13"/>
+      <c r="K35" s="13"/>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="6"/>
@@ -3369,10 +2921,7 @@
       <c r="H36" s="8"/>
       <c r="I36" s="8"/>
       <c r="J36" s="8"/>
-      <c r="K36" s="8"/>
-      <c r="L36" s="8"/>
-      <c r="M36" s="7"/>
-      <c r="N36" s="9"/>
+      <c r="K36" s="9"/>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="10"/>
@@ -3385,10 +2934,7 @@
       <c r="H37" s="12"/>
       <c r="I37" s="12"/>
       <c r="J37" s="12"/>
-      <c r="K37" s="12"/>
-      <c r="L37" s="12"/>
-      <c r="M37" s="11"/>
-      <c r="N37" s="13"/>
+      <c r="K37" s="13"/>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="6"/>
@@ -3401,36 +2947,28 @@
       <c r="H38" s="8"/>
       <c r="I38" s="8"/>
       <c r="J38" s="8"/>
-      <c r="K38" s="8"/>
-      <c r="L38" s="8"/>
-      <c r="M38" s="7"/>
-      <c r="N38" s="9"/>
+      <c r="K38" s="9"/>
     </row>
     <row r="41" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="19" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="B41" s="20" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="C41" s="21"/>
       <c r="D41" s="21"/>
       <c r="E41" s="20" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="F41" s="21"/>
       <c r="G41" s="21"/>
       <c r="H41" s="21"/>
-      <c r="I41" s="21"/>
-      <c r="J41" s="22"/>
-      <c r="K41" s="20" t="s">
-        <v>46</v>
-      </c>
-      <c r="L41" s="21"/>
-      <c r="M41" s="20" t="s">
-        <v>47</v>
-      </c>
-      <c r="N41" s="21"/>
+      <c r="I41" s="22" t="s">
+        <v>43</v>
+      </c>
+      <c r="J41" s="21"/>
+      <c r="K41" s="21"/>
     </row>
     <row r="42" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="5" t="s">
@@ -3465,15 +3003,6 @@
       </c>
       <c r="K42" s="5" t="s">
         <v>25</v>
-      </c>
-      <c r="L42" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="M42" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="N42" s="5" t="s">
-        <v>28</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3487,10 +3016,7 @@
       <c r="H43" s="8"/>
       <c r="I43" s="8"/>
       <c r="J43" s="8"/>
-      <c r="K43" s="8"/>
-      <c r="L43" s="8"/>
-      <c r="M43" s="7"/>
-      <c r="N43" s="9"/>
+      <c r="K43" s="9"/>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="10"/>
@@ -3503,10 +3029,7 @@
       <c r="H44" s="12"/>
       <c r="I44" s="12"/>
       <c r="J44" s="12"/>
-      <c r="K44" s="12"/>
-      <c r="L44" s="12"/>
-      <c r="M44" s="11"/>
-      <c r="N44" s="13"/>
+      <c r="K44" s="13"/>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="6"/>
@@ -3519,10 +3042,7 @@
       <c r="H45" s="8"/>
       <c r="I45" s="8"/>
       <c r="J45" s="8"/>
-      <c r="K45" s="8"/>
-      <c r="L45" s="8"/>
-      <c r="M45" s="7"/>
-      <c r="N45" s="9"/>
+      <c r="K45" s="9"/>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="10"/>
@@ -3535,10 +3055,7 @@
       <c r="H46" s="12"/>
       <c r="I46" s="12"/>
       <c r="J46" s="12"/>
-      <c r="K46" s="12"/>
-      <c r="L46" s="12"/>
-      <c r="M46" s="11"/>
-      <c r="N46" s="13"/>
+      <c r="K46" s="13"/>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="6"/>
@@ -3551,10 +3068,7 @@
       <c r="H47" s="8"/>
       <c r="I47" s="8"/>
       <c r="J47" s="8"/>
-      <c r="K47" s="8"/>
-      <c r="L47" s="8"/>
-      <c r="M47" s="7"/>
-      <c r="N47" s="9"/>
+      <c r="K47" s="9"/>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="10"/>
@@ -3567,10 +3081,7 @@
       <c r="H48" s="12"/>
       <c r="I48" s="12"/>
       <c r="J48" s="12"/>
-      <c r="K48" s="12"/>
-      <c r="L48" s="12"/>
-      <c r="M48" s="11"/>
-      <c r="N48" s="13"/>
+      <c r="K48" s="13"/>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="6"/>
@@ -3583,10 +3094,7 @@
       <c r="H49" s="8"/>
       <c r="I49" s="8"/>
       <c r="J49" s="8"/>
-      <c r="K49" s="8"/>
-      <c r="L49" s="8"/>
-      <c r="M49" s="7"/>
-      <c r="N49" s="9"/>
+      <c r="K49" s="9"/>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="10"/>
@@ -3599,10 +3107,7 @@
       <c r="H50" s="12"/>
       <c r="I50" s="12"/>
       <c r="J50" s="12"/>
-      <c r="K50" s="12"/>
-      <c r="L50" s="12"/>
-      <c r="M50" s="11"/>
-      <c r="N50" s="13"/>
+      <c r="K50" s="13"/>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="6"/>
@@ -3615,10 +3120,7 @@
       <c r="H51" s="8"/>
       <c r="I51" s="8"/>
       <c r="J51" s="8"/>
-      <c r="K51" s="8"/>
-      <c r="L51" s="8"/>
-      <c r="M51" s="7"/>
-      <c r="N51" s="9"/>
+      <c r="K51" s="9"/>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="10"/>
@@ -3631,10 +3133,7 @@
       <c r="H52" s="12"/>
       <c r="I52" s="12"/>
       <c r="J52" s="12"/>
-      <c r="K52" s="12"/>
-      <c r="L52" s="12"/>
-      <c r="M52" s="11"/>
-      <c r="N52" s="13"/>
+      <c r="K52" s="13"/>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="6"/>
@@ -3647,10 +3146,7 @@
       <c r="H53" s="8"/>
       <c r="I53" s="8"/>
       <c r="J53" s="8"/>
-      <c r="K53" s="8"/>
-      <c r="L53" s="8"/>
-      <c r="M53" s="7"/>
-      <c r="N53" s="9"/>
+      <c r="K53" s="9"/>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="10"/>
@@ -3663,10 +3159,7 @@
       <c r="H54" s="12"/>
       <c r="I54" s="12"/>
       <c r="J54" s="12"/>
-      <c r="K54" s="12"/>
-      <c r="L54" s="12"/>
-      <c r="M54" s="11"/>
-      <c r="N54" s="13"/>
+      <c r="K54" s="13"/>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="6"/>
@@ -3679,10 +3172,7 @@
       <c r="H55" s="8"/>
       <c r="I55" s="8"/>
       <c r="J55" s="8"/>
-      <c r="K55" s="8"/>
-      <c r="L55" s="8"/>
-      <c r="M55" s="7"/>
-      <c r="N55" s="9"/>
+      <c r="K55" s="9"/>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="10"/>
@@ -3695,10 +3185,7 @@
       <c r="H56" s="12"/>
       <c r="I56" s="12"/>
       <c r="J56" s="12"/>
-      <c r="K56" s="12"/>
-      <c r="L56" s="12"/>
-      <c r="M56" s="11"/>
-      <c r="N56" s="13"/>
+      <c r="K56" s="13"/>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="6"/>
@@ -3711,36 +3198,28 @@
       <c r="H57" s="8"/>
       <c r="I57" s="8"/>
       <c r="J57" s="8"/>
-      <c r="K57" s="8"/>
-      <c r="L57" s="8"/>
-      <c r="M57" s="7"/>
-      <c r="N57" s="9"/>
+      <c r="K57" s="9"/>
     </row>
     <row r="60" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A60" s="19" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="B60" s="20" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="C60" s="21"/>
       <c r="D60" s="21"/>
       <c r="E60" s="20" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="F60" s="21"/>
       <c r="G60" s="21"/>
       <c r="H60" s="21"/>
-      <c r="I60" s="21"/>
-      <c r="J60" s="22"/>
-      <c r="K60" s="20" t="s">
-        <v>46</v>
-      </c>
-      <c r="L60" s="21"/>
-      <c r="M60" s="20" t="s">
-        <v>47</v>
-      </c>
-      <c r="N60" s="21"/>
+      <c r="I60" s="22" t="s">
+        <v>43</v>
+      </c>
+      <c r="J60" s="21"/>
+      <c r="K60" s="21"/>
     </row>
     <row r="61" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A61" s="5" t="s">
@@ -3775,15 +3254,6 @@
       </c>
       <c r="K61" s="5" t="s">
         <v>25</v>
-      </c>
-      <c r="L61" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="M61" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="N61" s="5" t="s">
-        <v>28</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3797,10 +3267,7 @@
       <c r="H62" s="8"/>
       <c r="I62" s="8"/>
       <c r="J62" s="8"/>
-      <c r="K62" s="8"/>
-      <c r="L62" s="8"/>
-      <c r="M62" s="7"/>
-      <c r="N62" s="9"/>
+      <c r="K62" s="9"/>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="10"/>
@@ -3813,10 +3280,7 @@
       <c r="H63" s="12"/>
       <c r="I63" s="12"/>
       <c r="J63" s="12"/>
-      <c r="K63" s="12"/>
-      <c r="L63" s="12"/>
-      <c r="M63" s="11"/>
-      <c r="N63" s="13"/>
+      <c r="K63" s="13"/>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="6"/>
@@ -3829,10 +3293,7 @@
       <c r="H64" s="8"/>
       <c r="I64" s="8"/>
       <c r="J64" s="8"/>
-      <c r="K64" s="8"/>
-      <c r="L64" s="8"/>
-      <c r="M64" s="7"/>
-      <c r="N64" s="9"/>
+      <c r="K64" s="9"/>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="10"/>
@@ -3845,10 +3306,7 @@
       <c r="H65" s="12"/>
       <c r="I65" s="12"/>
       <c r="J65" s="12"/>
-      <c r="K65" s="12"/>
-      <c r="L65" s="12"/>
-      <c r="M65" s="11"/>
-      <c r="N65" s="13"/>
+      <c r="K65" s="13"/>
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="6"/>
@@ -3861,10 +3319,7 @@
       <c r="H66" s="8"/>
       <c r="I66" s="8"/>
       <c r="J66" s="8"/>
-      <c r="K66" s="8"/>
-      <c r="L66" s="8"/>
-      <c r="M66" s="7"/>
-      <c r="N66" s="9"/>
+      <c r="K66" s="9"/>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="10"/>
@@ -3877,10 +3332,7 @@
       <c r="H67" s="12"/>
       <c r="I67" s="12"/>
       <c r="J67" s="12"/>
-      <c r="K67" s="12"/>
-      <c r="L67" s="12"/>
-      <c r="M67" s="11"/>
-      <c r="N67" s="13"/>
+      <c r="K67" s="13"/>
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="6"/>
@@ -3893,10 +3345,7 @@
       <c r="H68" s="8"/>
       <c r="I68" s="8"/>
       <c r="J68" s="8"/>
-      <c r="K68" s="8"/>
-      <c r="L68" s="8"/>
-      <c r="M68" s="7"/>
-      <c r="N68" s="9"/>
+      <c r="K68" s="9"/>
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="10"/>
@@ -3909,10 +3358,7 @@
       <c r="H69" s="12"/>
       <c r="I69" s="12"/>
       <c r="J69" s="12"/>
-      <c r="K69" s="12"/>
-      <c r="L69" s="12"/>
-      <c r="M69" s="11"/>
-      <c r="N69" s="13"/>
+      <c r="K69" s="13"/>
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="6"/>
@@ -3925,10 +3371,7 @@
       <c r="H70" s="8"/>
       <c r="I70" s="8"/>
       <c r="J70" s="8"/>
-      <c r="K70" s="8"/>
-      <c r="L70" s="8"/>
-      <c r="M70" s="7"/>
-      <c r="N70" s="9"/>
+      <c r="K70" s="9"/>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="10"/>
@@ -3941,10 +3384,7 @@
       <c r="H71" s="12"/>
       <c r="I71" s="12"/>
       <c r="J71" s="12"/>
-      <c r="K71" s="12"/>
-      <c r="L71" s="12"/>
-      <c r="M71" s="11"/>
-      <c r="N71" s="13"/>
+      <c r="K71" s="13"/>
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="6"/>
@@ -3957,10 +3397,7 @@
       <c r="H72" s="8"/>
       <c r="I72" s="8"/>
       <c r="J72" s="8"/>
-      <c r="K72" s="8"/>
-      <c r="L72" s="8"/>
-      <c r="M72" s="7"/>
-      <c r="N72" s="9"/>
+      <c r="K72" s="9"/>
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="10"/>
@@ -3973,10 +3410,7 @@
       <c r="H73" s="12"/>
       <c r="I73" s="12"/>
       <c r="J73" s="12"/>
-      <c r="K73" s="12"/>
-      <c r="L73" s="12"/>
-      <c r="M73" s="11"/>
-      <c r="N73" s="13"/>
+      <c r="K73" s="13"/>
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="6"/>
@@ -3989,10 +3423,7 @@
       <c r="H74" s="8"/>
       <c r="I74" s="8"/>
       <c r="J74" s="8"/>
-      <c r="K74" s="8"/>
-      <c r="L74" s="8"/>
-      <c r="M74" s="7"/>
-      <c r="N74" s="9"/>
+      <c r="K74" s="9"/>
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="10"/>
@@ -4005,10 +3436,7 @@
       <c r="H75" s="12"/>
       <c r="I75" s="12"/>
       <c r="J75" s="12"/>
-      <c r="K75" s="12"/>
-      <c r="L75" s="12"/>
-      <c r="M75" s="11"/>
-      <c r="N75" s="13"/>
+      <c r="K75" s="13"/>
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="6"/>
@@ -4021,22 +3449,19 @@
       <c r="H76" s="8"/>
       <c r="I76" s="8"/>
       <c r="J76" s="8"/>
-      <c r="K76" s="8"/>
-      <c r="L76" s="8"/>
-      <c r="M76" s="7"/>
-      <c r="N76" s="9"/>
+      <c r="K76" s="9"/>
     </row>
   </sheetData>
   <mergeCells count="9">
     <mergeCell ref="F1:H1"/>
     <mergeCell ref="C3:D3"/>
-    <mergeCell ref="F3:I3"/>
+    <mergeCell ref="F3:H3"/>
     <mergeCell ref="C22:D22"/>
-    <mergeCell ref="F22:I22"/>
+    <mergeCell ref="F22:H22"/>
     <mergeCell ref="C41:D41"/>
-    <mergeCell ref="F41:I41"/>
+    <mergeCell ref="F41:H41"/>
     <mergeCell ref="C60:D60"/>
-    <mergeCell ref="F60:I60"/>
+    <mergeCell ref="F60:H60"/>
   </mergeCells>
   <conditionalFormatting sqref="A5:A19">
     <cfRule type="expression" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
@@ -4094,8 +3519,8 @@
       <formula>OR($A62="Accesorios",$A62="Vuelta a la calma")</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="20">
-    <dataValidation allowBlank="true" error="Un número de 0 a 10." errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="L3 N3 L22 N22 L41 N41 L60 N60" type="decimal">
+  <dataValidations count="15">
+    <dataValidation allowBlank="true" error="Un número de 0 a 10." errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="J3:K3 J22:K22 J41:K41 J60:K60" type="decimal">
       <formula1>0</formula1>
       <formula2>10</formula2>
     </dataValidation>
@@ -4123,10 +3548,6 @@
       <formula1>"Sí"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" error="Minutos del aeróbico (0,5 = 30 s)." errorStyle="stop" errorTitle="Minutos" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="K5:K19 K24:K38 K43:K57 K62:K76" type="decimal">
-      <formula1>0</formula1>
-      <formula2>600</formula2>
-    </dataValidation>
     <dataValidation allowBlank="true" error="Elige un día del desplegable." errorStyle="stop" errorTitle="Día" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C3" type="list">
       <formula1>"Lunes,Martes,Miércoles,Jueves,Viernes,Sábado,Domingo"</formula1>
       <formula2>0</formula2>
@@ -4135,10 +3556,6 @@
       <formula1>"Activación,P. Principal,Aeróbico,Accesorios,Vuelta a la calma"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" error="Elige una zona del desplegable." errorStyle="stop" errorTitle="Zona" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="L5:L19" type="list">
-      <formula1>"Z1,Z2,Z3,Z4,Z5"</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
     <dataValidation allowBlank="true" error="Elige un día del desplegable." errorStyle="stop" errorTitle="Día" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C22" type="list">
       <formula1>"Lunes,Martes,Miércoles,Jueves,Viernes,Sábado,Domingo"</formula1>
       <formula2>0</formula2>
@@ -4147,10 +3564,6 @@
       <formula1>"Activación,P. Principal,Aeróbico,Accesorios,Vuelta a la calma"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" error="Elige una zona del desplegable." errorStyle="stop" errorTitle="Zona" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="L24:L38" type="list">
-      <formula1>"Z1,Z2,Z3,Z4,Z5"</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
     <dataValidation allowBlank="true" error="Elige un día del desplegable." errorStyle="stop" errorTitle="Día" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C41" type="list">
       <formula1>"Lunes,Martes,Miércoles,Jueves,Viernes,Sábado,Domingo"</formula1>
       <formula2>0</formula2>
@@ -4159,20 +3572,12 @@
       <formula1>"Activación,P. Principal,Aeróbico,Accesorios,Vuelta a la calma"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" error="Elige una zona del desplegable." errorStyle="stop" errorTitle="Zona" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="L43:L57" type="list">
-      <formula1>"Z1,Z2,Z3,Z4,Z5"</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
     <dataValidation allowBlank="true" error="Elige un día del desplegable." errorStyle="stop" errorTitle="Día" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C60" type="list">
       <formula1>"Lunes,Martes,Miércoles,Jueves,Viernes,Sábado,Domingo"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Elige un bloque del desplegable." errorStyle="stop" errorTitle="Bloque" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="A62:A76" type="list">
       <formula1>"Activación,P. Principal,Aeróbico,Accesorios,Vuelta a la calma"</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-    <dataValidation allowBlank="true" error="Elige una zona del desplegable." errorStyle="stop" errorTitle="Zona" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="L62:L76" type="list">
-      <formula1>"Z1,Z2,Z3,Z4,Z5"</formula1>
       <formula2>0</formula2>
     </dataValidation>
   </dataValidations>
@@ -4192,25 +3597,23 @@
     <tabColor rgb="FF2E8B6E"/>
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:N76"/>
+  <dimension ref="A1:K76"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="17"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="34"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="0" width="8"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="13"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="6" style="0" width="9"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="7"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="9" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="7"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="20"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="0" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="40"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="14" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="B1" s="23" t="n">
         <f aca="false">'Semana 2'!B1+7</f>
@@ -4221,7 +3624,7 @@
         <v>al 22/11</v>
       </c>
       <c r="E1" s="17" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="F1" s="18"/>
       <c r="G1" s="18"/>
@@ -4229,29 +3632,24 @@
     </row>
     <row r="3" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="19" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="B3" s="20" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="C3" s="21"/>
       <c r="D3" s="21"/>
       <c r="E3" s="20" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="F3" s="21"/>
       <c r="G3" s="21"/>
       <c r="H3" s="21"/>
-      <c r="I3" s="21"/>
-      <c r="J3" s="22"/>
-      <c r="K3" s="20" t="s">
-        <v>46</v>
-      </c>
-      <c r="L3" s="21"/>
-      <c r="M3" s="20" t="s">
-        <v>47</v>
-      </c>
-      <c r="N3" s="21"/>
+      <c r="I3" s="22" t="s">
+        <v>43</v>
+      </c>
+      <c r="J3" s="21"/>
+      <c r="K3" s="21"/>
     </row>
     <row r="4" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="5" t="s">
@@ -4286,15 +3684,6 @@
       </c>
       <c r="K4" s="5" t="s">
         <v>25</v>
-      </c>
-      <c r="L4" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="M4" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="N4" s="5" t="s">
-        <v>28</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4308,10 +3697,7 @@
       <c r="H5" s="8"/>
       <c r="I5" s="8"/>
       <c r="J5" s="8"/>
-      <c r="K5" s="8"/>
-      <c r="L5" s="8"/>
-      <c r="M5" s="7"/>
-      <c r="N5" s="9"/>
+      <c r="K5" s="9"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="10"/>
@@ -4324,10 +3710,7 @@
       <c r="H6" s="12"/>
       <c r="I6" s="12"/>
       <c r="J6" s="12"/>
-      <c r="K6" s="12"/>
-      <c r="L6" s="12"/>
-      <c r="M6" s="11"/>
-      <c r="N6" s="13"/>
+      <c r="K6" s="13"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="6"/>
@@ -4340,10 +3723,7 @@
       <c r="H7" s="8"/>
       <c r="I7" s="8"/>
       <c r="J7" s="8"/>
-      <c r="K7" s="8"/>
-      <c r="L7" s="8"/>
-      <c r="M7" s="7"/>
-      <c r="N7" s="9"/>
+      <c r="K7" s="9"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="10"/>
@@ -4356,10 +3736,7 @@
       <c r="H8" s="12"/>
       <c r="I8" s="12"/>
       <c r="J8" s="12"/>
-      <c r="K8" s="12"/>
-      <c r="L8" s="12"/>
-      <c r="M8" s="11"/>
-      <c r="N8" s="13"/>
+      <c r="K8" s="13"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="6"/>
@@ -4372,10 +3749,7 @@
       <c r="H9" s="8"/>
       <c r="I9" s="8"/>
       <c r="J9" s="8"/>
-      <c r="K9" s="8"/>
-      <c r="L9" s="8"/>
-      <c r="M9" s="7"/>
-      <c r="N9" s="9"/>
+      <c r="K9" s="9"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="10"/>
@@ -4388,10 +3762,7 @@
       <c r="H10" s="12"/>
       <c r="I10" s="12"/>
       <c r="J10" s="12"/>
-      <c r="K10" s="12"/>
-      <c r="L10" s="12"/>
-      <c r="M10" s="11"/>
-      <c r="N10" s="13"/>
+      <c r="K10" s="13"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="6"/>
@@ -4404,10 +3775,7 @@
       <c r="H11" s="8"/>
       <c r="I11" s="8"/>
       <c r="J11" s="8"/>
-      <c r="K11" s="8"/>
-      <c r="L11" s="8"/>
-      <c r="M11" s="7"/>
-      <c r="N11" s="9"/>
+      <c r="K11" s="9"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="10"/>
@@ -4420,10 +3788,7 @@
       <c r="H12" s="12"/>
       <c r="I12" s="12"/>
       <c r="J12" s="12"/>
-      <c r="K12" s="12"/>
-      <c r="L12" s="12"/>
-      <c r="M12" s="11"/>
-      <c r="N12" s="13"/>
+      <c r="K12" s="13"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="6"/>
@@ -4436,10 +3801,7 @@
       <c r="H13" s="8"/>
       <c r="I13" s="8"/>
       <c r="J13" s="8"/>
-      <c r="K13" s="8"/>
-      <c r="L13" s="8"/>
-      <c r="M13" s="7"/>
-      <c r="N13" s="9"/>
+      <c r="K13" s="9"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="10"/>
@@ -4452,10 +3814,7 @@
       <c r="H14" s="12"/>
       <c r="I14" s="12"/>
       <c r="J14" s="12"/>
-      <c r="K14" s="12"/>
-      <c r="L14" s="12"/>
-      <c r="M14" s="11"/>
-      <c r="N14" s="13"/>
+      <c r="K14" s="13"/>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="6"/>
@@ -4468,10 +3827,7 @@
       <c r="H15" s="8"/>
       <c r="I15" s="8"/>
       <c r="J15" s="8"/>
-      <c r="K15" s="8"/>
-      <c r="L15" s="8"/>
-      <c r="M15" s="7"/>
-      <c r="N15" s="9"/>
+      <c r="K15" s="9"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="10"/>
@@ -4484,10 +3840,7 @@
       <c r="H16" s="12"/>
       <c r="I16" s="12"/>
       <c r="J16" s="12"/>
-      <c r="K16" s="12"/>
-      <c r="L16" s="12"/>
-      <c r="M16" s="11"/>
-      <c r="N16" s="13"/>
+      <c r="K16" s="13"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="6"/>
@@ -4500,10 +3853,7 @@
       <c r="H17" s="8"/>
       <c r="I17" s="8"/>
       <c r="J17" s="8"/>
-      <c r="K17" s="8"/>
-      <c r="L17" s="8"/>
-      <c r="M17" s="7"/>
-      <c r="N17" s="9"/>
+      <c r="K17" s="9"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="10"/>
@@ -4516,10 +3866,7 @@
       <c r="H18" s="12"/>
       <c r="I18" s="12"/>
       <c r="J18" s="12"/>
-      <c r="K18" s="12"/>
-      <c r="L18" s="12"/>
-      <c r="M18" s="11"/>
-      <c r="N18" s="13"/>
+      <c r="K18" s="13"/>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="6"/>
@@ -4532,36 +3879,28 @@
       <c r="H19" s="8"/>
       <c r="I19" s="8"/>
       <c r="J19" s="8"/>
-      <c r="K19" s="8"/>
-      <c r="L19" s="8"/>
-      <c r="M19" s="7"/>
-      <c r="N19" s="9"/>
+      <c r="K19" s="9"/>
     </row>
     <row r="22" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="19" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="B22" s="20" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="C22" s="21"/>
       <c r="D22" s="21"/>
       <c r="E22" s="20" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="F22" s="21"/>
       <c r="G22" s="21"/>
       <c r="H22" s="21"/>
-      <c r="I22" s="21"/>
-      <c r="J22" s="22"/>
-      <c r="K22" s="20" t="s">
-        <v>46</v>
-      </c>
-      <c r="L22" s="21"/>
-      <c r="M22" s="20" t="s">
-        <v>47</v>
-      </c>
-      <c r="N22" s="21"/>
+      <c r="I22" s="22" t="s">
+        <v>43</v>
+      </c>
+      <c r="J22" s="21"/>
+      <c r="K22" s="21"/>
     </row>
     <row r="23" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="5" t="s">
@@ -4596,15 +3935,6 @@
       </c>
       <c r="K23" s="5" t="s">
         <v>25</v>
-      </c>
-      <c r="L23" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="M23" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="N23" s="5" t="s">
-        <v>28</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4618,10 +3948,7 @@
       <c r="H24" s="8"/>
       <c r="I24" s="8"/>
       <c r="J24" s="8"/>
-      <c r="K24" s="8"/>
-      <c r="L24" s="8"/>
-      <c r="M24" s="7"/>
-      <c r="N24" s="9"/>
+      <c r="K24" s="9"/>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="10"/>
@@ -4634,10 +3961,7 @@
       <c r="H25" s="12"/>
       <c r="I25" s="12"/>
       <c r="J25" s="12"/>
-      <c r="K25" s="12"/>
-      <c r="L25" s="12"/>
-      <c r="M25" s="11"/>
-      <c r="N25" s="13"/>
+      <c r="K25" s="13"/>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="6"/>
@@ -4650,10 +3974,7 @@
       <c r="H26" s="8"/>
       <c r="I26" s="8"/>
       <c r="J26" s="8"/>
-      <c r="K26" s="8"/>
-      <c r="L26" s="8"/>
-      <c r="M26" s="7"/>
-      <c r="N26" s="9"/>
+      <c r="K26" s="9"/>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="10"/>
@@ -4666,10 +3987,7 @@
       <c r="H27" s="12"/>
       <c r="I27" s="12"/>
       <c r="J27" s="12"/>
-      <c r="K27" s="12"/>
-      <c r="L27" s="12"/>
-      <c r="M27" s="11"/>
-      <c r="N27" s="13"/>
+      <c r="K27" s="13"/>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="6"/>
@@ -4682,10 +4000,7 @@
       <c r="H28" s="8"/>
       <c r="I28" s="8"/>
       <c r="J28" s="8"/>
-      <c r="K28" s="8"/>
-      <c r="L28" s="8"/>
-      <c r="M28" s="7"/>
-      <c r="N28" s="9"/>
+      <c r="K28" s="9"/>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="10"/>
@@ -4698,10 +4013,7 @@
       <c r="H29" s="12"/>
       <c r="I29" s="12"/>
       <c r="J29" s="12"/>
-      <c r="K29" s="12"/>
-      <c r="L29" s="12"/>
-      <c r="M29" s="11"/>
-      <c r="N29" s="13"/>
+      <c r="K29" s="13"/>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="6"/>
@@ -4714,10 +4026,7 @@
       <c r="H30" s="8"/>
       <c r="I30" s="8"/>
       <c r="J30" s="8"/>
-      <c r="K30" s="8"/>
-      <c r="L30" s="8"/>
-      <c r="M30" s="7"/>
-      <c r="N30" s="9"/>
+      <c r="K30" s="9"/>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="10"/>
@@ -4730,10 +4039,7 @@
       <c r="H31" s="12"/>
       <c r="I31" s="12"/>
       <c r="J31" s="12"/>
-      <c r="K31" s="12"/>
-      <c r="L31" s="12"/>
-      <c r="M31" s="11"/>
-      <c r="N31" s="13"/>
+      <c r="K31" s="13"/>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="6"/>
@@ -4746,10 +4052,7 @@
       <c r="H32" s="8"/>
       <c r="I32" s="8"/>
       <c r="J32" s="8"/>
-      <c r="K32" s="8"/>
-      <c r="L32" s="8"/>
-      <c r="M32" s="7"/>
-      <c r="N32" s="9"/>
+      <c r="K32" s="9"/>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="10"/>
@@ -4762,10 +4065,7 @@
       <c r="H33" s="12"/>
       <c r="I33" s="12"/>
       <c r="J33" s="12"/>
-      <c r="K33" s="12"/>
-      <c r="L33" s="12"/>
-      <c r="M33" s="11"/>
-      <c r="N33" s="13"/>
+      <c r="K33" s="13"/>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="6"/>
@@ -4778,10 +4078,7 @@
       <c r="H34" s="8"/>
       <c r="I34" s="8"/>
       <c r="J34" s="8"/>
-      <c r="K34" s="8"/>
-      <c r="L34" s="8"/>
-      <c r="M34" s="7"/>
-      <c r="N34" s="9"/>
+      <c r="K34" s="9"/>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="10"/>
@@ -4794,10 +4091,7 @@
       <c r="H35" s="12"/>
       <c r="I35" s="12"/>
       <c r="J35" s="12"/>
-      <c r="K35" s="12"/>
-      <c r="L35" s="12"/>
-      <c r="M35" s="11"/>
-      <c r="N35" s="13"/>
+      <c r="K35" s="13"/>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="6"/>
@@ -4810,10 +4104,7 @@
       <c r="H36" s="8"/>
       <c r="I36" s="8"/>
       <c r="J36" s="8"/>
-      <c r="K36" s="8"/>
-      <c r="L36" s="8"/>
-      <c r="M36" s="7"/>
-      <c r="N36" s="9"/>
+      <c r="K36" s="9"/>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="10"/>
@@ -4826,10 +4117,7 @@
       <c r="H37" s="12"/>
       <c r="I37" s="12"/>
       <c r="J37" s="12"/>
-      <c r="K37" s="12"/>
-      <c r="L37" s="12"/>
-      <c r="M37" s="11"/>
-      <c r="N37" s="13"/>
+      <c r="K37" s="13"/>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="6"/>
@@ -4842,36 +4130,28 @@
       <c r="H38" s="8"/>
       <c r="I38" s="8"/>
       <c r="J38" s="8"/>
-      <c r="K38" s="8"/>
-      <c r="L38" s="8"/>
-      <c r="M38" s="7"/>
-      <c r="N38" s="9"/>
+      <c r="K38" s="9"/>
     </row>
     <row r="41" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="19" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="B41" s="20" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="C41" s="21"/>
       <c r="D41" s="21"/>
       <c r="E41" s="20" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="F41" s="21"/>
       <c r="G41" s="21"/>
       <c r="H41" s="21"/>
-      <c r="I41" s="21"/>
-      <c r="J41" s="22"/>
-      <c r="K41" s="20" t="s">
-        <v>46</v>
-      </c>
-      <c r="L41" s="21"/>
-      <c r="M41" s="20" t="s">
-        <v>47</v>
-      </c>
-      <c r="N41" s="21"/>
+      <c r="I41" s="22" t="s">
+        <v>43</v>
+      </c>
+      <c r="J41" s="21"/>
+      <c r="K41" s="21"/>
     </row>
     <row r="42" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="5" t="s">
@@ -4906,15 +4186,6 @@
       </c>
       <c r="K42" s="5" t="s">
         <v>25</v>
-      </c>
-      <c r="L42" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="M42" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="N42" s="5" t="s">
-        <v>28</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4928,10 +4199,7 @@
       <c r="H43" s="8"/>
       <c r="I43" s="8"/>
       <c r="J43" s="8"/>
-      <c r="K43" s="8"/>
-      <c r="L43" s="8"/>
-      <c r="M43" s="7"/>
-      <c r="N43" s="9"/>
+      <c r="K43" s="9"/>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="10"/>
@@ -4944,10 +4212,7 @@
       <c r="H44" s="12"/>
       <c r="I44" s="12"/>
       <c r="J44" s="12"/>
-      <c r="K44" s="12"/>
-      <c r="L44" s="12"/>
-      <c r="M44" s="11"/>
-      <c r="N44" s="13"/>
+      <c r="K44" s="13"/>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="6"/>
@@ -4960,10 +4225,7 @@
       <c r="H45" s="8"/>
       <c r="I45" s="8"/>
       <c r="J45" s="8"/>
-      <c r="K45" s="8"/>
-      <c r="L45" s="8"/>
-      <c r="M45" s="7"/>
-      <c r="N45" s="9"/>
+      <c r="K45" s="9"/>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="10"/>
@@ -4976,10 +4238,7 @@
       <c r="H46" s="12"/>
       <c r="I46" s="12"/>
       <c r="J46" s="12"/>
-      <c r="K46" s="12"/>
-      <c r="L46" s="12"/>
-      <c r="M46" s="11"/>
-      <c r="N46" s="13"/>
+      <c r="K46" s="13"/>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="6"/>
@@ -4992,10 +4251,7 @@
       <c r="H47" s="8"/>
       <c r="I47" s="8"/>
       <c r="J47" s="8"/>
-      <c r="K47" s="8"/>
-      <c r="L47" s="8"/>
-      <c r="M47" s="7"/>
-      <c r="N47" s="9"/>
+      <c r="K47" s="9"/>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="10"/>
@@ -5008,10 +4264,7 @@
       <c r="H48" s="12"/>
       <c r="I48" s="12"/>
       <c r="J48" s="12"/>
-      <c r="K48" s="12"/>
-      <c r="L48" s="12"/>
-      <c r="M48" s="11"/>
-      <c r="N48" s="13"/>
+      <c r="K48" s="13"/>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="6"/>
@@ -5024,10 +4277,7 @@
       <c r="H49" s="8"/>
       <c r="I49" s="8"/>
       <c r="J49" s="8"/>
-      <c r="K49" s="8"/>
-      <c r="L49" s="8"/>
-      <c r="M49" s="7"/>
-      <c r="N49" s="9"/>
+      <c r="K49" s="9"/>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="10"/>
@@ -5040,10 +4290,7 @@
       <c r="H50" s="12"/>
       <c r="I50" s="12"/>
       <c r="J50" s="12"/>
-      <c r="K50" s="12"/>
-      <c r="L50" s="12"/>
-      <c r="M50" s="11"/>
-      <c r="N50" s="13"/>
+      <c r="K50" s="13"/>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="6"/>
@@ -5056,10 +4303,7 @@
       <c r="H51" s="8"/>
       <c r="I51" s="8"/>
       <c r="J51" s="8"/>
-      <c r="K51" s="8"/>
-      <c r="L51" s="8"/>
-      <c r="M51" s="7"/>
-      <c r="N51" s="9"/>
+      <c r="K51" s="9"/>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="10"/>
@@ -5072,10 +4316,7 @@
       <c r="H52" s="12"/>
       <c r="I52" s="12"/>
       <c r="J52" s="12"/>
-      <c r="K52" s="12"/>
-      <c r="L52" s="12"/>
-      <c r="M52" s="11"/>
-      <c r="N52" s="13"/>
+      <c r="K52" s="13"/>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="6"/>
@@ -5088,10 +4329,7 @@
       <c r="H53" s="8"/>
       <c r="I53" s="8"/>
       <c r="J53" s="8"/>
-      <c r="K53" s="8"/>
-      <c r="L53" s="8"/>
-      <c r="M53" s="7"/>
-      <c r="N53" s="9"/>
+      <c r="K53" s="9"/>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="10"/>
@@ -5104,10 +4342,7 @@
       <c r="H54" s="12"/>
       <c r="I54" s="12"/>
       <c r="J54" s="12"/>
-      <c r="K54" s="12"/>
-      <c r="L54" s="12"/>
-      <c r="M54" s="11"/>
-      <c r="N54" s="13"/>
+      <c r="K54" s="13"/>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="6"/>
@@ -5120,10 +4355,7 @@
       <c r="H55" s="8"/>
       <c r="I55" s="8"/>
       <c r="J55" s="8"/>
-      <c r="K55" s="8"/>
-      <c r="L55" s="8"/>
-      <c r="M55" s="7"/>
-      <c r="N55" s="9"/>
+      <c r="K55" s="9"/>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="10"/>
@@ -5136,10 +4368,7 @@
       <c r="H56" s="12"/>
       <c r="I56" s="12"/>
       <c r="J56" s="12"/>
-      <c r="K56" s="12"/>
-      <c r="L56" s="12"/>
-      <c r="M56" s="11"/>
-      <c r="N56" s="13"/>
+      <c r="K56" s="13"/>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="6"/>
@@ -5152,36 +4381,28 @@
       <c r="H57" s="8"/>
       <c r="I57" s="8"/>
       <c r="J57" s="8"/>
-      <c r="K57" s="8"/>
-      <c r="L57" s="8"/>
-      <c r="M57" s="7"/>
-      <c r="N57" s="9"/>
+      <c r="K57" s="9"/>
     </row>
     <row r="60" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A60" s="19" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="B60" s="20" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="C60" s="21"/>
       <c r="D60" s="21"/>
       <c r="E60" s="20" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="F60" s="21"/>
       <c r="G60" s="21"/>
       <c r="H60" s="21"/>
-      <c r="I60" s="21"/>
-      <c r="J60" s="22"/>
-      <c r="K60" s="20" t="s">
-        <v>46</v>
-      </c>
-      <c r="L60" s="21"/>
-      <c r="M60" s="20" t="s">
-        <v>47</v>
-      </c>
-      <c r="N60" s="21"/>
+      <c r="I60" s="22" t="s">
+        <v>43</v>
+      </c>
+      <c r="J60" s="21"/>
+      <c r="K60" s="21"/>
     </row>
     <row r="61" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A61" s="5" t="s">
@@ -5216,15 +4437,6 @@
       </c>
       <c r="K61" s="5" t="s">
         <v>25</v>
-      </c>
-      <c r="L61" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="M61" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="N61" s="5" t="s">
-        <v>28</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5238,10 +4450,7 @@
       <c r="H62" s="8"/>
       <c r="I62" s="8"/>
       <c r="J62" s="8"/>
-      <c r="K62" s="8"/>
-      <c r="L62" s="8"/>
-      <c r="M62" s="7"/>
-      <c r="N62" s="9"/>
+      <c r="K62" s="9"/>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="10"/>
@@ -5254,10 +4463,7 @@
       <c r="H63" s="12"/>
       <c r="I63" s="12"/>
       <c r="J63" s="12"/>
-      <c r="K63" s="12"/>
-      <c r="L63" s="12"/>
-      <c r="M63" s="11"/>
-      <c r="N63" s="13"/>
+      <c r="K63" s="13"/>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="6"/>
@@ -5270,10 +4476,7 @@
       <c r="H64" s="8"/>
       <c r="I64" s="8"/>
       <c r="J64" s="8"/>
-      <c r="K64" s="8"/>
-      <c r="L64" s="8"/>
-      <c r="M64" s="7"/>
-      <c r="N64" s="9"/>
+      <c r="K64" s="9"/>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="10"/>
@@ -5286,10 +4489,7 @@
       <c r="H65" s="12"/>
       <c r="I65" s="12"/>
       <c r="J65" s="12"/>
-      <c r="K65" s="12"/>
-      <c r="L65" s="12"/>
-      <c r="M65" s="11"/>
-      <c r="N65" s="13"/>
+      <c r="K65" s="13"/>
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="6"/>
@@ -5302,10 +4502,7 @@
       <c r="H66" s="8"/>
       <c r="I66" s="8"/>
       <c r="J66" s="8"/>
-      <c r="K66" s="8"/>
-      <c r="L66" s="8"/>
-      <c r="M66" s="7"/>
-      <c r="N66" s="9"/>
+      <c r="K66" s="9"/>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="10"/>
@@ -5318,10 +4515,7 @@
       <c r="H67" s="12"/>
       <c r="I67" s="12"/>
       <c r="J67" s="12"/>
-      <c r="K67" s="12"/>
-      <c r="L67" s="12"/>
-      <c r="M67" s="11"/>
-      <c r="N67" s="13"/>
+      <c r="K67" s="13"/>
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="6"/>
@@ -5334,10 +4528,7 @@
       <c r="H68" s="8"/>
       <c r="I68" s="8"/>
       <c r="J68" s="8"/>
-      <c r="K68" s="8"/>
-      <c r="L68" s="8"/>
-      <c r="M68" s="7"/>
-      <c r="N68" s="9"/>
+      <c r="K68" s="9"/>
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="10"/>
@@ -5350,10 +4541,7 @@
       <c r="H69" s="12"/>
       <c r="I69" s="12"/>
       <c r="J69" s="12"/>
-      <c r="K69" s="12"/>
-      <c r="L69" s="12"/>
-      <c r="M69" s="11"/>
-      <c r="N69" s="13"/>
+      <c r="K69" s="13"/>
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="6"/>
@@ -5366,10 +4554,7 @@
       <c r="H70" s="8"/>
       <c r="I70" s="8"/>
       <c r="J70" s="8"/>
-      <c r="K70" s="8"/>
-      <c r="L70" s="8"/>
-      <c r="M70" s="7"/>
-      <c r="N70" s="9"/>
+      <c r="K70" s="9"/>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="10"/>
@@ -5382,10 +4567,7 @@
       <c r="H71" s="12"/>
       <c r="I71" s="12"/>
       <c r="J71" s="12"/>
-      <c r="K71" s="12"/>
-      <c r="L71" s="12"/>
-      <c r="M71" s="11"/>
-      <c r="N71" s="13"/>
+      <c r="K71" s="13"/>
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="6"/>
@@ -5398,10 +4580,7 @@
       <c r="H72" s="8"/>
       <c r="I72" s="8"/>
       <c r="J72" s="8"/>
-      <c r="K72" s="8"/>
-      <c r="L72" s="8"/>
-      <c r="M72" s="7"/>
-      <c r="N72" s="9"/>
+      <c r="K72" s="9"/>
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="10"/>
@@ -5414,10 +4593,7 @@
       <c r="H73" s="12"/>
       <c r="I73" s="12"/>
       <c r="J73" s="12"/>
-      <c r="K73" s="12"/>
-      <c r="L73" s="12"/>
-      <c r="M73" s="11"/>
-      <c r="N73" s="13"/>
+      <c r="K73" s="13"/>
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="6"/>
@@ -5430,10 +4606,7 @@
       <c r="H74" s="8"/>
       <c r="I74" s="8"/>
       <c r="J74" s="8"/>
-      <c r="K74" s="8"/>
-      <c r="L74" s="8"/>
-      <c r="M74" s="7"/>
-      <c r="N74" s="9"/>
+      <c r="K74" s="9"/>
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="10"/>
@@ -5446,10 +4619,7 @@
       <c r="H75" s="12"/>
       <c r="I75" s="12"/>
       <c r="J75" s="12"/>
-      <c r="K75" s="12"/>
-      <c r="L75" s="12"/>
-      <c r="M75" s="11"/>
-      <c r="N75" s="13"/>
+      <c r="K75" s="13"/>
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="6"/>
@@ -5462,22 +4632,19 @@
       <c r="H76" s="8"/>
       <c r="I76" s="8"/>
       <c r="J76" s="8"/>
-      <c r="K76" s="8"/>
-      <c r="L76" s="8"/>
-      <c r="M76" s="7"/>
-      <c r="N76" s="9"/>
+      <c r="K76" s="9"/>
     </row>
   </sheetData>
   <mergeCells count="9">
     <mergeCell ref="F1:H1"/>
     <mergeCell ref="C3:D3"/>
-    <mergeCell ref="F3:I3"/>
+    <mergeCell ref="F3:H3"/>
     <mergeCell ref="C22:D22"/>
-    <mergeCell ref="F22:I22"/>
+    <mergeCell ref="F22:H22"/>
     <mergeCell ref="C41:D41"/>
-    <mergeCell ref="F41:I41"/>
+    <mergeCell ref="F41:H41"/>
     <mergeCell ref="C60:D60"/>
-    <mergeCell ref="F60:I60"/>
+    <mergeCell ref="F60:H60"/>
   </mergeCells>
   <conditionalFormatting sqref="A5:A19">
     <cfRule type="expression" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
@@ -5535,8 +4702,8 @@
       <formula>OR($A62="Accesorios",$A62="Vuelta a la calma")</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="20">
-    <dataValidation allowBlank="true" error="Un número de 0 a 10." errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="L3 N3 L22 N22 L41 N41 L60 N60" type="decimal">
+  <dataValidations count="15">
+    <dataValidation allowBlank="true" error="Un número de 0 a 10." errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="J3:K3 J22:K22 J41:K41 J60:K60" type="decimal">
       <formula1>0</formula1>
       <formula2>10</formula2>
     </dataValidation>
@@ -5564,10 +4731,6 @@
       <formula1>"Sí"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" error="Minutos del aeróbico (0,5 = 30 s)." errorStyle="stop" errorTitle="Minutos" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="K5:K19 K24:K38 K43:K57 K62:K76" type="decimal">
-      <formula1>0</formula1>
-      <formula2>600</formula2>
-    </dataValidation>
     <dataValidation allowBlank="true" error="Elige un día del desplegable." errorStyle="stop" errorTitle="Día" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C3" type="list">
       <formula1>"Lunes,Martes,Miércoles,Jueves,Viernes,Sábado,Domingo"</formula1>
       <formula2>0</formula2>
@@ -5576,10 +4739,6 @@
       <formula1>"Activación,P. Principal,Aeróbico,Accesorios,Vuelta a la calma"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" error="Elige una zona del desplegable." errorStyle="stop" errorTitle="Zona" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="L5:L19" type="list">
-      <formula1>"Z1,Z2,Z3,Z4,Z5"</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
     <dataValidation allowBlank="true" error="Elige un día del desplegable." errorStyle="stop" errorTitle="Día" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C22" type="list">
       <formula1>"Lunes,Martes,Miércoles,Jueves,Viernes,Sábado,Domingo"</formula1>
       <formula2>0</formula2>
@@ -5588,10 +4747,6 @@
       <formula1>"Activación,P. Principal,Aeróbico,Accesorios,Vuelta a la calma"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" error="Elige una zona del desplegable." errorStyle="stop" errorTitle="Zona" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="L24:L38" type="list">
-      <formula1>"Z1,Z2,Z3,Z4,Z5"</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
     <dataValidation allowBlank="true" error="Elige un día del desplegable." errorStyle="stop" errorTitle="Día" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C41" type="list">
       <formula1>"Lunes,Martes,Miércoles,Jueves,Viernes,Sábado,Domingo"</formula1>
       <formula2>0</formula2>
@@ -5600,20 +4755,12 @@
       <formula1>"Activación,P. Principal,Aeróbico,Accesorios,Vuelta a la calma"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" error="Elige una zona del desplegable." errorStyle="stop" errorTitle="Zona" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="L43:L57" type="list">
-      <formula1>"Z1,Z2,Z3,Z4,Z5"</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
     <dataValidation allowBlank="true" error="Elige un día del desplegable." errorStyle="stop" errorTitle="Día" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C60" type="list">
       <formula1>"Lunes,Martes,Miércoles,Jueves,Viernes,Sábado,Domingo"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Elige un bloque del desplegable." errorStyle="stop" errorTitle="Bloque" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="A62:A76" type="list">
       <formula1>"Activación,P. Principal,Aeróbico,Accesorios,Vuelta a la calma"</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-    <dataValidation allowBlank="true" error="Elige una zona del desplegable." errorStyle="stop" errorTitle="Zona" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="L62:L76" type="list">
-      <formula1>"Z1,Z2,Z3,Z4,Z5"</formula1>
       <formula2>0</formula2>
     </dataValidation>
   </dataValidations>
@@ -5633,25 +4780,23 @@
     <tabColor rgb="FF2F6F9F"/>
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:N76"/>
+  <dimension ref="A1:K76"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="17"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="34"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="0" width="8"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="13"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="6" style="0" width="9"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="7"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="9" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="7"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="20"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="0" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="40"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="14" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="B1" s="23" t="n">
         <f aca="false">'Semana 3'!B1+7</f>
@@ -5662,7 +4807,7 @@
         <v>al 29/11</v>
       </c>
       <c r="E1" s="17" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="F1" s="18"/>
       <c r="G1" s="18"/>
@@ -5670,29 +4815,24 @@
     </row>
     <row r="3" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="19" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="B3" s="20" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="C3" s="21"/>
       <c r="D3" s="21"/>
       <c r="E3" s="20" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="F3" s="21"/>
       <c r="G3" s="21"/>
       <c r="H3" s="21"/>
-      <c r="I3" s="21"/>
-      <c r="J3" s="22"/>
-      <c r="K3" s="20" t="s">
-        <v>46</v>
-      </c>
-      <c r="L3" s="21"/>
-      <c r="M3" s="20" t="s">
-        <v>47</v>
-      </c>
-      <c r="N3" s="21"/>
+      <c r="I3" s="22" t="s">
+        <v>43</v>
+      </c>
+      <c r="J3" s="21"/>
+      <c r="K3" s="21"/>
     </row>
     <row r="4" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="5" t="s">
@@ -5727,15 +4867,6 @@
       </c>
       <c r="K4" s="5" t="s">
         <v>25</v>
-      </c>
-      <c r="L4" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="M4" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="N4" s="5" t="s">
-        <v>28</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5749,10 +4880,7 @@
       <c r="H5" s="8"/>
       <c r="I5" s="8"/>
       <c r="J5" s="8"/>
-      <c r="K5" s="8"/>
-      <c r="L5" s="8"/>
-      <c r="M5" s="7"/>
-      <c r="N5" s="9"/>
+      <c r="K5" s="9"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="10"/>
@@ -5765,10 +4893,7 @@
       <c r="H6" s="12"/>
       <c r="I6" s="12"/>
       <c r="J6" s="12"/>
-      <c r="K6" s="12"/>
-      <c r="L6" s="12"/>
-      <c r="M6" s="11"/>
-      <c r="N6" s="13"/>
+      <c r="K6" s="13"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="6"/>
@@ -5781,10 +4906,7 @@
       <c r="H7" s="8"/>
       <c r="I7" s="8"/>
       <c r="J7" s="8"/>
-      <c r="K7" s="8"/>
-      <c r="L7" s="8"/>
-      <c r="M7" s="7"/>
-      <c r="N7" s="9"/>
+      <c r="K7" s="9"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="10"/>
@@ -5797,10 +4919,7 @@
       <c r="H8" s="12"/>
       <c r="I8" s="12"/>
       <c r="J8" s="12"/>
-      <c r="K8" s="12"/>
-      <c r="L8" s="12"/>
-      <c r="M8" s="11"/>
-      <c r="N8" s="13"/>
+      <c r="K8" s="13"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="6"/>
@@ -5813,10 +4932,7 @@
       <c r="H9" s="8"/>
       <c r="I9" s="8"/>
       <c r="J9" s="8"/>
-      <c r="K9" s="8"/>
-      <c r="L9" s="8"/>
-      <c r="M9" s="7"/>
-      <c r="N9" s="9"/>
+      <c r="K9" s="9"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="10"/>
@@ -5829,10 +4945,7 @@
       <c r="H10" s="12"/>
       <c r="I10" s="12"/>
       <c r="J10" s="12"/>
-      <c r="K10" s="12"/>
-      <c r="L10" s="12"/>
-      <c r="M10" s="11"/>
-      <c r="N10" s="13"/>
+      <c r="K10" s="13"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="6"/>
@@ -5845,10 +4958,7 @@
       <c r="H11" s="8"/>
       <c r="I11" s="8"/>
       <c r="J11" s="8"/>
-      <c r="K11" s="8"/>
-      <c r="L11" s="8"/>
-      <c r="M11" s="7"/>
-      <c r="N11" s="9"/>
+      <c r="K11" s="9"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="10"/>
@@ -5861,10 +4971,7 @@
       <c r="H12" s="12"/>
       <c r="I12" s="12"/>
       <c r="J12" s="12"/>
-      <c r="K12" s="12"/>
-      <c r="L12" s="12"/>
-      <c r="M12" s="11"/>
-      <c r="N12" s="13"/>
+      <c r="K12" s="13"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="6"/>
@@ -5877,10 +4984,7 @@
       <c r="H13" s="8"/>
       <c r="I13" s="8"/>
       <c r="J13" s="8"/>
-      <c r="K13" s="8"/>
-      <c r="L13" s="8"/>
-      <c r="M13" s="7"/>
-      <c r="N13" s="9"/>
+      <c r="K13" s="9"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="10"/>
@@ -5893,10 +4997,7 @@
       <c r="H14" s="12"/>
       <c r="I14" s="12"/>
       <c r="J14" s="12"/>
-      <c r="K14" s="12"/>
-      <c r="L14" s="12"/>
-      <c r="M14" s="11"/>
-      <c r="N14" s="13"/>
+      <c r="K14" s="13"/>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="6"/>
@@ -5909,10 +5010,7 @@
       <c r="H15" s="8"/>
       <c r="I15" s="8"/>
       <c r="J15" s="8"/>
-      <c r="K15" s="8"/>
-      <c r="L15" s="8"/>
-      <c r="M15" s="7"/>
-      <c r="N15" s="9"/>
+      <c r="K15" s="9"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="10"/>
@@ -5925,10 +5023,7 @@
       <c r="H16" s="12"/>
       <c r="I16" s="12"/>
       <c r="J16" s="12"/>
-      <c r="K16" s="12"/>
-      <c r="L16" s="12"/>
-      <c r="M16" s="11"/>
-      <c r="N16" s="13"/>
+      <c r="K16" s="13"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="6"/>
@@ -5941,10 +5036,7 @@
       <c r="H17" s="8"/>
       <c r="I17" s="8"/>
       <c r="J17" s="8"/>
-      <c r="K17" s="8"/>
-      <c r="L17" s="8"/>
-      <c r="M17" s="7"/>
-      <c r="N17" s="9"/>
+      <c r="K17" s="9"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="10"/>
@@ -5957,10 +5049,7 @@
       <c r="H18" s="12"/>
       <c r="I18" s="12"/>
       <c r="J18" s="12"/>
-      <c r="K18" s="12"/>
-      <c r="L18" s="12"/>
-      <c r="M18" s="11"/>
-      <c r="N18" s="13"/>
+      <c r="K18" s="13"/>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="6"/>
@@ -5973,36 +5062,28 @@
       <c r="H19" s="8"/>
       <c r="I19" s="8"/>
       <c r="J19" s="8"/>
-      <c r="K19" s="8"/>
-      <c r="L19" s="8"/>
-      <c r="M19" s="7"/>
-      <c r="N19" s="9"/>
+      <c r="K19" s="9"/>
     </row>
     <row r="22" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="19" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="B22" s="20" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="C22" s="21"/>
       <c r="D22" s="21"/>
       <c r="E22" s="20" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="F22" s="21"/>
       <c r="G22" s="21"/>
       <c r="H22" s="21"/>
-      <c r="I22" s="21"/>
-      <c r="J22" s="22"/>
-      <c r="K22" s="20" t="s">
-        <v>46</v>
-      </c>
-      <c r="L22" s="21"/>
-      <c r="M22" s="20" t="s">
-        <v>47</v>
-      </c>
-      <c r="N22" s="21"/>
+      <c r="I22" s="22" t="s">
+        <v>43</v>
+      </c>
+      <c r="J22" s="21"/>
+      <c r="K22" s="21"/>
     </row>
     <row r="23" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="5" t="s">
@@ -6037,15 +5118,6 @@
       </c>
       <c r="K23" s="5" t="s">
         <v>25</v>
-      </c>
-      <c r="L23" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="M23" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="N23" s="5" t="s">
-        <v>28</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6059,10 +5131,7 @@
       <c r="H24" s="8"/>
       <c r="I24" s="8"/>
       <c r="J24" s="8"/>
-      <c r="K24" s="8"/>
-      <c r="L24" s="8"/>
-      <c r="M24" s="7"/>
-      <c r="N24" s="9"/>
+      <c r="K24" s="9"/>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="10"/>
@@ -6075,10 +5144,7 @@
       <c r="H25" s="12"/>
       <c r="I25" s="12"/>
       <c r="J25" s="12"/>
-      <c r="K25" s="12"/>
-      <c r="L25" s="12"/>
-      <c r="M25" s="11"/>
-      <c r="N25" s="13"/>
+      <c r="K25" s="13"/>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="6"/>
@@ -6091,10 +5157,7 @@
       <c r="H26" s="8"/>
       <c r="I26" s="8"/>
       <c r="J26" s="8"/>
-      <c r="K26" s="8"/>
-      <c r="L26" s="8"/>
-      <c r="M26" s="7"/>
-      <c r="N26" s="9"/>
+      <c r="K26" s="9"/>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="10"/>
@@ -6107,10 +5170,7 @@
       <c r="H27" s="12"/>
       <c r="I27" s="12"/>
       <c r="J27" s="12"/>
-      <c r="K27" s="12"/>
-      <c r="L27" s="12"/>
-      <c r="M27" s="11"/>
-      <c r="N27" s="13"/>
+      <c r="K27" s="13"/>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="6"/>
@@ -6123,10 +5183,7 @@
       <c r="H28" s="8"/>
       <c r="I28" s="8"/>
       <c r="J28" s="8"/>
-      <c r="K28" s="8"/>
-      <c r="L28" s="8"/>
-      <c r="M28" s="7"/>
-      <c r="N28" s="9"/>
+      <c r="K28" s="9"/>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="10"/>
@@ -6139,10 +5196,7 @@
       <c r="H29" s="12"/>
       <c r="I29" s="12"/>
       <c r="J29" s="12"/>
-      <c r="K29" s="12"/>
-      <c r="L29" s="12"/>
-      <c r="M29" s="11"/>
-      <c r="N29" s="13"/>
+      <c r="K29" s="13"/>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="6"/>
@@ -6155,10 +5209,7 @@
       <c r="H30" s="8"/>
       <c r="I30" s="8"/>
       <c r="J30" s="8"/>
-      <c r="K30" s="8"/>
-      <c r="L30" s="8"/>
-      <c r="M30" s="7"/>
-      <c r="N30" s="9"/>
+      <c r="K30" s="9"/>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="10"/>
@@ -6171,10 +5222,7 @@
       <c r="H31" s="12"/>
       <c r="I31" s="12"/>
       <c r="J31" s="12"/>
-      <c r="K31" s="12"/>
-      <c r="L31" s="12"/>
-      <c r="M31" s="11"/>
-      <c r="N31" s="13"/>
+      <c r="K31" s="13"/>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="6"/>
@@ -6187,10 +5235,7 @@
       <c r="H32" s="8"/>
       <c r="I32" s="8"/>
       <c r="J32" s="8"/>
-      <c r="K32" s="8"/>
-      <c r="L32" s="8"/>
-      <c r="M32" s="7"/>
-      <c r="N32" s="9"/>
+      <c r="K32" s="9"/>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="10"/>
@@ -6203,10 +5248,7 @@
       <c r="H33" s="12"/>
       <c r="I33" s="12"/>
       <c r="J33" s="12"/>
-      <c r="K33" s="12"/>
-      <c r="L33" s="12"/>
-      <c r="M33" s="11"/>
-      <c r="N33" s="13"/>
+      <c r="K33" s="13"/>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="6"/>
@@ -6219,10 +5261,7 @@
       <c r="H34" s="8"/>
       <c r="I34" s="8"/>
       <c r="J34" s="8"/>
-      <c r="K34" s="8"/>
-      <c r="L34" s="8"/>
-      <c r="M34" s="7"/>
-      <c r="N34" s="9"/>
+      <c r="K34" s="9"/>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="10"/>
@@ -6235,10 +5274,7 @@
       <c r="H35" s="12"/>
       <c r="I35" s="12"/>
       <c r="J35" s="12"/>
-      <c r="K35" s="12"/>
-      <c r="L35" s="12"/>
-      <c r="M35" s="11"/>
-      <c r="N35" s="13"/>
+      <c r="K35" s="13"/>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="6"/>
@@ -6251,10 +5287,7 @@
       <c r="H36" s="8"/>
       <c r="I36" s="8"/>
       <c r="J36" s="8"/>
-      <c r="K36" s="8"/>
-      <c r="L36" s="8"/>
-      <c r="M36" s="7"/>
-      <c r="N36" s="9"/>
+      <c r="K36" s="9"/>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="10"/>
@@ -6267,10 +5300,7 @@
       <c r="H37" s="12"/>
       <c r="I37" s="12"/>
       <c r="J37" s="12"/>
-      <c r="K37" s="12"/>
-      <c r="L37" s="12"/>
-      <c r="M37" s="11"/>
-      <c r="N37" s="13"/>
+      <c r="K37" s="13"/>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="6"/>
@@ -6283,36 +5313,28 @@
       <c r="H38" s="8"/>
       <c r="I38" s="8"/>
       <c r="J38" s="8"/>
-      <c r="K38" s="8"/>
-      <c r="L38" s="8"/>
-      <c r="M38" s="7"/>
-      <c r="N38" s="9"/>
+      <c r="K38" s="9"/>
     </row>
     <row r="41" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="19" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="B41" s="20" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="C41" s="21"/>
       <c r="D41" s="21"/>
       <c r="E41" s="20" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="F41" s="21"/>
       <c r="G41" s="21"/>
       <c r="H41" s="21"/>
-      <c r="I41" s="21"/>
-      <c r="J41" s="22"/>
-      <c r="K41" s="20" t="s">
-        <v>46</v>
-      </c>
-      <c r="L41" s="21"/>
-      <c r="M41" s="20" t="s">
-        <v>47</v>
-      </c>
-      <c r="N41" s="21"/>
+      <c r="I41" s="22" t="s">
+        <v>43</v>
+      </c>
+      <c r="J41" s="21"/>
+      <c r="K41" s="21"/>
     </row>
     <row r="42" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="5" t="s">
@@ -6347,15 +5369,6 @@
       </c>
       <c r="K42" s="5" t="s">
         <v>25</v>
-      </c>
-      <c r="L42" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="M42" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="N42" s="5" t="s">
-        <v>28</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6369,10 +5382,7 @@
       <c r="H43" s="8"/>
       <c r="I43" s="8"/>
       <c r="J43" s="8"/>
-      <c r="K43" s="8"/>
-      <c r="L43" s="8"/>
-      <c r="M43" s="7"/>
-      <c r="N43" s="9"/>
+      <c r="K43" s="9"/>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="10"/>
@@ -6385,10 +5395,7 @@
       <c r="H44" s="12"/>
       <c r="I44" s="12"/>
       <c r="J44" s="12"/>
-      <c r="K44" s="12"/>
-      <c r="L44" s="12"/>
-      <c r="M44" s="11"/>
-      <c r="N44" s="13"/>
+      <c r="K44" s="13"/>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="6"/>
@@ -6401,10 +5408,7 @@
       <c r="H45" s="8"/>
       <c r="I45" s="8"/>
       <c r="J45" s="8"/>
-      <c r="K45" s="8"/>
-      <c r="L45" s="8"/>
-      <c r="M45" s="7"/>
-      <c r="N45" s="9"/>
+      <c r="K45" s="9"/>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="10"/>
@@ -6417,10 +5421,7 @@
       <c r="H46" s="12"/>
       <c r="I46" s="12"/>
       <c r="J46" s="12"/>
-      <c r="K46" s="12"/>
-      <c r="L46" s="12"/>
-      <c r="M46" s="11"/>
-      <c r="N46" s="13"/>
+      <c r="K46" s="13"/>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="6"/>
@@ -6433,10 +5434,7 @@
       <c r="H47" s="8"/>
       <c r="I47" s="8"/>
       <c r="J47" s="8"/>
-      <c r="K47" s="8"/>
-      <c r="L47" s="8"/>
-      <c r="M47" s="7"/>
-      <c r="N47" s="9"/>
+      <c r="K47" s="9"/>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="10"/>
@@ -6449,10 +5447,7 @@
       <c r="H48" s="12"/>
       <c r="I48" s="12"/>
       <c r="J48" s="12"/>
-      <c r="K48" s="12"/>
-      <c r="L48" s="12"/>
-      <c r="M48" s="11"/>
-      <c r="N48" s="13"/>
+      <c r="K48" s="13"/>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="6"/>
@@ -6465,10 +5460,7 @@
       <c r="H49" s="8"/>
       <c r="I49" s="8"/>
       <c r="J49" s="8"/>
-      <c r="K49" s="8"/>
-      <c r="L49" s="8"/>
-      <c r="M49" s="7"/>
-      <c r="N49" s="9"/>
+      <c r="K49" s="9"/>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="10"/>
@@ -6481,10 +5473,7 @@
       <c r="H50" s="12"/>
       <c r="I50" s="12"/>
       <c r="J50" s="12"/>
-      <c r="K50" s="12"/>
-      <c r="L50" s="12"/>
-      <c r="M50" s="11"/>
-      <c r="N50" s="13"/>
+      <c r="K50" s="13"/>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="6"/>
@@ -6497,10 +5486,7 @@
       <c r="H51" s="8"/>
       <c r="I51" s="8"/>
       <c r="J51" s="8"/>
-      <c r="K51" s="8"/>
-      <c r="L51" s="8"/>
-      <c r="M51" s="7"/>
-      <c r="N51" s="9"/>
+      <c r="K51" s="9"/>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="10"/>
@@ -6513,10 +5499,7 @@
       <c r="H52" s="12"/>
       <c r="I52" s="12"/>
       <c r="J52" s="12"/>
-      <c r="K52" s="12"/>
-      <c r="L52" s="12"/>
-      <c r="M52" s="11"/>
-      <c r="N52" s="13"/>
+      <c r="K52" s="13"/>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="6"/>
@@ -6529,10 +5512,7 @@
       <c r="H53" s="8"/>
       <c r="I53" s="8"/>
       <c r="J53" s="8"/>
-      <c r="K53" s="8"/>
-      <c r="L53" s="8"/>
-      <c r="M53" s="7"/>
-      <c r="N53" s="9"/>
+      <c r="K53" s="9"/>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="10"/>
@@ -6545,10 +5525,7 @@
       <c r="H54" s="12"/>
       <c r="I54" s="12"/>
       <c r="J54" s="12"/>
-      <c r="K54" s="12"/>
-      <c r="L54" s="12"/>
-      <c r="M54" s="11"/>
-      <c r="N54" s="13"/>
+      <c r="K54" s="13"/>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="6"/>
@@ -6561,10 +5538,7 @@
       <c r="H55" s="8"/>
       <c r="I55" s="8"/>
       <c r="J55" s="8"/>
-      <c r="K55" s="8"/>
-      <c r="L55" s="8"/>
-      <c r="M55" s="7"/>
-      <c r="N55" s="9"/>
+      <c r="K55" s="9"/>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="10"/>
@@ -6577,10 +5551,7 @@
       <c r="H56" s="12"/>
       <c r="I56" s="12"/>
       <c r="J56" s="12"/>
-      <c r="K56" s="12"/>
-      <c r="L56" s="12"/>
-      <c r="M56" s="11"/>
-      <c r="N56" s="13"/>
+      <c r="K56" s="13"/>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="6"/>
@@ -6593,36 +5564,28 @@
       <c r="H57" s="8"/>
       <c r="I57" s="8"/>
       <c r="J57" s="8"/>
-      <c r="K57" s="8"/>
-      <c r="L57" s="8"/>
-      <c r="M57" s="7"/>
-      <c r="N57" s="9"/>
+      <c r="K57" s="9"/>
     </row>
     <row r="60" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A60" s="19" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="B60" s="20" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="C60" s="21"/>
       <c r="D60" s="21"/>
       <c r="E60" s="20" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="F60" s="21"/>
       <c r="G60" s="21"/>
       <c r="H60" s="21"/>
-      <c r="I60" s="21"/>
-      <c r="J60" s="22"/>
-      <c r="K60" s="20" t="s">
-        <v>46</v>
-      </c>
-      <c r="L60" s="21"/>
-      <c r="M60" s="20" t="s">
-        <v>47</v>
-      </c>
-      <c r="N60" s="21"/>
+      <c r="I60" s="22" t="s">
+        <v>43</v>
+      </c>
+      <c r="J60" s="21"/>
+      <c r="K60" s="21"/>
     </row>
     <row r="61" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A61" s="5" t="s">
@@ -6657,15 +5620,6 @@
       </c>
       <c r="K61" s="5" t="s">
         <v>25</v>
-      </c>
-      <c r="L61" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="M61" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="N61" s="5" t="s">
-        <v>28</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6679,10 +5633,7 @@
       <c r="H62" s="8"/>
       <c r="I62" s="8"/>
       <c r="J62" s="8"/>
-      <c r="K62" s="8"/>
-      <c r="L62" s="8"/>
-      <c r="M62" s="7"/>
-      <c r="N62" s="9"/>
+      <c r="K62" s="9"/>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="10"/>
@@ -6695,10 +5646,7 @@
       <c r="H63" s="12"/>
       <c r="I63" s="12"/>
       <c r="J63" s="12"/>
-      <c r="K63" s="12"/>
-      <c r="L63" s="12"/>
-      <c r="M63" s="11"/>
-      <c r="N63" s="13"/>
+      <c r="K63" s="13"/>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="6"/>
@@ -6711,10 +5659,7 @@
       <c r="H64" s="8"/>
       <c r="I64" s="8"/>
       <c r="J64" s="8"/>
-      <c r="K64" s="8"/>
-      <c r="L64" s="8"/>
-      <c r="M64" s="7"/>
-      <c r="N64" s="9"/>
+      <c r="K64" s="9"/>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="10"/>
@@ -6727,10 +5672,7 @@
       <c r="H65" s="12"/>
       <c r="I65" s="12"/>
       <c r="J65" s="12"/>
-      <c r="K65" s="12"/>
-      <c r="L65" s="12"/>
-      <c r="M65" s="11"/>
-      <c r="N65" s="13"/>
+      <c r="K65" s="13"/>
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="6"/>
@@ -6743,10 +5685,7 @@
       <c r="H66" s="8"/>
       <c r="I66" s="8"/>
       <c r="J66" s="8"/>
-      <c r="K66" s="8"/>
-      <c r="L66" s="8"/>
-      <c r="M66" s="7"/>
-      <c r="N66" s="9"/>
+      <c r="K66" s="9"/>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="10"/>
@@ -6759,10 +5698,7 @@
       <c r="H67" s="12"/>
       <c r="I67" s="12"/>
       <c r="J67" s="12"/>
-      <c r="K67" s="12"/>
-      <c r="L67" s="12"/>
-      <c r="M67" s="11"/>
-      <c r="N67" s="13"/>
+      <c r="K67" s="13"/>
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="6"/>
@@ -6775,10 +5711,7 @@
       <c r="H68" s="8"/>
       <c r="I68" s="8"/>
       <c r="J68" s="8"/>
-      <c r="K68" s="8"/>
-      <c r="L68" s="8"/>
-      <c r="M68" s="7"/>
-      <c r="N68" s="9"/>
+      <c r="K68" s="9"/>
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="10"/>
@@ -6791,10 +5724,7 @@
       <c r="H69" s="12"/>
       <c r="I69" s="12"/>
       <c r="J69" s="12"/>
-      <c r="K69" s="12"/>
-      <c r="L69" s="12"/>
-      <c r="M69" s="11"/>
-      <c r="N69" s="13"/>
+      <c r="K69" s="13"/>
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="6"/>
@@ -6807,10 +5737,7 @@
       <c r="H70" s="8"/>
       <c r="I70" s="8"/>
       <c r="J70" s="8"/>
-      <c r="K70" s="8"/>
-      <c r="L70" s="8"/>
-      <c r="M70" s="7"/>
-      <c r="N70" s="9"/>
+      <c r="K70" s="9"/>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="10"/>
@@ -6823,10 +5750,7 @@
       <c r="H71" s="12"/>
       <c r="I71" s="12"/>
       <c r="J71" s="12"/>
-      <c r="K71" s="12"/>
-      <c r="L71" s="12"/>
-      <c r="M71" s="11"/>
-      <c r="N71" s="13"/>
+      <c r="K71" s="13"/>
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="6"/>
@@ -6839,10 +5763,7 @@
       <c r="H72" s="8"/>
       <c r="I72" s="8"/>
       <c r="J72" s="8"/>
-      <c r="K72" s="8"/>
-      <c r="L72" s="8"/>
-      <c r="M72" s="7"/>
-      <c r="N72" s="9"/>
+      <c r="K72" s="9"/>
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="10"/>
@@ -6855,10 +5776,7 @@
       <c r="H73" s="12"/>
       <c r="I73" s="12"/>
       <c r="J73" s="12"/>
-      <c r="K73" s="12"/>
-      <c r="L73" s="12"/>
-      <c r="M73" s="11"/>
-      <c r="N73" s="13"/>
+      <c r="K73" s="13"/>
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="6"/>
@@ -6871,10 +5789,7 @@
       <c r="H74" s="8"/>
       <c r="I74" s="8"/>
       <c r="J74" s="8"/>
-      <c r="K74" s="8"/>
-      <c r="L74" s="8"/>
-      <c r="M74" s="7"/>
-      <c r="N74" s="9"/>
+      <c r="K74" s="9"/>
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="10"/>
@@ -6887,10 +5802,7 @@
       <c r="H75" s="12"/>
       <c r="I75" s="12"/>
       <c r="J75" s="12"/>
-      <c r="K75" s="12"/>
-      <c r="L75" s="12"/>
-      <c r="M75" s="11"/>
-      <c r="N75" s="13"/>
+      <c r="K75" s="13"/>
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="6"/>
@@ -6903,22 +5815,19 @@
       <c r="H76" s="8"/>
       <c r="I76" s="8"/>
       <c r="J76" s="8"/>
-      <c r="K76" s="8"/>
-      <c r="L76" s="8"/>
-      <c r="M76" s="7"/>
-      <c r="N76" s="9"/>
+      <c r="K76" s="9"/>
     </row>
   </sheetData>
   <mergeCells count="9">
     <mergeCell ref="F1:H1"/>
     <mergeCell ref="C3:D3"/>
-    <mergeCell ref="F3:I3"/>
+    <mergeCell ref="F3:H3"/>
     <mergeCell ref="C22:D22"/>
-    <mergeCell ref="F22:I22"/>
+    <mergeCell ref="F22:H22"/>
     <mergeCell ref="C41:D41"/>
-    <mergeCell ref="F41:I41"/>
+    <mergeCell ref="F41:H41"/>
     <mergeCell ref="C60:D60"/>
-    <mergeCell ref="F60:I60"/>
+    <mergeCell ref="F60:H60"/>
   </mergeCells>
   <conditionalFormatting sqref="A5:A19">
     <cfRule type="expression" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
@@ -6976,8 +5885,8 @@
       <formula>OR($A62="Accesorios",$A62="Vuelta a la calma")</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="20">
-    <dataValidation allowBlank="true" error="Un número de 0 a 10." errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="L3 N3 L22 N22 L41 N41 L60 N60" type="decimal">
+  <dataValidations count="15">
+    <dataValidation allowBlank="true" error="Un número de 0 a 10." errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="J3:K3 J22:K22 J41:K41 J60:K60" type="decimal">
       <formula1>0</formula1>
       <formula2>10</formula2>
     </dataValidation>
@@ -7005,10 +5914,6 @@
       <formula1>"Sí"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" error="Minutos del aeróbico (0,5 = 30 s)." errorStyle="stop" errorTitle="Minutos" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="K5:K19 K24:K38 K43:K57 K62:K76" type="decimal">
-      <formula1>0</formula1>
-      <formula2>600</formula2>
-    </dataValidation>
     <dataValidation allowBlank="true" error="Elige un día del desplegable." errorStyle="stop" errorTitle="Día" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C3" type="list">
       <formula1>"Lunes,Martes,Miércoles,Jueves,Viernes,Sábado,Domingo"</formula1>
       <formula2>0</formula2>
@@ -7017,10 +5922,6 @@
       <formula1>"Activación,P. Principal,Aeróbico,Accesorios,Vuelta a la calma"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" error="Elige una zona del desplegable." errorStyle="stop" errorTitle="Zona" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="L5:L19" type="list">
-      <formula1>"Z1,Z2,Z3,Z4,Z5"</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
     <dataValidation allowBlank="true" error="Elige un día del desplegable." errorStyle="stop" errorTitle="Día" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C22" type="list">
       <formula1>"Lunes,Martes,Miércoles,Jueves,Viernes,Sábado,Domingo"</formula1>
       <formula2>0</formula2>
@@ -7029,10 +5930,6 @@
       <formula1>"Activación,P. Principal,Aeróbico,Accesorios,Vuelta a la calma"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" error="Elige una zona del desplegable." errorStyle="stop" errorTitle="Zona" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="L24:L38" type="list">
-      <formula1>"Z1,Z2,Z3,Z4,Z5"</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
     <dataValidation allowBlank="true" error="Elige un día del desplegable." errorStyle="stop" errorTitle="Día" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C41" type="list">
       <formula1>"Lunes,Martes,Miércoles,Jueves,Viernes,Sábado,Domingo"</formula1>
       <formula2>0</formula2>
@@ -7041,20 +5938,12 @@
       <formula1>"Activación,P. Principal,Aeróbico,Accesorios,Vuelta a la calma"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" error="Elige una zona del desplegable." errorStyle="stop" errorTitle="Zona" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="L43:L57" type="list">
-      <formula1>"Z1,Z2,Z3,Z4,Z5"</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
     <dataValidation allowBlank="true" error="Elige un día del desplegable." errorStyle="stop" errorTitle="Día" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C60" type="list">
       <formula1>"Lunes,Martes,Miércoles,Jueves,Viernes,Sábado,Domingo"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Elige un bloque del desplegable." errorStyle="stop" errorTitle="Bloque" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="A62:A76" type="list">
       <formula1>"Activación,P. Principal,Aeróbico,Accesorios,Vuelta a la calma"</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-    <dataValidation allowBlank="true" error="Elige una zona del desplegable." errorStyle="stop" errorTitle="Zona" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="L62:L76" type="list">
-      <formula1>"Z1,Z2,Z3,Z4,Z5"</formula1>
       <formula2>0</formula2>
     </dataValidation>
   </dataValidations>
@@ -7074,25 +5963,23 @@
     <tabColor rgb="FF2E8B6E"/>
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:N76"/>
+  <dimension ref="A1:K76"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="17"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="34"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="0" width="8"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="13"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="6" style="0" width="9"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="7"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="9" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="7"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="20"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="0" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="40"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="14" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="B1" s="23" t="n">
         <f aca="false">'Semana 4'!B1+7</f>
@@ -7103,7 +5990,7 @@
         <v>al 06/12</v>
       </c>
       <c r="E1" s="17" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="F1" s="18"/>
       <c r="G1" s="18"/>
@@ -7111,29 +5998,24 @@
     </row>
     <row r="3" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="19" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="B3" s="20" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="C3" s="21"/>
       <c r="D3" s="21"/>
       <c r="E3" s="20" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="F3" s="21"/>
       <c r="G3" s="21"/>
       <c r="H3" s="21"/>
-      <c r="I3" s="21"/>
-      <c r="J3" s="22"/>
-      <c r="K3" s="20" t="s">
-        <v>46</v>
-      </c>
-      <c r="L3" s="21"/>
-      <c r="M3" s="20" t="s">
-        <v>47</v>
-      </c>
-      <c r="N3" s="21"/>
+      <c r="I3" s="22" t="s">
+        <v>43</v>
+      </c>
+      <c r="J3" s="21"/>
+      <c r="K3" s="21"/>
     </row>
     <row r="4" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="5" t="s">
@@ -7168,15 +6050,6 @@
       </c>
       <c r="K4" s="5" t="s">
         <v>25</v>
-      </c>
-      <c r="L4" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="M4" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="N4" s="5" t="s">
-        <v>28</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7190,10 +6063,7 @@
       <c r="H5" s="8"/>
       <c r="I5" s="8"/>
       <c r="J5" s="8"/>
-      <c r="K5" s="8"/>
-      <c r="L5" s="8"/>
-      <c r="M5" s="7"/>
-      <c r="N5" s="9"/>
+      <c r="K5" s="9"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="10"/>
@@ -7206,10 +6076,7 @@
       <c r="H6" s="12"/>
       <c r="I6" s="12"/>
       <c r="J6" s="12"/>
-      <c r="K6" s="12"/>
-      <c r="L6" s="12"/>
-      <c r="M6" s="11"/>
-      <c r="N6" s="13"/>
+      <c r="K6" s="13"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="6"/>
@@ -7222,10 +6089,7 @@
       <c r="H7" s="8"/>
       <c r="I7" s="8"/>
       <c r="J7" s="8"/>
-      <c r="K7" s="8"/>
-      <c r="L7" s="8"/>
-      <c r="M7" s="7"/>
-      <c r="N7" s="9"/>
+      <c r="K7" s="9"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="10"/>
@@ -7238,10 +6102,7 @@
       <c r="H8" s="12"/>
       <c r="I8" s="12"/>
       <c r="J8" s="12"/>
-      <c r="K8" s="12"/>
-      <c r="L8" s="12"/>
-      <c r="M8" s="11"/>
-      <c r="N8" s="13"/>
+      <c r="K8" s="13"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="6"/>
@@ -7254,10 +6115,7 @@
       <c r="H9" s="8"/>
       <c r="I9" s="8"/>
       <c r="J9" s="8"/>
-      <c r="K9" s="8"/>
-      <c r="L9" s="8"/>
-      <c r="M9" s="7"/>
-      <c r="N9" s="9"/>
+      <c r="K9" s="9"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="10"/>
@@ -7270,10 +6128,7 @@
       <c r="H10" s="12"/>
       <c r="I10" s="12"/>
       <c r="J10" s="12"/>
-      <c r="K10" s="12"/>
-      <c r="L10" s="12"/>
-      <c r="M10" s="11"/>
-      <c r="N10" s="13"/>
+      <c r="K10" s="13"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="6"/>
@@ -7286,10 +6141,7 @@
       <c r="H11" s="8"/>
       <c r="I11" s="8"/>
       <c r="J11" s="8"/>
-      <c r="K11" s="8"/>
-      <c r="L11" s="8"/>
-      <c r="M11" s="7"/>
-      <c r="N11" s="9"/>
+      <c r="K11" s="9"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="10"/>
@@ -7302,10 +6154,7 @@
       <c r="H12" s="12"/>
       <c r="I12" s="12"/>
       <c r="J12" s="12"/>
-      <c r="K12" s="12"/>
-      <c r="L12" s="12"/>
-      <c r="M12" s="11"/>
-      <c r="N12" s="13"/>
+      <c r="K12" s="13"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="6"/>
@@ -7318,10 +6167,7 @@
       <c r="H13" s="8"/>
       <c r="I13" s="8"/>
       <c r="J13" s="8"/>
-      <c r="K13" s="8"/>
-      <c r="L13" s="8"/>
-      <c r="M13" s="7"/>
-      <c r="N13" s="9"/>
+      <c r="K13" s="9"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="10"/>
@@ -7334,10 +6180,7 @@
       <c r="H14" s="12"/>
       <c r="I14" s="12"/>
       <c r="J14" s="12"/>
-      <c r="K14" s="12"/>
-      <c r="L14" s="12"/>
-      <c r="M14" s="11"/>
-      <c r="N14" s="13"/>
+      <c r="K14" s="13"/>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="6"/>
@@ -7350,10 +6193,7 @@
       <c r="H15" s="8"/>
       <c r="I15" s="8"/>
       <c r="J15" s="8"/>
-      <c r="K15" s="8"/>
-      <c r="L15" s="8"/>
-      <c r="M15" s="7"/>
-      <c r="N15" s="9"/>
+      <c r="K15" s="9"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="10"/>
@@ -7366,10 +6206,7 @@
       <c r="H16" s="12"/>
       <c r="I16" s="12"/>
       <c r="J16" s="12"/>
-      <c r="K16" s="12"/>
-      <c r="L16" s="12"/>
-      <c r="M16" s="11"/>
-      <c r="N16" s="13"/>
+      <c r="K16" s="13"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="6"/>
@@ -7382,10 +6219,7 @@
       <c r="H17" s="8"/>
       <c r="I17" s="8"/>
       <c r="J17" s="8"/>
-      <c r="K17" s="8"/>
-      <c r="L17" s="8"/>
-      <c r="M17" s="7"/>
-      <c r="N17" s="9"/>
+      <c r="K17" s="9"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="10"/>
@@ -7398,10 +6232,7 @@
       <c r="H18" s="12"/>
       <c r="I18" s="12"/>
       <c r="J18" s="12"/>
-      <c r="K18" s="12"/>
-      <c r="L18" s="12"/>
-      <c r="M18" s="11"/>
-      <c r="N18" s="13"/>
+      <c r="K18" s="13"/>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="6"/>
@@ -7414,36 +6245,28 @@
       <c r="H19" s="8"/>
       <c r="I19" s="8"/>
       <c r="J19" s="8"/>
-      <c r="K19" s="8"/>
-      <c r="L19" s="8"/>
-      <c r="M19" s="7"/>
-      <c r="N19" s="9"/>
+      <c r="K19" s="9"/>
     </row>
     <row r="22" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="19" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="B22" s="20" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="C22" s="21"/>
       <c r="D22" s="21"/>
       <c r="E22" s="20" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="F22" s="21"/>
       <c r="G22" s="21"/>
       <c r="H22" s="21"/>
-      <c r="I22" s="21"/>
-      <c r="J22" s="22"/>
-      <c r="K22" s="20" t="s">
-        <v>46</v>
-      </c>
-      <c r="L22" s="21"/>
-      <c r="M22" s="20" t="s">
-        <v>47</v>
-      </c>
-      <c r="N22" s="21"/>
+      <c r="I22" s="22" t="s">
+        <v>43</v>
+      </c>
+      <c r="J22" s="21"/>
+      <c r="K22" s="21"/>
     </row>
     <row r="23" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="5" t="s">
@@ -7478,15 +6301,6 @@
       </c>
       <c r="K23" s="5" t="s">
         <v>25</v>
-      </c>
-      <c r="L23" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="M23" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="N23" s="5" t="s">
-        <v>28</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7500,10 +6314,7 @@
       <c r="H24" s="8"/>
       <c r="I24" s="8"/>
       <c r="J24" s="8"/>
-      <c r="K24" s="8"/>
-      <c r="L24" s="8"/>
-      <c r="M24" s="7"/>
-      <c r="N24" s="9"/>
+      <c r="K24" s="9"/>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="10"/>
@@ -7516,10 +6327,7 @@
       <c r="H25" s="12"/>
       <c r="I25" s="12"/>
       <c r="J25" s="12"/>
-      <c r="K25" s="12"/>
-      <c r="L25" s="12"/>
-      <c r="M25" s="11"/>
-      <c r="N25" s="13"/>
+      <c r="K25" s="13"/>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="6"/>
@@ -7532,10 +6340,7 @@
       <c r="H26" s="8"/>
       <c r="I26" s="8"/>
       <c r="J26" s="8"/>
-      <c r="K26" s="8"/>
-      <c r="L26" s="8"/>
-      <c r="M26" s="7"/>
-      <c r="N26" s="9"/>
+      <c r="K26" s="9"/>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="10"/>
@@ -7548,10 +6353,7 @@
       <c r="H27" s="12"/>
       <c r="I27" s="12"/>
       <c r="J27" s="12"/>
-      <c r="K27" s="12"/>
-      <c r="L27" s="12"/>
-      <c r="M27" s="11"/>
-      <c r="N27" s="13"/>
+      <c r="K27" s="13"/>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="6"/>
@@ -7564,10 +6366,7 @@
       <c r="H28" s="8"/>
       <c r="I28" s="8"/>
       <c r="J28" s="8"/>
-      <c r="K28" s="8"/>
-      <c r="L28" s="8"/>
-      <c r="M28" s="7"/>
-      <c r="N28" s="9"/>
+      <c r="K28" s="9"/>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="10"/>
@@ -7580,10 +6379,7 @@
       <c r="H29" s="12"/>
       <c r="I29" s="12"/>
       <c r="J29" s="12"/>
-      <c r="K29" s="12"/>
-      <c r="L29" s="12"/>
-      <c r="M29" s="11"/>
-      <c r="N29" s="13"/>
+      <c r="K29" s="13"/>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="6"/>
@@ -7596,10 +6392,7 @@
       <c r="H30" s="8"/>
       <c r="I30" s="8"/>
       <c r="J30" s="8"/>
-      <c r="K30" s="8"/>
-      <c r="L30" s="8"/>
-      <c r="M30" s="7"/>
-      <c r="N30" s="9"/>
+      <c r="K30" s="9"/>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="10"/>
@@ -7612,10 +6405,7 @@
       <c r="H31" s="12"/>
       <c r="I31" s="12"/>
       <c r="J31" s="12"/>
-      <c r="K31" s="12"/>
-      <c r="L31" s="12"/>
-      <c r="M31" s="11"/>
-      <c r="N31" s="13"/>
+      <c r="K31" s="13"/>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="6"/>
@@ -7628,10 +6418,7 @@
       <c r="H32" s="8"/>
       <c r="I32" s="8"/>
       <c r="J32" s="8"/>
-      <c r="K32" s="8"/>
-      <c r="L32" s="8"/>
-      <c r="M32" s="7"/>
-      <c r="N32" s="9"/>
+      <c r="K32" s="9"/>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="10"/>
@@ -7644,10 +6431,7 @@
       <c r="H33" s="12"/>
       <c r="I33" s="12"/>
       <c r="J33" s="12"/>
-      <c r="K33" s="12"/>
-      <c r="L33" s="12"/>
-      <c r="M33" s="11"/>
-      <c r="N33" s="13"/>
+      <c r="K33" s="13"/>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="6"/>
@@ -7660,10 +6444,7 @@
       <c r="H34" s="8"/>
       <c r="I34" s="8"/>
       <c r="J34" s="8"/>
-      <c r="K34" s="8"/>
-      <c r="L34" s="8"/>
-      <c r="M34" s="7"/>
-      <c r="N34" s="9"/>
+      <c r="K34" s="9"/>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="10"/>
@@ -7676,10 +6457,7 @@
       <c r="H35" s="12"/>
       <c r="I35" s="12"/>
       <c r="J35" s="12"/>
-      <c r="K35" s="12"/>
-      <c r="L35" s="12"/>
-      <c r="M35" s="11"/>
-      <c r="N35" s="13"/>
+      <c r="K35" s="13"/>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="6"/>
@@ -7692,10 +6470,7 @@
       <c r="H36" s="8"/>
       <c r="I36" s="8"/>
       <c r="J36" s="8"/>
-      <c r="K36" s="8"/>
-      <c r="L36" s="8"/>
-      <c r="M36" s="7"/>
-      <c r="N36" s="9"/>
+      <c r="K36" s="9"/>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="10"/>
@@ -7708,10 +6483,7 @@
       <c r="H37" s="12"/>
       <c r="I37" s="12"/>
       <c r="J37" s="12"/>
-      <c r="K37" s="12"/>
-      <c r="L37" s="12"/>
-      <c r="M37" s="11"/>
-      <c r="N37" s="13"/>
+      <c r="K37" s="13"/>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="6"/>
@@ -7724,36 +6496,28 @@
       <c r="H38" s="8"/>
       <c r="I38" s="8"/>
       <c r="J38" s="8"/>
-      <c r="K38" s="8"/>
-      <c r="L38" s="8"/>
-      <c r="M38" s="7"/>
-      <c r="N38" s="9"/>
+      <c r="K38" s="9"/>
     </row>
     <row r="41" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="19" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="B41" s="20" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="C41" s="21"/>
       <c r="D41" s="21"/>
       <c r="E41" s="20" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="F41" s="21"/>
       <c r="G41" s="21"/>
       <c r="H41" s="21"/>
-      <c r="I41" s="21"/>
-      <c r="J41" s="22"/>
-      <c r="K41" s="20" t="s">
-        <v>46</v>
-      </c>
-      <c r="L41" s="21"/>
-      <c r="M41" s="20" t="s">
-        <v>47</v>
-      </c>
-      <c r="N41" s="21"/>
+      <c r="I41" s="22" t="s">
+        <v>43</v>
+      </c>
+      <c r="J41" s="21"/>
+      <c r="K41" s="21"/>
     </row>
     <row r="42" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="5" t="s">
@@ -7788,15 +6552,6 @@
       </c>
       <c r="K42" s="5" t="s">
         <v>25</v>
-      </c>
-      <c r="L42" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="M42" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="N42" s="5" t="s">
-        <v>28</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7810,10 +6565,7 @@
       <c r="H43" s="8"/>
       <c r="I43" s="8"/>
       <c r="J43" s="8"/>
-      <c r="K43" s="8"/>
-      <c r="L43" s="8"/>
-      <c r="M43" s="7"/>
-      <c r="N43" s="9"/>
+      <c r="K43" s="9"/>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="10"/>
@@ -7826,10 +6578,7 @@
       <c r="H44" s="12"/>
       <c r="I44" s="12"/>
       <c r="J44" s="12"/>
-      <c r="K44" s="12"/>
-      <c r="L44" s="12"/>
-      <c r="M44" s="11"/>
-      <c r="N44" s="13"/>
+      <c r="K44" s="13"/>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="6"/>
@@ -7842,10 +6591,7 @@
       <c r="H45" s="8"/>
       <c r="I45" s="8"/>
       <c r="J45" s="8"/>
-      <c r="K45" s="8"/>
-      <c r="L45" s="8"/>
-      <c r="M45" s="7"/>
-      <c r="N45" s="9"/>
+      <c r="K45" s="9"/>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="10"/>
@@ -7858,10 +6604,7 @@
       <c r="H46" s="12"/>
       <c r="I46" s="12"/>
       <c r="J46" s="12"/>
-      <c r="K46" s="12"/>
-      <c r="L46" s="12"/>
-      <c r="M46" s="11"/>
-      <c r="N46" s="13"/>
+      <c r="K46" s="13"/>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="6"/>
@@ -7874,10 +6617,7 @@
       <c r="H47" s="8"/>
       <c r="I47" s="8"/>
       <c r="J47" s="8"/>
-      <c r="K47" s="8"/>
-      <c r="L47" s="8"/>
-      <c r="M47" s="7"/>
-      <c r="N47" s="9"/>
+      <c r="K47" s="9"/>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="10"/>
@@ -7890,10 +6630,7 @@
       <c r="H48" s="12"/>
       <c r="I48" s="12"/>
       <c r="J48" s="12"/>
-      <c r="K48" s="12"/>
-      <c r="L48" s="12"/>
-      <c r="M48" s="11"/>
-      <c r="N48" s="13"/>
+      <c r="K48" s="13"/>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="6"/>
@@ -7906,10 +6643,7 @@
       <c r="H49" s="8"/>
       <c r="I49" s="8"/>
       <c r="J49" s="8"/>
-      <c r="K49" s="8"/>
-      <c r="L49" s="8"/>
-      <c r="M49" s="7"/>
-      <c r="N49" s="9"/>
+      <c r="K49" s="9"/>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="10"/>
@@ -7922,10 +6656,7 @@
       <c r="H50" s="12"/>
       <c r="I50" s="12"/>
       <c r="J50" s="12"/>
-      <c r="K50" s="12"/>
-      <c r="L50" s="12"/>
-      <c r="M50" s="11"/>
-      <c r="N50" s="13"/>
+      <c r="K50" s="13"/>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="6"/>
@@ -7938,10 +6669,7 @@
       <c r="H51" s="8"/>
       <c r="I51" s="8"/>
       <c r="J51" s="8"/>
-      <c r="K51" s="8"/>
-      <c r="L51" s="8"/>
-      <c r="M51" s="7"/>
-      <c r="N51" s="9"/>
+      <c r="K51" s="9"/>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="10"/>
@@ -7954,10 +6682,7 @@
       <c r="H52" s="12"/>
       <c r="I52" s="12"/>
       <c r="J52" s="12"/>
-      <c r="K52" s="12"/>
-      <c r="L52" s="12"/>
-      <c r="M52" s="11"/>
-      <c r="N52" s="13"/>
+      <c r="K52" s="13"/>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="6"/>
@@ -7970,10 +6695,7 @@
       <c r="H53" s="8"/>
       <c r="I53" s="8"/>
       <c r="J53" s="8"/>
-      <c r="K53" s="8"/>
-      <c r="L53" s="8"/>
-      <c r="M53" s="7"/>
-      <c r="N53" s="9"/>
+      <c r="K53" s="9"/>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="10"/>
@@ -7986,10 +6708,7 @@
       <c r="H54" s="12"/>
       <c r="I54" s="12"/>
       <c r="J54" s="12"/>
-      <c r="K54" s="12"/>
-      <c r="L54" s="12"/>
-      <c r="M54" s="11"/>
-      <c r="N54" s="13"/>
+      <c r="K54" s="13"/>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="6"/>
@@ -8002,10 +6721,7 @@
       <c r="H55" s="8"/>
       <c r="I55" s="8"/>
       <c r="J55" s="8"/>
-      <c r="K55" s="8"/>
-      <c r="L55" s="8"/>
-      <c r="M55" s="7"/>
-      <c r="N55" s="9"/>
+      <c r="K55" s="9"/>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="10"/>
@@ -8018,10 +6734,7 @@
       <c r="H56" s="12"/>
       <c r="I56" s="12"/>
       <c r="J56" s="12"/>
-      <c r="K56" s="12"/>
-      <c r="L56" s="12"/>
-      <c r="M56" s="11"/>
-      <c r="N56" s="13"/>
+      <c r="K56" s="13"/>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="6"/>
@@ -8034,36 +6747,28 @@
       <c r="H57" s="8"/>
       <c r="I57" s="8"/>
       <c r="J57" s="8"/>
-      <c r="K57" s="8"/>
-      <c r="L57" s="8"/>
-      <c r="M57" s="7"/>
-      <c r="N57" s="9"/>
+      <c r="K57" s="9"/>
     </row>
     <row r="60" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A60" s="19" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="B60" s="20" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="C60" s="21"/>
       <c r="D60" s="21"/>
       <c r="E60" s="20" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="F60" s="21"/>
       <c r="G60" s="21"/>
       <c r="H60" s="21"/>
-      <c r="I60" s="21"/>
-      <c r="J60" s="22"/>
-      <c r="K60" s="20" t="s">
-        <v>46</v>
-      </c>
-      <c r="L60" s="21"/>
-      <c r="M60" s="20" t="s">
-        <v>47</v>
-      </c>
-      <c r="N60" s="21"/>
+      <c r="I60" s="22" t="s">
+        <v>43</v>
+      </c>
+      <c r="J60" s="21"/>
+      <c r="K60" s="21"/>
     </row>
     <row r="61" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A61" s="5" t="s">
@@ -8098,15 +6803,6 @@
       </c>
       <c r="K61" s="5" t="s">
         <v>25</v>
-      </c>
-      <c r="L61" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="M61" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="N61" s="5" t="s">
-        <v>28</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8120,10 +6816,7 @@
       <c r="H62" s="8"/>
       <c r="I62" s="8"/>
       <c r="J62" s="8"/>
-      <c r="K62" s="8"/>
-      <c r="L62" s="8"/>
-      <c r="M62" s="7"/>
-      <c r="N62" s="9"/>
+      <c r="K62" s="9"/>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="10"/>
@@ -8136,10 +6829,7 @@
       <c r="H63" s="12"/>
       <c r="I63" s="12"/>
       <c r="J63" s="12"/>
-      <c r="K63" s="12"/>
-      <c r="L63" s="12"/>
-      <c r="M63" s="11"/>
-      <c r="N63" s="13"/>
+      <c r="K63" s="13"/>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="6"/>
@@ -8152,10 +6842,7 @@
       <c r="H64" s="8"/>
       <c r="I64" s="8"/>
       <c r="J64" s="8"/>
-      <c r="K64" s="8"/>
-      <c r="L64" s="8"/>
-      <c r="M64" s="7"/>
-      <c r="N64" s="9"/>
+      <c r="K64" s="9"/>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="10"/>
@@ -8168,10 +6855,7 @@
       <c r="H65" s="12"/>
       <c r="I65" s="12"/>
       <c r="J65" s="12"/>
-      <c r="K65" s="12"/>
-      <c r="L65" s="12"/>
-      <c r="M65" s="11"/>
-      <c r="N65" s="13"/>
+      <c r="K65" s="13"/>
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="6"/>
@@ -8184,10 +6868,7 @@
       <c r="H66" s="8"/>
       <c r="I66" s="8"/>
       <c r="J66" s="8"/>
-      <c r="K66" s="8"/>
-      <c r="L66" s="8"/>
-      <c r="M66" s="7"/>
-      <c r="N66" s="9"/>
+      <c r="K66" s="9"/>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="10"/>
@@ -8200,10 +6881,7 @@
       <c r="H67" s="12"/>
       <c r="I67" s="12"/>
       <c r="J67" s="12"/>
-      <c r="K67" s="12"/>
-      <c r="L67" s="12"/>
-      <c r="M67" s="11"/>
-      <c r="N67" s="13"/>
+      <c r="K67" s="13"/>
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="6"/>
@@ -8216,10 +6894,7 @@
       <c r="H68" s="8"/>
       <c r="I68" s="8"/>
       <c r="J68" s="8"/>
-      <c r="K68" s="8"/>
-      <c r="L68" s="8"/>
-      <c r="M68" s="7"/>
-      <c r="N68" s="9"/>
+      <c r="K68" s="9"/>
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="10"/>
@@ -8232,10 +6907,7 @@
       <c r="H69" s="12"/>
       <c r="I69" s="12"/>
       <c r="J69" s="12"/>
-      <c r="K69" s="12"/>
-      <c r="L69" s="12"/>
-      <c r="M69" s="11"/>
-      <c r="N69" s="13"/>
+      <c r="K69" s="13"/>
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="6"/>
@@ -8248,10 +6920,7 @@
       <c r="H70" s="8"/>
       <c r="I70" s="8"/>
       <c r="J70" s="8"/>
-      <c r="K70" s="8"/>
-      <c r="L70" s="8"/>
-      <c r="M70" s="7"/>
-      <c r="N70" s="9"/>
+      <c r="K70" s="9"/>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="10"/>
@@ -8264,10 +6933,7 @@
       <c r="H71" s="12"/>
       <c r="I71" s="12"/>
       <c r="J71" s="12"/>
-      <c r="K71" s="12"/>
-      <c r="L71" s="12"/>
-      <c r="M71" s="11"/>
-      <c r="N71" s="13"/>
+      <c r="K71" s="13"/>
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="6"/>
@@ -8280,10 +6946,7 @@
       <c r="H72" s="8"/>
       <c r="I72" s="8"/>
       <c r="J72" s="8"/>
-      <c r="K72" s="8"/>
-      <c r="L72" s="8"/>
-      <c r="M72" s="7"/>
-      <c r="N72" s="9"/>
+      <c r="K72" s="9"/>
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="10"/>
@@ -8296,10 +6959,7 @@
       <c r="H73" s="12"/>
       <c r="I73" s="12"/>
       <c r="J73" s="12"/>
-      <c r="K73" s="12"/>
-      <c r="L73" s="12"/>
-      <c r="M73" s="11"/>
-      <c r="N73" s="13"/>
+      <c r="K73" s="13"/>
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="6"/>
@@ -8312,10 +6972,7 @@
       <c r="H74" s="8"/>
       <c r="I74" s="8"/>
       <c r="J74" s="8"/>
-      <c r="K74" s="8"/>
-      <c r="L74" s="8"/>
-      <c r="M74" s="7"/>
-      <c r="N74" s="9"/>
+      <c r="K74" s="9"/>
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="10"/>
@@ -8328,10 +6985,7 @@
       <c r="H75" s="12"/>
       <c r="I75" s="12"/>
       <c r="J75" s="12"/>
-      <c r="K75" s="12"/>
-      <c r="L75" s="12"/>
-      <c r="M75" s="11"/>
-      <c r="N75" s="13"/>
+      <c r="K75" s="13"/>
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="6"/>
@@ -8344,22 +6998,19 @@
       <c r="H76" s="8"/>
       <c r="I76" s="8"/>
       <c r="J76" s="8"/>
-      <c r="K76" s="8"/>
-      <c r="L76" s="8"/>
-      <c r="M76" s="7"/>
-      <c r="N76" s="9"/>
+      <c r="K76" s="9"/>
     </row>
   </sheetData>
   <mergeCells count="9">
     <mergeCell ref="F1:H1"/>
     <mergeCell ref="C3:D3"/>
-    <mergeCell ref="F3:I3"/>
+    <mergeCell ref="F3:H3"/>
     <mergeCell ref="C22:D22"/>
-    <mergeCell ref="F22:I22"/>
+    <mergeCell ref="F22:H22"/>
     <mergeCell ref="C41:D41"/>
-    <mergeCell ref="F41:I41"/>
+    <mergeCell ref="F41:H41"/>
     <mergeCell ref="C60:D60"/>
-    <mergeCell ref="F60:I60"/>
+    <mergeCell ref="F60:H60"/>
   </mergeCells>
   <conditionalFormatting sqref="A5:A19">
     <cfRule type="expression" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
@@ -8417,8 +7068,8 @@
       <formula>OR($A62="Accesorios",$A62="Vuelta a la calma")</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="20">
-    <dataValidation allowBlank="true" error="Un número de 0 a 10." errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="L3 N3 L22 N22 L41 N41 L60 N60" type="decimal">
+  <dataValidations count="15">
+    <dataValidation allowBlank="true" error="Un número de 0 a 10." errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="J3:K3 J22:K22 J41:K41 J60:K60" type="decimal">
       <formula1>0</formula1>
       <formula2>10</formula2>
     </dataValidation>
@@ -8446,10 +7097,6 @@
       <formula1>"Sí"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" error="Minutos del aeróbico (0,5 = 30 s)." errorStyle="stop" errorTitle="Minutos" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="K5:K19 K24:K38 K43:K57 K62:K76" type="decimal">
-      <formula1>0</formula1>
-      <formula2>600</formula2>
-    </dataValidation>
     <dataValidation allowBlank="true" error="Elige un día del desplegable." errorStyle="stop" errorTitle="Día" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C3" type="list">
       <formula1>"Lunes,Martes,Miércoles,Jueves,Viernes,Sábado,Domingo"</formula1>
       <formula2>0</formula2>
@@ -8458,10 +7105,6 @@
       <formula1>"Activación,P. Principal,Aeróbico,Accesorios,Vuelta a la calma"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" error="Elige una zona del desplegable." errorStyle="stop" errorTitle="Zona" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="L5:L19" type="list">
-      <formula1>"Z1,Z2,Z3,Z4,Z5"</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
     <dataValidation allowBlank="true" error="Elige un día del desplegable." errorStyle="stop" errorTitle="Día" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C22" type="list">
       <formula1>"Lunes,Martes,Miércoles,Jueves,Viernes,Sábado,Domingo"</formula1>
       <formula2>0</formula2>
@@ -8470,10 +7113,6 @@
       <formula1>"Activación,P. Principal,Aeróbico,Accesorios,Vuelta a la calma"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" error="Elige una zona del desplegable." errorStyle="stop" errorTitle="Zona" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="L24:L38" type="list">
-      <formula1>"Z1,Z2,Z3,Z4,Z5"</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
     <dataValidation allowBlank="true" error="Elige un día del desplegable." errorStyle="stop" errorTitle="Día" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C41" type="list">
       <formula1>"Lunes,Martes,Miércoles,Jueves,Viernes,Sábado,Domingo"</formula1>
       <formula2>0</formula2>
@@ -8482,20 +7121,12 @@
       <formula1>"Activación,P. Principal,Aeróbico,Accesorios,Vuelta a la calma"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" error="Elige una zona del desplegable." errorStyle="stop" errorTitle="Zona" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="L43:L57" type="list">
-      <formula1>"Z1,Z2,Z3,Z4,Z5"</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
     <dataValidation allowBlank="true" error="Elige un día del desplegable." errorStyle="stop" errorTitle="Día" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="C60" type="list">
       <formula1>"Lunes,Martes,Miércoles,Jueves,Viernes,Sábado,Domingo"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Elige un bloque del desplegable." errorStyle="stop" errorTitle="Bloque" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="A62:A76" type="list">
       <formula1>"Activación,P. Principal,Aeróbico,Accesorios,Vuelta a la calma"</formula1>
-      <formula2>0</formula2>
-    </dataValidation>
-    <dataValidation allowBlank="true" error="Elige una zona del desplegable." errorStyle="stop" errorTitle="Zona" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="L62:L76" type="list">
-      <formula1>"Z1,Z2,Z3,Z4,Z5"</formula1>
       <formula2>0</formula2>
     </dataValidation>
   </dataValidations>
